--- a/1. Database Design/Java23 QuyenPhan Database Design.xlsx
+++ b/1. Database Design/Java23 QuyenPhan Database Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java23\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDBD7EB-78F6-4816-B32D-BB2358DF7671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9244EE11-2682-4302-A5BC-A0EE2C86A733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="588" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="588" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="B2. ERD - Mô hình logic" sheetId="2" r:id="rId3"/>
     <sheet name="B3. Mô hình quan hệ" sheetId="6" r:id="rId4"/>
     <sheet name="B4. Mô hình vật lý" sheetId="4" r:id="rId5"/>
-    <sheet name="B5. Tạo dự liệu mẫu" sheetId="3" r:id="rId6"/>
+    <sheet name="B5. Tạo dữ liệu mẫu" sheetId="7" r:id="rId6"/>
+    <sheet name=" Tạo dữ liệu mẫu" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -217,6 +218,7 @@
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Quyen Ngoc Phan</author>
     <author>tc={D2762586-1568-4CA1-84B1-25C4A6B7BF3D}</author>
     <author>tc={5BB71AC4-9659-4B49-AE00-20328F749FE8}</author>
     <author>tc={B0B8351A-F8B3-4EDE-8A43-27DE73070A70}</author>
@@ -225,18 +227,42 @@
     <author>tc={757E2222-AC3E-4A43-98F1-5381EF486FA8}</author>
   </authors>
   <commentList>
-    <comment ref="K6" authorId="0" shapeId="0" xr:uid="{D2762586-1568-4CA1-84B1-25C4A6B7BF3D}">
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{D734A94E-ECE9-4657-94BA-485A93097C8B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Khi có color, sẽ có thêm tính năng chọn màu sắc để hiển thị ra chính xác hình ảnh nào của mặt hàng
+Không có color, show danh sách cách hình ảnh</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K6" authorId="1" shapeId="0" xr:uid="{D2762586-1568-4CA1-84B1-25C4A6B7BF3D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Khách
-Nhân Viên
+    Nhân Viên
 Quản Lý 
 Giám Đốc</t>
       </text>
     </comment>
-    <comment ref="L6" authorId="1" shapeId="0" xr:uid="{5BB71AC4-9659-4B49-AE00-20328F749FE8}">
+    <comment ref="L6" authorId="2" shapeId="0" xr:uid="{5BB71AC4-9659-4B49-AE00-20328F749FE8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -250,7 +276,7 @@
 Hủy đơn hàng</t>
       </text>
     </comment>
-    <comment ref="N6" authorId="2" shapeId="0" xr:uid="{B0B8351A-F8B3-4EDE-8A43-27DE73070A70}">
+    <comment ref="N6" authorId="3" shapeId="0" xr:uid="{B0B8351A-F8B3-4EDE-8A43-27DE73070A70}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -261,7 +287,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="Q7" authorId="3" shapeId="0" xr:uid="{F97C4A89-C3BD-42B8-81A3-F88B0C7B2B49}">
+    <comment ref="Q7" authorId="4" shapeId="0" xr:uid="{F97C4A89-C3BD-42B8-81A3-F88B0C7B2B49}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -269,7 +295,7 @@
     Số lượng bán của mặt hàng trong đơn hàng</t>
       </text>
     </comment>
-    <comment ref="D10" authorId="4" shapeId="0" xr:uid="{6B85BF31-59E0-4C41-93B2-A52F1794EB43}">
+    <comment ref="D10" authorId="5" shapeId="0" xr:uid="{6B85BF31-59E0-4C41-93B2-A52F1794EB43}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -277,7 +303,7 @@
     Số lượng tồn kho theo mặt hàng, kích cỡ</t>
       </text>
     </comment>
-    <comment ref="G12" authorId="5" shapeId="0" xr:uid="{757E2222-AC3E-4A43-98F1-5381EF486FA8}">
+    <comment ref="G12" authorId="6" shapeId="0" xr:uid="{757E2222-AC3E-4A43-98F1-5381EF486FA8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -290,6 +316,63 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={E646A1A1-DCBC-4F49-B1A6-A9D7B46D63E2}</author>
+    <author>tc={508B8DE6-074D-4A1A-844B-D73F6B5EBBE1}</author>
+    <author>tc={AB272FB2-F830-4CCD-A63B-0C9DA1A2AD0E}</author>
+    <author>tc={FE0DAA01-0588-4842-B2E6-3A7FF300AD2E}</author>
+    <author>tc={DECE3802-28E9-416E-BD79-0A73C13DEDAE}</author>
+  </authors>
+  <commentList>
+    <comment ref="J26" authorId="0" shapeId="0" xr:uid="{E646A1A1-DCBC-4F49-B1A6-A9D7B46D63E2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Có rất nhiều màu sắc color, rgb, hexa -&gt; sử dụng varchar để lưu chứ k tạo 1 bảng riêng</t>
+      </text>
+    </comment>
+    <comment ref="L26" authorId="1" shapeId="0" xr:uid="{508B8DE6-074D-4A1A-844B-D73F6B5EBBE1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Số lượng hàng còn lại ở thời điểm hiện tại</t>
+      </text>
+    </comment>
+    <comment ref="C40" authorId="2" shapeId="0" xr:uid="{AB272FB2-F830-4CCD-A63B-0C9DA1A2AD0E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Khách
+Nhân Viên
+Quản Lý 
+Giám Đốc</t>
+      </text>
+    </comment>
+    <comment ref="C83" authorId="3" shapeId="0" xr:uid="{FE0DAA01-0588-4842-B2E6-3A7FF300AD2E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Tiền mặt, thẻ tín dụng, thẻ ghi nợ, ví điện tử</t>
+      </text>
+    </comment>
+    <comment ref="I90" authorId="4" shapeId="0" xr:uid="{DECE3802-28E9-416E-BD79-0A73C13DEDAE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Người tạo</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={AEBDE81C-C7EB-44D3-9FD1-1E7BD5E6786F}</author>
@@ -458,7 +541,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="611">
   <si>
     <t>MatHang</t>
   </si>
@@ -1343,27 +1426,6 @@
     <t>C07_CUSTOMER_ADDRESS</t>
   </si>
   <si>
-    <t>C09_ACCOUNT_ID</t>
-  </si>
-  <si>
-    <t>T09_ACCOUNT</t>
-  </si>
-  <si>
-    <t>C09_USERNAME</t>
-  </si>
-  <si>
-    <t>C09_PASSWORD</t>
-  </si>
-  <si>
-    <t>C09_ACCOUNT_STATUS</t>
-  </si>
-  <si>
-    <t>C07_ACCOUNT_ID</t>
-  </si>
-  <si>
-    <t>C09_ROLE_ID</t>
-  </si>
-  <si>
     <t>T10_ROLE</t>
   </si>
   <si>
@@ -1451,19 +1513,7 @@
     <t>C08_EMPLOYEE_DOB</t>
   </si>
   <si>
-    <t>C08_ACCOUNT_ID</t>
-  </si>
-  <si>
     <t>C08_TITLE_ID</t>
-  </si>
-  <si>
-    <t>T14_TITLE</t>
-  </si>
-  <si>
-    <t>C14_TITLE_ID</t>
-  </si>
-  <si>
-    <t>C14_TITLE_NAME</t>
   </si>
   <si>
     <t>T15_BILL</t>
@@ -2243,17 +2293,260 @@
     <t>Nhân Viên 5</t>
   </si>
   <si>
-    <t>SHOULD BE N-N RELATIVE</t>
-  </si>
-  <si>
     <t>C06_CREATED_BY</t>
+  </si>
+  <si>
+    <t>C01_REF_ITEM_ID</t>
+  </si>
+  <si>
+    <t>T04_ITEMGROUP</t>
+  </si>
+  <si>
+    <t>C04_ITEMGROUP_ID</t>
+  </si>
+  <si>
+    <t>C04_ITEMGROUP_NAME</t>
+  </si>
+  <si>
+    <t>Sử dụng dữ liệu từ các bảng ITEM, SIZE
+---
+ITEM, SIZE có ID lẻ: AMOUNT = 125, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5
+ITEM, SIZE có ID chẵn: AMOUNT = 280, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5 + 20
+---
+1 item có thể có nhiều BUY_PRICE
+chọn BUY_PRICE của phiếu mới nhất hoặc BUY_PRICE có giá cao nhất trong tất cả các phiếu nhập</t>
+  </si>
+  <si>
+    <t>C05_COLOR_ID</t>
+  </si>
+  <si>
+    <t>Sử dụng ITEM ID từ bảng ITEM và fake default path
+----
+Cặp dữ liệu: itemId, randomColor, file://image/p_itemId.png</t>
+  </si>
+  <si>
+    <t>C07_USERNAME</t>
+  </si>
+  <si>
+    <t>C07_PASSWORD</t>
+  </si>
+  <si>
+    <t>C07_ACCOUNT_STATUS</t>
+  </si>
+  <si>
+    <t>Nếu có ROLE và TITLE thì sẽ khác nhau gì</t>
+  </si>
+  <si>
+    <t>ROLE: Khách, Nhân Viên, Quản Lý, Giám Đốc =&gt; tác động đến permission của nhân viên và khách hàng khi vào ứng dụng</t>
+  </si>
+  <si>
+    <t>TITLE: Nhân viên giữ xe, nhân viên giao hàng, nhân viên bán hàng, nhân viên chạy quảng cáo =&gt; chọn nhân viên, quản lý làm công việc phù hợp</t>
+  </si>
+  <si>
+    <t>Nhân viên giao hàng</t>
+  </si>
+  <si>
+    <t>Nhân viên bán hàng</t>
+  </si>
+  <si>
+    <t>Nhân viên giữ xe</t>
+  </si>
+  <si>
+    <t>Nhân viên chạy quảng cáo</t>
+  </si>
+  <si>
+    <t>Quản lý 1</t>
+  </si>
+  <si>
+    <t>Quản lý 2</t>
+  </si>
+  <si>
+    <t>$2a$12$VIV/HG44mCN3467Y.aEwoe6iTHNrIvr27keSCmZrVN4V7empgW/t.</t>
+  </si>
+  <si>
+    <t>random</t>
+  </si>
+  <si>
+    <t>sysdate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - customerId(day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - customerId(year)</t>
+  </si>
+  <si>
+    <t>Khách Hàng 1</t>
+  </si>
+  <si>
+    <t>Khách Hàng 2</t>
+  </si>
+  <si>
+    <t>Khách Hàng 3</t>
+  </si>
+  <si>
+    <t>Khách Hàng 4</t>
+  </si>
+  <si>
+    <t>Khách Hàng 5</t>
+  </si>
+  <si>
+    <t>Khách Hàng 6</t>
+  </si>
+  <si>
+    <t>Khách Hàng 7</t>
+  </si>
+  <si>
+    <t>Khách Hàng 8</t>
+  </si>
+  <si>
+    <t>Khách Hàng 9</t>
+  </si>
+  <si>
+    <t>Khách Hàng 10</t>
+  </si>
+  <si>
+    <t>C08_USERNAME</t>
+  </si>
+  <si>
+    <t>C08_PASSWORD</t>
+  </si>
+  <si>
+    <t>C08_ACCOUNT_STATUS</t>
+  </si>
+  <si>
+    <t>C08_ROLE</t>
+  </si>
+  <si>
+    <t>Nhân viên 11</t>
+  </si>
+  <si>
+    <t>Nhân viên 12</t>
+  </si>
+  <si>
+    <t>Nhân viên 13</t>
+  </si>
+  <si>
+    <t>nv11@gmal.com</t>
+  </si>
+  <si>
+    <t>nv12@gmal.com</t>
+  </si>
+  <si>
+    <t>nv13@gmal.com</t>
+  </si>
+  <si>
+    <t>nv11auto</t>
+  </si>
+  <si>
+    <t>nv12def</t>
+  </si>
+  <si>
+    <t>nv13auto</t>
+  </si>
+  <si>
+    <t>C13_PMETHOD_ID</t>
+  </si>
+  <si>
+    <t>C13_PMETHOD_DESC</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>Duyệt danh sách ORDER có orderId
+----
++ billId: Tự động tăng
++ deliveryFee: random [20, 28, 48, 56, 80]
++ totalOfMoney: dựa vào order, item, order detail để tính tiền</t>
+  </si>
+  <si>
+    <t>Hủy Đơn Hàng</t>
+  </si>
+  <si>
+    <t>today -  irn_id</t>
+  </si>
+  <si>
+    <t>Quản lý</t>
+  </si>
+  <si>
+    <t>6 8 9</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp A1</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp A2</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp A3</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp A4</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp A5</t>
+  </si>
+  <si>
+    <t>Lấy từ T01_ITEM</t>
+  </si>
+  <si>
+    <t>ITEM_ID || ITEM_ID - 10</t>
+  </si>
+  <si>
+    <t>random 200 400 580 600 1200</t>
+  </si>
+  <si>
+    <t>random 88 122 244 366 150</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>random 1 2 3 4 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2445,6 +2738,13 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -2496,7 +2796,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2537,21 +2837,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2669,43 +2960,19 @@
     <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2732,19 +2999,12 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2753,7 +3013,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2772,6 +3075,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>33169</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>165721</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1181057</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>10374</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2713B5C0-31E2-4DFA-AA13-104DD4729CC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1037216" y="2102097"/>
+          <a:ext cx="3666970" cy="2767148"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3044,8 +3396,7 @@
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="K6" dT="2025-03-02T14:20:09.75" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{D2762586-1568-4CA1-84B1-25C4A6B7BF3D}">
-    <text>Khách
-Nhân Viên
+    <text>Nhân Viên
 Quản Lý 
 Giám Đốc</text>
   </threadedComment>
@@ -3077,6 +3428,29 @@
 </file>
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="J26" dT="2024-04-02T12:50:53.71" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{E646A1A1-DCBC-4F49-B1A6-A9D7B46D63E2}">
+    <text>Có rất nhiều màu sắc color, rgb, hexa -&gt; sử dụng varchar để lưu chứ k tạo 1 bảng riêng</text>
+  </threadedComment>
+  <threadedComment ref="L26" dT="2024-04-02T13:53:18.17" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{508B8DE6-074D-4A1A-844B-D73F6B5EBBE1}">
+    <text>Số lượng hàng còn lại ở thời điểm hiện tại</text>
+  </threadedComment>
+  <threadedComment ref="C40" dT="2025-03-02T14:20:09.75" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{AB272FB2-F830-4CCD-A63B-0C9DA1A2AD0E}">
+    <text>Khách
+Nhân Viên
+Quản Lý 
+Giám Đốc</text>
+  </threadedComment>
+  <threadedComment ref="C83" dT="2024-04-06T14:23:17.00" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{FE0DAA01-0588-4842-B2E6-3A7FF300AD2E}">
+    <text>Tiền mặt, thẻ tín dụng, thẻ ghi nợ, ví điện tử</text>
+  </threadedComment>
+  <threadedComment ref="I90" dT="2025-03-02T14:36:28.94" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{DECE3802-28E9-416E-BD79-0A73C13DEDAE}">
+    <text>Người tạo</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="D4" dT="2024-03-19T12:47:34.71" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{AEBDE81C-C7EB-44D3-9FD1-1E7BD5E6786F}">
     <text>Các sản phầm mua vào đều chung giá, k quan tâm kích cỡ, màu sắc, chất liệu</text>
@@ -3112,21 +3486,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A4:L24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="8" width="16.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="8" width="16.88671875" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" customWidth="1"/>
-    <col min="13" max="18" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="17.44140625" customWidth="1"/>
+    <col min="13" max="18" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -3161,7 +3535,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -3196,7 +3570,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="28" t="s">
         <v>118</v>
       </c>
@@ -3231,7 +3605,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>119</v>
       </c>
@@ -3261,7 +3635,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -3291,7 +3665,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="28" t="s">
         <v>90</v>
       </c>
@@ -3314,7 +3688,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="28" t="s">
         <v>117</v>
       </c>
@@ -3337,7 +3711,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
         <v>116</v>
       </c>
@@ -3360,7 +3734,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="28" t="s">
         <v>115</v>
       </c>
@@ -3377,7 +3751,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
@@ -3391,7 +3765,7 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -3404,7 +3778,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -3417,7 +3791,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -3430,7 +3804,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -3443,7 +3817,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -3456,7 +3830,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -3469,7 +3843,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -3482,12 +3856,12 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="2:12" s="14" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:12" s="14" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3498,27 +3872,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00967ACB-CFA1-460B-A734-E9F64BF353E8}">
   <dimension ref="A2:P58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="9" width="16.85546875" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="13" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="5" width="20.6640625" customWidth="1"/>
+    <col min="6" max="9" width="16.88671875" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="11" max="13" width="18.6640625" customWidth="1"/>
     <col min="14" max="14" width="21" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" customWidth="1"/>
-    <col min="16" max="16" width="18.28515625" customWidth="1"/>
-    <col min="17" max="21" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="17.44140625" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" customWidth="1"/>
+    <col min="17" max="21" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="F2" s="14" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -3562,7 +3936,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="30" t="s">
         <v>1</v>
       </c>
@@ -3606,7 +3980,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="28" t="s">
         <v>118</v>
       </c>
@@ -3650,7 +4024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>119</v>
       </c>
@@ -3689,7 +4063,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -3722,7 +4096,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="28" t="s">
         <v>117</v>
       </c>
@@ -3748,7 +4122,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="28" t="s">
         <v>116</v>
       </c>
@@ -3772,7 +4146,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
         <v>115</v>
       </c>
@@ -3796,7 +4170,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
@@ -3816,7 +4190,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -3831,7 +4205,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -3847,7 +4221,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -3863,7 +4237,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -3879,7 +4253,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -3895,7 +4269,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -3911,7 +4285,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -3927,7 +4301,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -3943,12 +4317,12 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>65</v>
       </c>
@@ -3962,7 +4336,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="24" spans="2:16" s="14" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:16" s="14" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24"/>
       <c r="C24" t="s">
         <v>66</v>
@@ -3988,7 +4362,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
         <v>67</v>
       </c>
@@ -4017,7 +4391,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" s="8" t="s">
         <v>68</v>
       </c>
@@ -4044,7 +4418,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>69</v>
       </c>
@@ -4068,7 +4442,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="H28" s="23" t="s">
         <v>139</v>
       </c>
@@ -4085,7 +4459,7 @@
       <c r="O28" s="23"/>
       <c r="P28" s="23"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="H29" s="23" t="s">
         <v>139</v>
       </c>
@@ -4102,7 +4476,7 @@
       <c r="O29" s="23"/>
       <c r="P29" s="23"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="G30" s="31" t="s">
         <v>141</v>
       </c>
@@ -4122,14 +4496,14 @@
       <c r="O30" s="23"/>
       <c r="P30" s="23"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="N31" s="23" t="s">
         <v>101</v>
       </c>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="N32" s="4" t="s">
         <v>102</v>
       </c>
@@ -4137,7 +4511,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="N33" s="4">
         <v>1</v>
       </c>
@@ -4145,7 +4519,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="H34" t="s">
         <v>0</v>
       </c>
@@ -4156,7 +4530,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="H35" s="28" t="s">
         <v>1</v>
       </c>
@@ -4173,7 +4547,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="H36" s="23" t="s">
         <v>132</v>
       </c>
@@ -4190,7 +4564,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="H37" s="23" t="s">
         <v>133</v>
       </c>
@@ -4201,7 +4575,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="H38" s="23" t="s">
         <v>134</v>
       </c>
@@ -4215,7 +4589,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -4227,7 +4601,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
       <c r="D40" s="23"/>
@@ -4239,7 +4613,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -4251,7 +4625,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B42" s="23"/>
       <c r="C42" s="23"/>
       <c r="D42" s="23"/>
@@ -4263,7 +4637,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
         <v>160</v>
       </c>
@@ -4277,7 +4651,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B44" s="2" t="s">
         <v>104</v>
       </c>
@@ -4298,7 +4672,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B45" s="23" t="s">
         <v>159</v>
       </c>
@@ -4319,7 +4693,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B46" s="23" t="s">
         <v>159</v>
       </c>
@@ -4340,7 +4714,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B47" s="23" t="s">
         <v>159</v>
       </c>
@@ -4358,7 +4732,7 @@
       </c>
       <c r="G47" s="23"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B48" s="23"/>
       <c r="C48" s="23"/>
       <c r="D48" s="23"/>
@@ -4367,7 +4741,7 @@
       <c r="G48" s="23"/>
       <c r="H48" s="23"/>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
       <c r="D49" s="23"/>
@@ -4376,7 +4750,7 @@
       <c r="G49" s="23"/>
       <c r="H49" s="23"/>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" s="23" t="s">
         <v>127</v>
       </c>
@@ -4387,7 +4761,7 @@
       <c r="G50" s="23"/>
       <c r="H50" s="23"/>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
         <v>104</v>
       </c>
@@ -4402,7 +4776,7 @@
       <c r="G51" s="23"/>
       <c r="H51" s="23"/>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B52" s="23" t="s">
         <v>159</v>
       </c>
@@ -4417,7 +4791,7 @@
       <c r="G52" s="23"/>
       <c r="H52" s="23"/>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B53" s="23" t="s">
         <v>161</v>
       </c>
@@ -4432,7 +4806,7 @@
       <c r="G53" s="23"/>
       <c r="H53" s="23"/>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B54" s="23" t="s">
         <v>162</v>
       </c>
@@ -4447,7 +4821,7 @@
       <c r="G54" s="23"/>
       <c r="H54" s="23"/>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
       <c r="D55" s="23"/>
@@ -4456,7 +4830,7 @@
       <c r="G55" s="23"/>
       <c r="H55" s="23"/>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B56" s="23"/>
       <c r="C56" s="23"/>
       <c r="D56" s="23"/>
@@ -4465,7 +4839,7 @@
       <c r="G56" s="23"/>
       <c r="H56" s="23"/>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B57" s="23"/>
       <c r="C57" s="23"/>
       <c r="D57" s="23"/>
@@ -4474,7 +4848,7 @@
       <c r="G57" s="23"/>
       <c r="H57" s="23"/>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B58" s="23"/>
       <c r="C58" s="23"/>
       <c r="D58" s="23"/>
@@ -4493,16 +4867,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:U43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" customWidth="1"/>
-    <col min="16" max="16" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>76</v>
       </c>
@@ -4515,7 +4889,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4523,7 +4897,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -4532,10 +4906,10 @@
       </c>
       <c r="P4" s="25"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N5" s="25"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
         <v>38</v>
       </c>
@@ -4547,7 +4921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D8" s="4"/>
       <c r="P8" s="17" t="s">
         <v>54</v>
@@ -4556,7 +4930,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B9" s="5" t="s">
         <v>23</v>
       </c>
@@ -4597,7 +4971,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>40</v>
       </c>
@@ -4638,7 +5012,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>58</v>
       </c>
@@ -4673,7 +5047,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>41</v>
       </c>
@@ -4708,7 +5082,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>52</v>
       </c>
@@ -4724,14 +5098,14 @@
       <c r="Q13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="R13" s="47" t="s">
+      <c r="R13" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="S13" s="47"/>
-      <c r="T13" s="47"/>
-      <c r="U13" s="47"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="S13" s="73"/>
+      <c r="T13" s="73"/>
+      <c r="U13" s="73"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D14" s="4"/>
       <c r="O14" s="12" t="s">
         <v>38</v>
@@ -4742,20 +5116,20 @@
       <c r="Q14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="47"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="R14" s="73"/>
+      <c r="S14" s="73"/>
+      <c r="T14" s="73"/>
+      <c r="U14" s="73"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="J16" s="25"/>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="10" t="s">
         <v>32</v>
       </c>
@@ -4775,7 +5149,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -4786,7 +5160,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>33</v>
       </c>
@@ -4815,7 +5189,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="11">
         <v>1</v>
       </c>
@@ -4838,7 +5212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>49</v>
       </c>
@@ -4870,7 +5244,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <v>3</v>
       </c>
@@ -4897,7 +5271,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="G23" s="4">
         <v>4</v>
       </c>
@@ -4914,7 +5288,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="G24" s="4">
         <v>5</v>
       </c>
@@ -4928,7 +5302,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="G25" s="4">
         <v>6</v>
       </c>
@@ -4942,7 +5316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="G26" s="4">
         <v>7</v>
       </c>
@@ -4959,7 +5333,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="N27" s="25" t="s">
         <v>1</v>
       </c>
@@ -4967,7 +5341,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>64</v>
       </c>
@@ -4978,7 +5352,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>65</v>
       </c>
@@ -4989,7 +5363,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
         <v>66</v>
       </c>
@@ -5000,7 +5374,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>67</v>
       </c>
@@ -5015,7 +5389,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>68</v>
       </c>
@@ -5033,7 +5407,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>69</v>
       </c>
@@ -5044,7 +5418,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="N34">
         <v>3</v>
       </c>
@@ -5052,7 +5426,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>169</v>
       </c>
@@ -5064,7 +5438,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>170</v>
       </c>
@@ -5072,31 +5446,31 @@
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="I37" s="23"/>
       <c r="J37" s="23"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="I38" s="23"/>
       <c r="J38" s="23"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
       <c r="I39" s="23"/>
       <c r="J39" s="23"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
       <c r="I40" s="23"/>
       <c r="J40" s="23"/>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
       <c r="I42" s="26"/>
       <c r="J42" s="26"/>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
       <c r="I43" s="23"/>
       <c r="J43" s="23"/>
     </row>
@@ -5112,27 +5486,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD2C7DF-5616-418E-B427-D50946AF144B}">
   <dimension ref="A2:Q58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="9" width="16.85546875" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="13" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="5" width="20.6640625" customWidth="1"/>
+    <col min="6" max="9" width="16.88671875" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="11" max="13" width="18.6640625" customWidth="1"/>
     <col min="14" max="14" width="21" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" customWidth="1"/>
-    <col min="16" max="16" width="18.28515625" customWidth="1"/>
-    <col min="17" max="21" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="17.44140625" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" customWidth="1"/>
+    <col min="17" max="21" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="F2" s="14" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>141</v>
       </c>
@@ -5173,7 +5547,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -5217,7 +5591,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="30" t="s">
         <v>1</v>
       </c>
@@ -5261,7 +5635,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="28" t="s">
         <v>118</v>
       </c>
@@ -5305,7 +5679,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>119</v>
       </c>
@@ -5344,7 +5718,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -5377,7 +5751,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="28" t="s">
         <v>117</v>
       </c>
@@ -5403,7 +5777,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="28" t="s">
         <v>116</v>
       </c>
@@ -5427,7 +5801,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28" t="s">
         <v>115</v>
       </c>
@@ -5451,7 +5825,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
@@ -5471,7 +5845,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -5486,7 +5860,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -5502,7 +5876,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -5518,7 +5892,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -5534,7 +5908,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -5550,7 +5924,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -5566,7 +5940,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -5582,7 +5956,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -5598,12 +5972,12 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="C23" s="32" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="24" spans="2:17" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24"/>
       <c r="C24" s="16" t="s">
         <v>172</v>
@@ -5622,17 +5996,17 @@
       <c r="P24"/>
       <c r="Q24"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="C25" s="16" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="C27" s="32" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="C28" s="16" t="s">
         <v>175</v>
       </c>
@@ -5642,7 +6016,7 @@
       <c r="O28" s="23"/>
       <c r="P28" s="23"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="C29" s="16" t="s">
         <v>176</v>
       </c>
@@ -5652,47 +6026,47 @@
       <c r="O29" s="23"/>
       <c r="P29" s="23"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="L30" s="23"/>
       <c r="M30" s="23"/>
       <c r="N30" s="23"/>
       <c r="O30" s="23"/>
       <c r="P30" s="23"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
       <c r="C31" s="32" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
       <c r="C32" s="16" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C33" s="16" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C35" s="32" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C36" s="16" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C37" s="16"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C38" s="16" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="23"/>
       <c r="C39" s="33" t="s">
         <v>183</v>
@@ -5703,23 +6077,23 @@
       <c r="G39" s="23"/>
       <c r="H39" s="23"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G40" s="23"/>
       <c r="H40" s="23"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G41" s="23"/>
       <c r="H41" s="23"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G42" s="23"/>
       <c r="H42" s="23"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G43" s="23"/>
       <c r="H43" s="23"/>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
       <c r="D49" s="23"/>
@@ -5728,32 +6102,32 @@
       <c r="G49" s="23"/>
       <c r="H49" s="23"/>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F50" s="23"/>
       <c r="G50" s="23"/>
       <c r="H50" s="23"/>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F51" s="23"/>
       <c r="G51" s="23"/>
       <c r="H51" s="23"/>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F52" s="23"/>
       <c r="G52" s="23"/>
       <c r="H52" s="23"/>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F53" s="23"/>
       <c r="G53" s="23"/>
       <c r="H53" s="23"/>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F54" s="23"/>
       <c r="G54" s="23"/>
       <c r="H54" s="23"/>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
       <c r="D55" s="23"/>
@@ -5762,7 +6136,7 @@
       <c r="G55" s="23"/>
       <c r="H55" s="23"/>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B56" s="23"/>
       <c r="C56" s="23"/>
       <c r="D56" s="23"/>
@@ -5771,7 +6145,7 @@
       <c r="G56" s="23"/>
       <c r="H56" s="23"/>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B57" s="23"/>
       <c r="C57" s="23"/>
       <c r="D57" s="23"/>
@@ -5780,7 +6154,7 @@
       <c r="G57" s="23"/>
       <c r="H57" s="23"/>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B58" s="23"/>
       <c r="C58" s="23"/>
       <c r="D58" s="23"/>
@@ -5799,49 +6173,52 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:T58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" customWidth="1"/>
-    <col min="7" max="7" width="29.85546875" customWidth="1"/>
-    <col min="8" max="8" width="24.85546875" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="21.109375" customWidth="1"/>
+    <col min="7" max="7" width="29.88671875" customWidth="1"/>
+    <col min="8" max="8" width="24.88671875" customWidth="1"/>
+    <col min="9" max="9" width="21.88671875" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" customWidth="1"/>
     <col min="12" max="12" width="26" customWidth="1"/>
-    <col min="13" max="13" width="27.7109375" customWidth="1"/>
-    <col min="14" max="14" width="30.85546875" customWidth="1"/>
-    <col min="15" max="17" width="22.7109375" customWidth="1"/>
-    <col min="18" max="18" width="24.140625" customWidth="1"/>
-    <col min="19" max="19" width="35.140625" customWidth="1"/>
-    <col min="20" max="20" width="21.5703125" customWidth="1"/>
-    <col min="21" max="22" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="27.6640625" customWidth="1"/>
+    <col min="14" max="14" width="30.88671875" customWidth="1"/>
+    <col min="15" max="17" width="22.6640625" customWidth="1"/>
+    <col min="18" max="18" width="24.109375" customWidth="1"/>
+    <col min="19" max="19" width="35.109375" customWidth="1"/>
+    <col min="20" max="20" width="21.5546875" customWidth="1"/>
+    <col min="21" max="22" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>188</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="D3" s="4" t="s">
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+    </row>
+    <row r="3" spans="2:20" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="J3" s="77" t="s">
-        <v>543</v>
-      </c>
-      <c r="K3" s="77"/>
-      <c r="R3" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="R3" s="23" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>189</v>
       </c>
@@ -5864,43 +6241,39 @@
         <v>236</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>245</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="J4" s="1"/>
       <c r="K4" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>282</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="O4" s="1"/>
       <c r="P4" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="36" t="s">
         <v>190</v>
       </c>
@@ -5908,7 +6281,7 @@
         <v>197</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>215</v>
@@ -5923,43 +6296,39 @@
         <v>237</v>
       </c>
       <c r="I5" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="J5" s="36" t="s">
-        <v>244</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="J5" s="36"/>
       <c r="K5" s="36" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="N5" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="O5" s="36" t="s">
-        <v>283</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="O5" s="36"/>
       <c r="P5" s="36" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="Q5" s="36" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="R5" s="36" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="S5" s="36" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>191</v>
       </c>
@@ -5982,43 +6351,39 @@
         <v>238</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="J6" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M6" s="36" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>284</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="Q6" s="36" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="S6" s="36" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="38" t="s">
         <v>217</v>
       </c>
@@ -6039,36 +6404,36 @@
         <v>239</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>247</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="J7" s="2"/>
       <c r="K7" s="13"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="N7" s="34"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="R7" s="38" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>533</v>
+      </c>
       <c r="C8" s="2" t="s">
         <v>202</v>
       </c>
@@ -6084,29 +6449,27 @@
         <v>240</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>248</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="N8" s="34"/>
       <c r="O8" s="2"/>
       <c r="P8" s="38" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="38"/>
       <c r="C9" s="34"/>
       <c r="D9" s="2" t="s">
@@ -6121,11 +6484,9 @@
         <v>241</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>250</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -6135,11 +6496,11 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="38" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="28"/>
       <c r="C10" s="34"/>
       <c r="D10" s="2" t="s">
@@ -6154,7 +6515,7 @@
         <v>242</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -6168,20 +6529,20 @@
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="28"/>
       <c r="C11" s="34"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="28" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="I11" s="38" t="s">
-        <v>281</v>
+      <c r="I11" s="2" t="s">
+        <v>567</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -6195,20 +6556,20 @@
       <c r="S11" s="38"/>
       <c r="T11" s="38"/>
     </row>
-    <row r="12" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="34"/>
       <c r="C12" s="34"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="28" t="s">
-        <v>544</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="I12" s="38" t="s">
-        <v>280</v>
+        <v>532</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>568</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -6222,14 +6583,18 @@
       <c r="S12" s="38"/>
       <c r="T12" s="38"/>
     </row>
-    <row r="13" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="13"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="H13" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>569</v>
+      </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -6242,15 +6607,19 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="28"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>570</v>
+      </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -6263,7 +6632,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
       <c r="D15" s="2"/>
@@ -6284,7 +6653,7 @@
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
     </row>
-    <row r="16" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="34"/>
       <c r="C16" s="34"/>
       <c r="D16" s="2"/>
@@ -6305,7 +6674,7 @@
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
     </row>
-    <row r="17" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
       <c r="D17" s="2"/>
@@ -6326,7 +6695,7 @@
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
     </row>
-    <row r="18" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
       <c r="D18" s="2"/>
@@ -6347,7 +6716,7 @@
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
     </row>
-    <row r="19" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
       <c r="D19" s="2"/>
@@ -6368,7 +6737,7 @@
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
     </row>
-    <row r="20" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
       <c r="D20" s="2"/>
@@ -6389,27 +6758,27 @@
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I21" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I22" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I23" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I24" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>184</v>
       </c>
@@ -6419,15 +6788,15 @@
       <c r="I25" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="J25" s="48" t="s">
+      <c r="J25" s="74" t="s">
         <v>209</v>
       </c>
-      <c r="K25" s="48"/>
+      <c r="K25" s="74"/>
       <c r="N25" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>185</v>
       </c>
@@ -6450,7 +6819,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>186</v>
       </c>
@@ -6474,7 +6843,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>192</v>
       </c>
@@ -6495,7 +6864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B29" s="16" t="s">
         <v>187</v>
       </c>
@@ -6512,7 +6881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
       <c r="F30" t="s">
         <v>221</v>
       </c>
@@ -6529,7 +6898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
       <c r="F31" s="15" t="s">
         <v>222</v>
       </c>
@@ -6549,7 +6918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
       <c r="F32" s="15">
         <v>1</v>
       </c>
@@ -6572,9 +6941,9 @@
         <v>204</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="40" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C33" s="41"/>
       <c r="D33" s="41"/>
@@ -6583,7 +6952,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="H33" s="39" t="s">
         <v>227</v>
@@ -6598,18 +6967,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="40" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F34" s="15">
         <v>1</v>
@@ -6630,18 +6999,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="43">
         <v>1</v>
       </c>
       <c r="C35" s="43" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D35" s="43" t="s">
         <v>142</v>
       </c>
       <c r="E35" s="45" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F35" s="15">
         <v>2</v>
@@ -6650,7 +7019,7 @@
         <v>219</v>
       </c>
       <c r="H35" s="39" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="I35" s="15">
         <v>9</v>
@@ -6662,7 +7031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="43">
         <v>1</v>
       </c>
@@ -6673,7 +7042,7 @@
         <v>142</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="I36" s="15">
         <v>10</v>
@@ -6685,12 +7054,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="43">
         <v>1</v>
       </c>
       <c r="C37" s="43" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D37" s="43" t="s">
         <v>144</v>
@@ -6704,24 +7073,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="43">
         <v>2</v>
       </c>
       <c r="C38" s="43" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D38" s="43" t="s">
         <v>144</v>
       </c>
       <c r="E38" s="45" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F38" s="15" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="43">
         <v>2</v>
       </c>
@@ -6729,10 +7098,10 @@
         <v>73</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E39" s="45" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F39" s="15" t="s">
         <v>200</v>
@@ -6750,15 +7119,15 @@
         <v>228</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" s="43">
         <v>2</v>
       </c>
       <c r="C40" s="43" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E40" s="43"/>
       <c r="F40" s="15">
@@ -6777,15 +7146,15 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="43">
         <v>2</v>
       </c>
       <c r="C41" s="43" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E41" s="43"/>
       <c r="F41" s="15">
@@ -6804,7 +7173,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="43"/>
       <c r="C42" s="43"/>
       <c r="D42" s="43"/>
@@ -6823,7 +7192,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="44"/>
       <c r="C43" s="44"/>
       <c r="D43" s="44"/>
@@ -6840,7 +7209,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="42"/>
       <c r="C44" s="42"/>
       <c r="D44" s="42"/>
@@ -6857,7 +7226,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F45" s="15">
         <v>2</v>
       </c>
@@ -6870,7 +7239,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F46" s="15">
         <v>2</v>
       </c>
@@ -6883,7 +7252,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F47" s="15">
         <v>2</v>
       </c>
@@ -6896,50 +7265,50 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E49" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="50" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E50" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="51" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E51" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="53" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E53" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="54" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E54" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="56" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E56" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="57" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E57" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="58" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E58" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J2:K2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H32" r:id="rId1" xr:uid="{1A8A6682-DD81-47D1-AB9E-2DE37B892992}"/>
@@ -6949,25 +7318,2768 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId5"/>
-  <legacyDrawing r:id="rId6"/>
+  <drawing r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E46F37-4B03-4545-ABD0-F1F3CE57095A}">
+  <dimension ref="A3:L201"/>
+  <sheetFormatPr defaultColWidth="30.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="10" max="10" width="37.44140625" customWidth="1"/>
+    <col min="11" max="11" width="34.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B3" s="52" t="s">
+        <v>534</v>
+      </c>
+      <c r="C3" s="23"/>
+    </row>
+    <row r="4" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="53" t="s">
+        <v>535</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>536</v>
+      </c>
+      <c r="G4" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="21">
+        <v>1</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="G5" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="H5" s="54" t="s">
+        <v>198</v>
+      </c>
+      <c r="I5" s="54" t="s">
+        <v>201</v>
+      </c>
+      <c r="J5" s="54" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="21">
+        <v>2</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="G6" s="21">
+        <v>1</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="I6" s="21">
+        <v>0</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="21">
+        <v>3</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="G7" s="21">
+        <v>2</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="21">
+        <v>0</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="21">
+        <v>4</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="G8" s="21">
+        <v>3</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="21">
+        <v>5</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="G9" s="21">
+        <v>4</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="21">
+        <v>6</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="G10" s="21">
+        <v>5</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="I10" s="21">
+        <v>0</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="21">
+        <v>7</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="G11" s="21">
+        <v>2</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="I11" s="21">
+        <v>1</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G12" s="21">
+        <v>7</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="21">
+        <v>1</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G13" s="21">
+        <v>8</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="21">
+        <v>1</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="G14" s="21">
+        <v>9</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="21">
+        <v>1</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B15" s="53" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>217</v>
+      </c>
+      <c r="E15" s="55" t="s">
+        <v>533</v>
+      </c>
+      <c r="G15" s="21">
+        <v>10</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="I15" s="21">
+        <v>1</v>
+      </c>
+      <c r="J15" s="21" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="21">
+        <v>1</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="D16" s="21">
+        <v>1</v>
+      </c>
+      <c r="E16" s="21"/>
+    </row>
+    <row r="17" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B17" s="21">
+        <v>2</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="D17" s="21">
+        <v>1</v>
+      </c>
+      <c r="E17" s="21">
+        <v>1</v>
+      </c>
+      <c r="G17" s="52" t="s">
+        <v>221</v>
+      </c>
+      <c r="H17" s="23"/>
+    </row>
+    <row r="18" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B18" s="21">
+        <v>3</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="D18" s="21">
+        <v>1</v>
+      </c>
+      <c r="E18" s="21">
+        <v>2</v>
+      </c>
+      <c r="G18" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="H18" s="53" t="s">
+        <v>538</v>
+      </c>
+      <c r="I18" s="54" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="21">
+        <v>4</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="D19" s="21">
+        <v>2</v>
+      </c>
+      <c r="E19" s="21"/>
+      <c r="G19" s="79" t="s">
+        <v>539</v>
+      </c>
+      <c r="H19" s="79"/>
+      <c r="I19" s="79"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="21">
+        <v>5</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="D20" s="21">
+        <v>2</v>
+      </c>
+      <c r="E20" s="21"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="21">
+        <v>6</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="D21" s="21">
+        <v>3</v>
+      </c>
+      <c r="E21" s="21"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="21">
+        <v>7</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="D22" s="21">
+        <v>3</v>
+      </c>
+      <c r="E22" s="21"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="21">
+        <v>8</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="D23" s="21">
+        <v>3</v>
+      </c>
+      <c r="E23" s="21"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="21">
+        <v>9</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="D24" s="21">
+        <v>3</v>
+      </c>
+      <c r="E24" s="21"/>
+    </row>
+    <row r="25" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B25" s="21">
+        <v>10</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="D25" s="21">
+        <v>3</v>
+      </c>
+      <c r="E25" s="21">
+        <v>8</v>
+      </c>
+      <c r="G25" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+    </row>
+    <row r="26" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B26" s="21">
+        <v>11</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="D26" s="21">
+        <v>4</v>
+      </c>
+      <c r="E26" s="21"/>
+      <c r="G26" s="53" t="s">
+        <v>281</v>
+      </c>
+      <c r="H26" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="I26" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="J26" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="K26" s="54" t="s">
+        <v>213</v>
+      </c>
+      <c r="L26" s="54" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="21">
+        <v>12</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="D27" s="21">
+        <v>1</v>
+      </c>
+      <c r="E27" s="21"/>
+      <c r="G27" s="23" t="s">
+        <v>506</v>
+      </c>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="21">
+        <v>13</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="D28" s="21">
+        <v>4</v>
+      </c>
+      <c r="E28" s="21"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="77" t="s">
+        <v>537</v>
+      </c>
+      <c r="I28" s="77"/>
+      <c r="J28" s="77"/>
+      <c r="K28" s="77"/>
+      <c r="L28" s="23"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="21">
+        <v>14</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="D29" s="21">
+        <v>5</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="77"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="77"/>
+      <c r="L29" s="23"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B30" s="21">
+        <v>15</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="D30" s="21">
+        <v>5</v>
+      </c>
+      <c r="E30" s="21"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="77"/>
+      <c r="J30" s="77"/>
+      <c r="K30" s="77"/>
+      <c r="L30" s="23"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B31" s="21">
+        <v>16</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="D31" s="21">
+        <v>6</v>
+      </c>
+      <c r="E31" s="21"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="77"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="23"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B32" s="21">
+        <v>17</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="D32" s="21">
+        <v>6</v>
+      </c>
+      <c r="E32" s="21"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="77"/>
+      <c r="K32" s="77"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="21">
+        <v>18</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="D33" s="21">
+        <v>5</v>
+      </c>
+      <c r="E33" s="21"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="77"/>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34" s="21">
+        <v>19</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="D34" s="21">
+        <v>7</v>
+      </c>
+      <c r="E34" s="21">
+        <v>20</v>
+      </c>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="77"/>
+      <c r="K34" s="77"/>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35" s="21">
+        <v>20</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="D35" s="21">
+        <v>7</v>
+      </c>
+      <c r="E35" s="21"/>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="D37" s="66" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="D38" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B39" s="52" t="s">
+        <v>244</v>
+      </c>
+      <c r="D39" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B40" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="21">
+        <v>1</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B42" s="21">
+        <v>2</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B43" s="21">
+        <v>3</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B44" s="21">
+        <v>4</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B45" s="21">
+        <v>5</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B46" s="21">
+        <v>6</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B47" s="21">
+        <v>7</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B48" s="21">
+        <v>8</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B51" s="52" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B52" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="J52" s="78" t="s">
+        <v>541</v>
+      </c>
+      <c r="K52" s="78"/>
+      <c r="L52" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B53" s="21">
+        <v>1</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="D53" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E53" s="56" t="s">
+        <v>418</v>
+      </c>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="I53" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="J53" s="68" t="s">
+        <v>552</v>
+      </c>
+      <c r="K53" s="67"/>
+      <c r="L53" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B54" s="21">
+        <v>2</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="D54" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="H54" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="I54" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="J54" s="68" t="s">
+        <v>552</v>
+      </c>
+      <c r="K54" s="67"/>
+      <c r="L54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B55" s="21">
+        <v>3</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="D55" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21" t="s">
+        <v>556</v>
+      </c>
+      <c r="H55" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="I55" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="J55" s="68" t="s">
+        <v>552</v>
+      </c>
+      <c r="K55" s="67"/>
+      <c r="L55" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B56" s="21">
+        <v>4</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>560</v>
+      </c>
+      <c r="D56" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="H56" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="I56" s="21" t="s">
+        <v>429</v>
+      </c>
+      <c r="J56" s="68" t="s">
+        <v>552</v>
+      </c>
+      <c r="K56" s="67"/>
+      <c r="L56" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B57" s="21">
+        <v>5</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="D57" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>553</v>
+      </c>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="I57" s="21" t="s">
+        <v>432</v>
+      </c>
+      <c r="J57" s="68" t="s">
+        <v>552</v>
+      </c>
+      <c r="K57" s="67"/>
+      <c r="L57" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B58" s="21">
+        <v>6</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>562</v>
+      </c>
+      <c r="D58" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>434</v>
+      </c>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="I58" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="J58" s="68" t="s">
+        <v>552</v>
+      </c>
+      <c r="K58" s="67"/>
+      <c r="L58" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B59" s="21">
+        <v>7</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>563</v>
+      </c>
+      <c r="D59" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>437</v>
+      </c>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="I59" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="J59" s="68" t="s">
+        <v>552</v>
+      </c>
+      <c r="K59" s="67"/>
+      <c r="L59" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B60" s="21">
+        <v>8</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>564</v>
+      </c>
+      <c r="D60" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
+      <c r="H60" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="I60" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="J60" s="68" t="s">
+        <v>552</v>
+      </c>
+      <c r="K60" s="67"/>
+      <c r="L60" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B61" s="21">
+        <v>9</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="D61" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="I61" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="J61" s="68" t="s">
+        <v>552</v>
+      </c>
+      <c r="K61" s="67"/>
+      <c r="L61" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B62" s="21">
+        <v>10</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="D62" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>446</v>
+      </c>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="I62" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="J62" s="68" t="s">
+        <v>552</v>
+      </c>
+      <c r="K62" s="67"/>
+      <c r="L62" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L63" s="4"/>
+    </row>
+    <row r="65" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B65" s="52" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B66" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="I66" s="78" t="s">
+        <v>568</v>
+      </c>
+      <c r="J66" s="78"/>
+      <c r="K66" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="L66" s="38" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B67" s="21">
+        <v>1</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="D67" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E67" s="56" t="s">
+        <v>458</v>
+      </c>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
+      <c r="H67" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="I67" s="69" t="s">
+        <v>420</v>
+      </c>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3">
+        <v>1</v>
+      </c>
+      <c r="L67" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B68" s="21">
+        <v>2</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="D68" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="H68" s="21" t="s">
+        <v>462</v>
+      </c>
+      <c r="I68" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3">
+        <v>1</v>
+      </c>
+      <c r="L68" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B69" s="21">
+        <v>3</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="D69" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E69" s="56" t="s">
+        <v>464</v>
+      </c>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21" t="s">
+        <v>556</v>
+      </c>
+      <c r="H69" s="21" t="s">
+        <v>465</v>
+      </c>
+      <c r="I69" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3">
+        <v>1</v>
+      </c>
+      <c r="L69" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B70" s="21">
+        <v>4</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>466</v>
+      </c>
+      <c r="D70" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E70" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="H70" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="I70" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3">
+        <v>1</v>
+      </c>
+      <c r="L70" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B71" s="21">
+        <v>5</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>469</v>
+      </c>
+      <c r="D71" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E71" s="56" t="s">
+        <v>470</v>
+      </c>
+      <c r="F71" s="21" t="s">
+        <v>553</v>
+      </c>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21" t="s">
+        <v>471</v>
+      </c>
+      <c r="I71" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3">
+        <v>1</v>
+      </c>
+      <c r="L71" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B72" s="21">
+        <v>6</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="D72" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E72" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="I72" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3">
+        <v>1</v>
+      </c>
+      <c r="L72" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B73" s="21">
+        <v>7</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="D73" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E73" s="56" t="s">
+        <v>476</v>
+      </c>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21" t="s">
+        <v>477</v>
+      </c>
+      <c r="I73" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3">
+        <v>1</v>
+      </c>
+      <c r="L73" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B74" s="21">
+        <v>8</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="D74" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E74" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="I74" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3">
+        <v>1</v>
+      </c>
+      <c r="L74" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B75" s="21">
+        <v>9</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="D75" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E75" s="56" t="s">
+        <v>482</v>
+      </c>
+      <c r="F75" s="21"/>
+      <c r="G75" s="21"/>
+      <c r="H75" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="I75" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3">
+        <v>1</v>
+      </c>
+      <c r="L75" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B76" s="21">
+        <v>10</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="D76" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E76" s="21" t="s">
+        <v>485</v>
+      </c>
+      <c r="F76" s="21"/>
+      <c r="G76" s="21"/>
+      <c r="H76" s="21" t="s">
+        <v>486</v>
+      </c>
+      <c r="I76" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3">
+        <v>1</v>
+      </c>
+      <c r="L76" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B77" s="21">
+        <v>11</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>571</v>
+      </c>
+      <c r="D77" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="F77" s="21"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="I77" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3">
+        <v>1</v>
+      </c>
+      <c r="L77" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B78" s="21">
+        <v>12</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="D78" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E78" s="56" t="s">
+        <v>575</v>
+      </c>
+      <c r="F78" s="21"/>
+      <c r="G78" s="21"/>
+      <c r="H78" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="I78" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3">
+        <v>1</v>
+      </c>
+      <c r="L78" s="21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B79" s="21">
+        <v>13</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="D79" s="21">
+        <v>123456789</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="F79" s="21"/>
+      <c r="G79" s="21"/>
+      <c r="H79" s="21" t="s">
+        <v>579</v>
+      </c>
+      <c r="I79" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3">
+        <v>1</v>
+      </c>
+      <c r="L79" s="21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B82" s="52" t="s">
+        <v>261</v>
+      </c>
+      <c r="C82" s="23"/>
+    </row>
+    <row r="83" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B83" s="53" t="s">
+        <v>580</v>
+      </c>
+      <c r="C83" s="54" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B84" s="21">
+        <v>1</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B85" s="21">
+        <v>2</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B86" s="21">
+        <v>3</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B87" s="21">
+        <v>4</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B88" s="54"/>
+    </row>
+    <row r="89" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B89" s="52" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B90" s="53" t="s">
+        <v>230</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="D90" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="E90" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="F90" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H90" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="I90" s="28" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B91" s="21">
+        <v>1</v>
+      </c>
+      <c r="C91" s="21" t="s">
+        <v>582</v>
+      </c>
+      <c r="D91" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E91" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="F91" s="21">
+        <v>1</v>
+      </c>
+      <c r="G91" s="56" t="s">
+        <v>388</v>
+      </c>
+      <c r="H91" s="21">
+        <v>1</v>
+      </c>
+      <c r="I91" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B92" s="21">
+        <v>2</v>
+      </c>
+      <c r="C92" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="D92" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E92" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="F92" s="21">
+        <v>2</v>
+      </c>
+      <c r="G92" s="56" t="s">
+        <v>390</v>
+      </c>
+      <c r="H92" s="21">
+        <v>1</v>
+      </c>
+      <c r="I92" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B93" s="21">
+        <v>3</v>
+      </c>
+      <c r="C93" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="D93" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E93" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="F93" s="21">
+        <v>3</v>
+      </c>
+      <c r="G93" s="56" t="s">
+        <v>392</v>
+      </c>
+      <c r="H93" s="21">
+        <v>2</v>
+      </c>
+      <c r="I93" s="21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B94" s="21">
+        <v>4</v>
+      </c>
+      <c r="C94" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="D94" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E94" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="F94" s="21">
+        <v>4</v>
+      </c>
+      <c r="G94" s="56" t="s">
+        <v>394</v>
+      </c>
+      <c r="H94" s="21">
+        <v>2</v>
+      </c>
+      <c r="I94" s="21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B95" s="21">
+        <v>5</v>
+      </c>
+      <c r="C95" s="21" t="s">
+        <v>586</v>
+      </c>
+      <c r="D95" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E95" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="F95" s="21">
+        <v>5</v>
+      </c>
+      <c r="G95" s="56" t="s">
+        <v>396</v>
+      </c>
+      <c r="H95" s="21">
+        <v>3</v>
+      </c>
+      <c r="I95" s="21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B96" s="21">
+        <v>6</v>
+      </c>
+      <c r="C96" s="21" t="s">
+        <v>587</v>
+      </c>
+      <c r="D96" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E96" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="F96" s="21">
+        <v>6</v>
+      </c>
+      <c r="G96" s="56" t="s">
+        <v>390</v>
+      </c>
+      <c r="H96" s="21">
+        <v>3</v>
+      </c>
+      <c r="I96" s="21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B97" s="21">
+        <v>7</v>
+      </c>
+      <c r="C97" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="D97" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E97" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="F97" s="21">
+        <v>7</v>
+      </c>
+      <c r="G97" s="56" t="s">
+        <v>392</v>
+      </c>
+      <c r="H97" s="21">
+        <v>4</v>
+      </c>
+      <c r="I97" s="21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B98" s="21">
+        <v>8</v>
+      </c>
+      <c r="C98" s="21" t="s">
+        <v>589</v>
+      </c>
+      <c r="D98" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E98" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="F98" s="21">
+        <v>8</v>
+      </c>
+      <c r="G98" s="56" t="s">
+        <v>396</v>
+      </c>
+      <c r="H98" s="21">
+        <v>4</v>
+      </c>
+      <c r="I98" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B99" s="21">
+        <v>9</v>
+      </c>
+      <c r="C99" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="D99" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E99" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="F99" s="21">
+        <v>1</v>
+      </c>
+      <c r="G99" s="56" t="s">
+        <v>396</v>
+      </c>
+      <c r="H99" s="21">
+        <v>4</v>
+      </c>
+      <c r="I99" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B100" s="21">
+        <v>10</v>
+      </c>
+      <c r="C100" s="21" t="s">
+        <v>591</v>
+      </c>
+      <c r="D100" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E100" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="F100" s="21">
+        <v>2</v>
+      </c>
+      <c r="G100" s="56" t="s">
+        <v>396</v>
+      </c>
+      <c r="H100" s="21">
+        <v>4</v>
+      </c>
+      <c r="I100" s="21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" s="23" t="s">
+        <v>596</v>
+      </c>
+      <c r="B101" s="72">
+        <v>11</v>
+      </c>
+      <c r="C101" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="D101" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E101" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="F101" s="21">
+        <v>9</v>
+      </c>
+      <c r="G101" s="56" t="s">
+        <v>403</v>
+      </c>
+      <c r="H101" s="21">
+        <v>3</v>
+      </c>
+      <c r="I101" s="21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" s="23" t="s">
+        <v>596</v>
+      </c>
+      <c r="B102" s="72">
+        <v>12</v>
+      </c>
+      <c r="C102" s="21" t="s">
+        <v>593</v>
+      </c>
+      <c r="D102" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E102" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="F102" s="21">
+        <v>10</v>
+      </c>
+      <c r="G102" s="56" t="s">
+        <v>405</v>
+      </c>
+      <c r="H102" s="21">
+        <v>3</v>
+      </c>
+      <c r="I102" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" s="23" t="s">
+        <v>596</v>
+      </c>
+      <c r="B103" s="72">
+        <v>13</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>594</v>
+      </c>
+      <c r="D103" s="21">
+        <v>258369741</v>
+      </c>
+      <c r="E103" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="F103" s="21">
+        <v>5</v>
+      </c>
+      <c r="G103" s="56" t="s">
+        <v>407</v>
+      </c>
+      <c r="H103" s="21">
+        <v>1</v>
+      </c>
+      <c r="I103" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B107" s="52" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B108" s="53" t="s">
+        <v>275</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E108" s="38" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B110" s="77" t="s">
+        <v>595</v>
+      </c>
+      <c r="C110" s="75"/>
+      <c r="D110" s="75"/>
+      <c r="E110" s="75"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B111" s="75"/>
+      <c r="C111" s="75"/>
+      <c r="D111" s="75"/>
+      <c r="E111" s="75"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B112" s="75"/>
+      <c r="C112" s="75"/>
+      <c r="D112" s="75"/>
+      <c r="E112" s="75"/>
+    </row>
+    <row r="113" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B113" s="75"/>
+      <c r="C113" s="75"/>
+      <c r="D113" s="75"/>
+      <c r="E113" s="75"/>
+      <c r="F113" s="23"/>
+      <c r="G113" s="23"/>
+      <c r="H113" s="23"/>
+      <c r="I113" s="23"/>
+    </row>
+    <row r="114" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B114" s="75"/>
+      <c r="C114" s="75"/>
+      <c r="D114" s="75"/>
+      <c r="E114" s="75"/>
+      <c r="F114" s="70"/>
+      <c r="G114" s="70"/>
+      <c r="H114" s="71"/>
+      <c r="I114" s="71"/>
+    </row>
+    <row r="115" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B115" s="75"/>
+      <c r="C115" s="75"/>
+      <c r="D115" s="75"/>
+      <c r="E115" s="75"/>
+      <c r="G115" s="23"/>
+    </row>
+    <row r="116" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D116" s="23"/>
+      <c r="G116" s="23"/>
+    </row>
+    <row r="117" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D117" s="23"/>
+      <c r="G117" s="23"/>
+    </row>
+    <row r="118" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B118" s="52" t="s">
+        <v>307</v>
+      </c>
+      <c r="C118" s="23"/>
+      <c r="D118" s="23"/>
+      <c r="G118" s="23"/>
+    </row>
+    <row r="119" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B119" s="53" t="s">
+        <v>280</v>
+      </c>
+      <c r="C119" s="53" t="s">
+        <v>282</v>
+      </c>
+      <c r="D119" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="G119" s="23"/>
+    </row>
+    <row r="120" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B120" s="76" t="s">
+        <v>517</v>
+      </c>
+      <c r="C120" s="76"/>
+      <c r="D120" s="76"/>
+      <c r="G120" s="23"/>
+    </row>
+    <row r="121" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B121" s="76"/>
+      <c r="C121" s="76"/>
+      <c r="D121" s="76"/>
+      <c r="G121" s="23"/>
+    </row>
+    <row r="122" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B122" s="76"/>
+      <c r="C122" s="76"/>
+      <c r="D122" s="76"/>
+      <c r="G122" s="23"/>
+    </row>
+    <row r="123" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B123" s="21">
+        <v>1</v>
+      </c>
+      <c r="C123" s="21">
+        <v>1</v>
+      </c>
+      <c r="D123" s="21">
+        <v>2</v>
+      </c>
+      <c r="G123" s="23"/>
+    </row>
+    <row r="124" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B124" s="21">
+        <v>1</v>
+      </c>
+      <c r="C124" s="21">
+        <v>3</v>
+      </c>
+      <c r="D124" s="21">
+        <v>4</v>
+      </c>
+      <c r="G124" s="23"/>
+    </row>
+    <row r="125" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B125" s="21">
+        <v>2</v>
+      </c>
+      <c r="C125" s="21">
+        <v>4</v>
+      </c>
+      <c r="D125" s="21">
+        <v>2</v>
+      </c>
+      <c r="G125" s="23"/>
+    </row>
+    <row r="126" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B126" s="21">
+        <v>2</v>
+      </c>
+      <c r="C126" s="21">
+        <v>5</v>
+      </c>
+      <c r="D126" s="21">
+        <v>2</v>
+      </c>
+      <c r="G126" s="23"/>
+    </row>
+    <row r="127" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B127" s="21">
+        <v>3</v>
+      </c>
+      <c r="C127" s="21">
+        <v>6</v>
+      </c>
+      <c r="D127" s="21">
+        <v>4</v>
+      </c>
+      <c r="G127" s="23"/>
+    </row>
+    <row r="128" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B128" s="21">
+        <v>3</v>
+      </c>
+      <c r="C128" s="21">
+        <v>2</v>
+      </c>
+      <c r="D128" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B129" s="21">
+        <v>4</v>
+      </c>
+      <c r="C129" s="21">
+        <v>8</v>
+      </c>
+      <c r="D129" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B130" s="21">
+        <v>4</v>
+      </c>
+      <c r="C130" s="21">
+        <v>12</v>
+      </c>
+      <c r="D130" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B131" s="21">
+        <v>5</v>
+      </c>
+      <c r="C131" s="21">
+        <v>88</v>
+      </c>
+      <c r="D131" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B132" s="21">
+        <v>5</v>
+      </c>
+      <c r="C132" s="21">
+        <v>22</v>
+      </c>
+      <c r="D132" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B133" s="21">
+        <v>5</v>
+      </c>
+      <c r="C133" s="21">
+        <v>11</v>
+      </c>
+      <c r="D133" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B134" s="21">
+        <v>5</v>
+      </c>
+      <c r="C134" s="21">
+        <v>33</v>
+      </c>
+      <c r="D134" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B135" s="21">
+        <v>6</v>
+      </c>
+      <c r="C135" s="21">
+        <v>2</v>
+      </c>
+      <c r="D135" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B136" s="21">
+        <v>7</v>
+      </c>
+      <c r="C136" s="21">
+        <v>1</v>
+      </c>
+      <c r="D136" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B137" s="21">
+        <v>8</v>
+      </c>
+      <c r="C137" s="21">
+        <v>27</v>
+      </c>
+      <c r="D137" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B138" s="21">
+        <v>8</v>
+      </c>
+      <c r="C138" s="21">
+        <v>23</v>
+      </c>
+      <c r="D138" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B139" s="21">
+        <v>8</v>
+      </c>
+      <c r="C139" s="21">
+        <v>98</v>
+      </c>
+      <c r="D139" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B140" s="21">
+        <v>9</v>
+      </c>
+      <c r="C140" s="21">
+        <v>100</v>
+      </c>
+      <c r="D140" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B141" s="21">
+        <v>9</v>
+      </c>
+      <c r="C141" s="21">
+        <v>11</v>
+      </c>
+      <c r="D141" s="21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B142" s="21">
+        <v>9</v>
+      </c>
+      <c r="C142" s="21">
+        <v>45</v>
+      </c>
+      <c r="D142" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B143" s="21">
+        <v>9</v>
+      </c>
+      <c r="C143" s="21">
+        <v>22</v>
+      </c>
+      <c r="D143" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B144" s="21">
+        <v>9</v>
+      </c>
+      <c r="C144" s="21">
+        <v>32</v>
+      </c>
+      <c r="D144" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B145" s="21">
+        <v>10</v>
+      </c>
+      <c r="C145" s="21">
+        <v>18</v>
+      </c>
+      <c r="D145" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B146" s="21">
+        <v>10</v>
+      </c>
+      <c r="C146" s="21">
+        <v>29</v>
+      </c>
+      <c r="D146" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B147" s="21">
+        <v>11</v>
+      </c>
+      <c r="C147" s="21">
+        <v>33</v>
+      </c>
+      <c r="D147" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B148" s="21">
+        <v>11</v>
+      </c>
+      <c r="C148" s="21">
+        <v>65</v>
+      </c>
+      <c r="D148" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B149" s="21">
+        <v>11</v>
+      </c>
+      <c r="C149" s="21">
+        <v>1</v>
+      </c>
+      <c r="D149" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B150" s="21">
+        <v>11</v>
+      </c>
+      <c r="C150" s="21">
+        <v>2</v>
+      </c>
+      <c r="D150" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B151" s="21">
+        <v>11</v>
+      </c>
+      <c r="C151" s="21">
+        <v>5</v>
+      </c>
+      <c r="D151" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B152" s="21">
+        <v>11</v>
+      </c>
+      <c r="C152" s="21">
+        <v>7</v>
+      </c>
+      <c r="D152" s="21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B153" s="21">
+        <v>12</v>
+      </c>
+      <c r="C153" s="21">
+        <v>55</v>
+      </c>
+      <c r="D153" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B154" s="21">
+        <v>13</v>
+      </c>
+      <c r="C154" s="21">
+        <v>92</v>
+      </c>
+      <c r="D154" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B155" s="21">
+        <v>13</v>
+      </c>
+      <c r="C155" s="21">
+        <v>14</v>
+      </c>
+      <c r="D155" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B159" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B160" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D160" s="38" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B161" s="21">
+        <v>1</v>
+      </c>
+      <c r="C161" s="21"/>
+      <c r="D161" s="21"/>
+    </row>
+    <row r="162" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B162" s="21">
+        <v>2</v>
+      </c>
+      <c r="C162" s="21"/>
+      <c r="D162" s="21"/>
+    </row>
+    <row r="163" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B163" s="21">
+        <v>3</v>
+      </c>
+      <c r="C163" s="21"/>
+      <c r="D163" s="21"/>
+    </row>
+    <row r="164" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B164" s="21">
+        <v>4</v>
+      </c>
+      <c r="C164" s="21"/>
+      <c r="D164" s="21"/>
+    </row>
+    <row r="165" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B165" s="21">
+        <v>5</v>
+      </c>
+      <c r="C165" s="56" t="s">
+        <v>597</v>
+      </c>
+      <c r="D165" s="21" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B166" s="21">
+        <v>6</v>
+      </c>
+      <c r="C166" s="21"/>
+      <c r="D166" s="56" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B167" s="21">
+        <v>7</v>
+      </c>
+      <c r="C167" s="21"/>
+      <c r="D167" s="21"/>
+    </row>
+    <row r="168" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B168" s="21">
+        <v>8</v>
+      </c>
+      <c r="C168" s="21"/>
+      <c r="D168" s="21"/>
+    </row>
+    <row r="169" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B169" s="21">
+        <v>9</v>
+      </c>
+      <c r="C169" s="21"/>
+      <c r="D169" s="21"/>
+    </row>
+    <row r="170" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B170" s="21">
+        <v>10</v>
+      </c>
+      <c r="C170" s="21"/>
+      <c r="D170" s="21"/>
+    </row>
+    <row r="173" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B173" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B174" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B175" s="3">
+        <v>1</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D175" s="3">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B176" s="3">
+        <v>2</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="D176" s="3">
+        <v>23456</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B177" s="3">
+        <v>3</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D177" s="3">
+        <v>34567</v>
+      </c>
+    </row>
+    <row r="178" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B178" s="3">
+        <v>4</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="D178" s="3">
+        <v>72727</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B179" s="3">
+        <v>5</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D179" s="3">
+        <v>28282</v>
+      </c>
+    </row>
+    <row r="182" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B182" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C182" s="23"/>
+      <c r="D182" s="23"/>
+      <c r="E182" s="23"/>
+      <c r="F182" s="23"/>
+    </row>
+    <row r="183" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B183" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="C183" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F183" s="38" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="184" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B184" s="23" t="s">
+        <v>606</v>
+      </c>
+      <c r="C184" s="23" t="s">
+        <v>605</v>
+      </c>
+      <c r="D184" s="23" t="s">
+        <v>607</v>
+      </c>
+      <c r="E184" s="23" t="s">
+        <v>608</v>
+      </c>
+      <c r="F184" s="23" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="185" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B185" s="23"/>
+      <c r="C185" s="23"/>
+      <c r="D185" s="23"/>
+      <c r="E185" s="23"/>
+      <c r="F185" s="23"/>
+    </row>
+    <row r="186" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B186" s="23">
+        <v>1</v>
+      </c>
+      <c r="C186" s="23">
+        <v>1</v>
+      </c>
+      <c r="D186" s="23"/>
+      <c r="E186" s="23"/>
+      <c r="F186" s="23"/>
+    </row>
+    <row r="187" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B187" s="23">
+        <v>2</v>
+      </c>
+      <c r="C187" s="23">
+        <v>2</v>
+      </c>
+      <c r="D187" s="23"/>
+      <c r="E187" s="23"/>
+      <c r="F187" s="23"/>
+    </row>
+    <row r="188" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B188" s="23">
+        <v>3</v>
+      </c>
+      <c r="C188" s="23">
+        <v>3</v>
+      </c>
+      <c r="D188" s="23"/>
+      <c r="E188" s="23"/>
+      <c r="F188" s="23"/>
+    </row>
+    <row r="189" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B189" s="23">
+        <v>4</v>
+      </c>
+      <c r="C189" s="23">
+        <v>4</v>
+      </c>
+      <c r="D189" s="23"/>
+      <c r="E189" s="23"/>
+      <c r="F189" s="23"/>
+    </row>
+    <row r="190" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B190" s="23">
+        <v>5</v>
+      </c>
+      <c r="C190" s="23">
+        <v>5</v>
+      </c>
+      <c r="D190" s="23"/>
+      <c r="E190" s="23"/>
+      <c r="F190" s="23"/>
+    </row>
+    <row r="191" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B191" s="23">
+        <v>6</v>
+      </c>
+      <c r="C191" s="23">
+        <v>6</v>
+      </c>
+      <c r="D191" s="23"/>
+      <c r="E191" s="23"/>
+      <c r="F191" s="23"/>
+    </row>
+    <row r="192" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B192" s="23"/>
+      <c r="C192" s="23" t="s">
+        <v>609</v>
+      </c>
+      <c r="D192" s="23"/>
+      <c r="E192" s="23"/>
+      <c r="F192" s="23"/>
+    </row>
+    <row r="193" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B193" s="23">
+        <v>10</v>
+      </c>
+      <c r="C193" s="23">
+        <v>10</v>
+      </c>
+      <c r="D193" s="23"/>
+      <c r="E193" s="23"/>
+      <c r="F193" s="23"/>
+    </row>
+    <row r="194" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B194" s="23">
+        <v>1</v>
+      </c>
+      <c r="C194" s="23">
+        <v>11</v>
+      </c>
+      <c r="D194" s="23"/>
+      <c r="E194" s="23"/>
+      <c r="F194" s="23"/>
+    </row>
+    <row r="195" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B195" s="23"/>
+      <c r="C195" s="23" t="s">
+        <v>609</v>
+      </c>
+      <c r="D195" s="23"/>
+      <c r="E195" s="23"/>
+      <c r="F195" s="23"/>
+    </row>
+    <row r="196" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B196" s="23">
+        <v>10</v>
+      </c>
+      <c r="C196" s="23">
+        <v>20</v>
+      </c>
+      <c r="D196" s="4"/>
+      <c r="E196" s="4"/>
+      <c r="F196" s="4"/>
+    </row>
+    <row r="197" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B197" s="4"/>
+      <c r="C197" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="D197" s="4"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4"/>
+    </row>
+    <row r="198" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B198" s="81">
+        <v>3</v>
+      </c>
+      <c r="C198" s="81">
+        <v>1</v>
+      </c>
+      <c r="D198" s="4"/>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4"/>
+    </row>
+    <row r="199" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B199" s="81">
+        <v>6</v>
+      </c>
+      <c r="C199" s="81">
+        <v>5</v>
+      </c>
+      <c r="D199" s="4"/>
+      <c r="E199" s="4"/>
+      <c r="F199" s="4"/>
+    </row>
+    <row r="200" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B200" s="81">
+        <v>9</v>
+      </c>
+      <c r="C200" s="81">
+        <v>10</v>
+      </c>
+      <c r="D200" s="4"/>
+      <c r="E200" s="4"/>
+      <c r="F200" s="4"/>
+    </row>
+    <row r="201" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B201" s="4"/>
+      <c r="C201" s="4"/>
+      <c r="D201" s="4"/>
+      <c r="E201" s="4"/>
+      <c r="F201" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B120:D122"/>
+    <mergeCell ref="B110:E115"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="H28:K34"/>
+    <mergeCell ref="G19:I22"/>
+    <mergeCell ref="J52:K52"/>
+  </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B3:AI135"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="71"/>
-    <col min="2" max="14" width="28.7109375" style="71" customWidth="1"/>
-    <col min="15" max="32" width="9.140625" style="71"/>
-    <col min="33" max="33" width="17.7109375" style="71" customWidth="1"/>
-    <col min="34" max="34" width="16" style="71" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="71"/>
+    <col min="2" max="14" width="28.6640625" customWidth="1"/>
+    <col min="33" max="33" width="17.6640625" customWidth="1"/>
+    <col min="34" max="34" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="60" t="s">
+    <row r="3" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B3" s="52" t="s">
         <v>189</v>
       </c>
       <c r="C3" s="23"/>
@@ -6983,41 +10095,41 @@
       <c r="M3" s="23"/>
       <c r="N3" s="23"/>
     </row>
-    <row r="4" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="61" t="s">
+    <row r="4" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="54" t="s">
         <v>191</v>
       </c>
-      <c r="D4" s="62" t="s">
-        <v>321</v>
-      </c>
-      <c r="E4" s="63" t="s">
+      <c r="D4" s="54" t="s">
+        <v>310</v>
+      </c>
+      <c r="E4" s="55" t="s">
         <v>217</v>
       </c>
       <c r="F4" s="23"/>
-      <c r="G4" s="60" t="s">
-        <v>322</v>
+      <c r="G4" s="52" t="s">
+        <v>311</v>
       </c>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="60" t="s">
-        <v>323</v>
+      <c r="J4" s="52" t="s">
+        <v>312</v>
       </c>
       <c r="K4" s="23"/>
       <c r="L4" s="23"/>
-      <c r="M4" s="60" t="s">
-        <v>324</v>
+      <c r="M4" s="52" t="s">
+        <v>313</v>
       </c>
       <c r="N4" s="23"/>
     </row>
-    <row r="5" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="21">
         <v>1</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="D5" s="21">
         <v>100</v>
@@ -7026,42 +10138,42 @@
         <v>1</v>
       </c>
       <c r="F5" s="23"/>
-      <c r="G5" s="61" t="s">
-        <v>326</v>
-      </c>
-      <c r="H5" s="62" t="s">
-        <v>327</v>
+      <c r="G5" s="53" t="s">
+        <v>315</v>
+      </c>
+      <c r="H5" s="54" t="s">
+        <v>316</v>
       </c>
       <c r="I5" s="23"/>
-      <c r="J5" s="61" t="s">
-        <v>328</v>
-      </c>
-      <c r="K5" s="62" t="s">
-        <v>329</v>
+      <c r="J5" s="53" t="s">
+        <v>317</v>
+      </c>
+      <c r="K5" s="54" t="s">
+        <v>318</v>
       </c>
       <c r="L5" s="23"/>
-      <c r="M5" s="61" t="s">
-        <v>281</v>
-      </c>
-      <c r="N5" s="62" t="s">
-        <v>330</v>
-      </c>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="51"/>
-      <c r="T5" s="51"/>
-      <c r="U5" s="51"/>
-      <c r="V5" s="51"/>
-      <c r="W5" s="51"/>
-      <c r="X5" s="51"/>
-      <c r="Y5" s="51"/>
-    </row>
-    <row r="6" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="M5" s="53" t="s">
+        <v>273</v>
+      </c>
+      <c r="N5" s="54" t="s">
+        <v>319</v>
+      </c>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+    </row>
+    <row r="6" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B6" s="21">
         <v>2</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="D6" s="21">
         <v>60</v>
@@ -7074,38 +10186,38 @@
         <v>1</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="21">
         <v>1</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="L6" s="23"/>
       <c r="M6" s="21">
         <v>1</v>
       </c>
       <c r="N6" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="51"/>
-      <c r="V6" s="51"/>
-      <c r="W6" s="51"/>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="51"/>
-    </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+    </row>
+    <row r="7" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B7" s="21">
         <v>3</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="D7" s="21">
         <v>80</v>
@@ -7118,7 +10230,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="21">
@@ -7132,24 +10244,24 @@
         <v>2</v>
       </c>
       <c r="N7" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="51"/>
-      <c r="W7" s="51"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="51"/>
-    </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+    </row>
+    <row r="8" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B8" s="21">
         <v>4</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="D8" s="21">
         <v>40</v>
@@ -7162,38 +10274,38 @@
         <v>3</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="21">
         <v>3</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="L8" s="23"/>
       <c r="M8" s="21">
         <v>3</v>
       </c>
       <c r="N8" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="51"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="51"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-    </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+    </row>
+    <row r="9" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B9" s="21">
         <v>5</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="D9" s="21">
         <v>60</v>
@@ -7206,35 +10318,35 @@
         <v>4</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="I9" s="23"/>
       <c r="J9" s="21">
         <v>4</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="L9" s="23"/>
       <c r="M9" s="21">
         <v>4</v>
       </c>
       <c r="N9" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="T9" s="51"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-    </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+    </row>
+    <row r="10" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B10" s="21">
         <v>6</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="D10" s="21">
         <v>180</v>
@@ -7247,32 +10359,32 @@
         <v>5</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="21">
         <v>5</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
-      <c r="P10" s="51"/>
-      <c r="T10" s="51"/>
-      <c r="U10" s="51"/>
-      <c r="V10" s="51"/>
-      <c r="W10" s="51"/>
-      <c r="X10" s="51"/>
-      <c r="Y10" s="51"/>
-    </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="P10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+    </row>
+    <row r="11" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B11" s="21">
         <v>7</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="D11" s="21">
         <v>80</v>
@@ -7285,34 +10397,34 @@
         <v>6</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="21">
         <v>6</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="L11" s="23"/>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="51"/>
-      <c r="T11" s="51"/>
-      <c r="U11" s="51"/>
-      <c r="V11" s="51"/>
-      <c r="W11" s="51"/>
-      <c r="X11" s="51"/>
-      <c r="Y11" s="51"/>
-    </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B12" s="21">
         <v>8</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="D12" s="21">
         <v>126</v>
@@ -7325,28 +10437,28 @@
         <v>7</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="I12" s="23"/>
       <c r="J12" s="21">
         <v>7</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="L12" s="23"/>
       <c r="M12" s="23"/>
       <c r="N12" s="23"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="51"/>
-    </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B13" s="21">
         <v>9</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="D13" s="21">
         <v>142</v>
@@ -7363,16 +10475,16 @@
       <c r="L13" s="23"/>
       <c r="M13" s="23"/>
       <c r="N13" s="23"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="51"/>
-    </row>
-    <row r="14" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+    </row>
+    <row r="14" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" s="21">
         <v>10</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="D14" s="21">
         <v>195</v>
@@ -7381,28 +10493,28 @@
         <v>3</v>
       </c>
       <c r="F14" s="23"/>
-      <c r="G14" s="60" t="s">
-        <v>357</v>
+      <c r="G14" s="52" t="s">
+        <v>346</v>
       </c>
       <c r="H14" s="23"/>
       <c r="I14" s="23"/>
-      <c r="J14" s="60" t="s">
-        <v>358</v>
+      <c r="J14" s="52" t="s">
+        <v>347</v>
       </c>
       <c r="K14" s="23"/>
       <c r="L14" s="23"/>
       <c r="M14" s="23"/>
       <c r="N14" s="23"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="51"/>
-    </row>
-    <row r="15" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+    </row>
+    <row r="15" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15" s="21">
         <v>11</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="D15" s="21">
         <v>180</v>
@@ -7411,33 +10523,33 @@
         <v>4</v>
       </c>
       <c r="F15" s="23"/>
-      <c r="G15" s="61" t="s">
-        <v>360</v>
-      </c>
-      <c r="H15" s="62" t="s">
-        <v>361</v>
+      <c r="G15" s="53" t="s">
+        <v>349</v>
+      </c>
+      <c r="H15" s="54" t="s">
+        <v>350</v>
       </c>
       <c r="I15" s="23"/>
-      <c r="J15" s="61" t="s">
-        <v>362</v>
-      </c>
-      <c r="K15" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="L15" s="62" t="s">
-        <v>364</v>
-      </c>
-      <c r="M15" s="62" t="s">
-        <v>365</v>
+      <c r="J15" s="53" t="s">
+        <v>351</v>
+      </c>
+      <c r="K15" s="54" t="s">
+        <v>352</v>
+      </c>
+      <c r="L15" s="54" t="s">
+        <v>353</v>
+      </c>
+      <c r="M15" s="54" t="s">
+        <v>354</v>
       </c>
       <c r="N15" s="23"/>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B16" s="21">
         <v>12</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="D16" s="21">
         <v>88</v>
@@ -7450,7 +10562,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="21">
@@ -7463,16 +10575,16 @@
         <v>0</v>
       </c>
       <c r="M16" s="21" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="N16" s="23"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B17" s="21">
         <v>13</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="D17" s="21">
         <v>200</v>
@@ -7485,7 +10597,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="I17" s="23"/>
       <c r="J17" s="21">
@@ -7498,16 +10610,16 @@
         <v>0</v>
       </c>
       <c r="M17" s="21" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="N17" s="23"/>
     </row>
-    <row r="18" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B18" s="21">
         <v>14</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="D18" s="21">
         <v>120</v>
@@ -7520,7 +10632,7 @@
         <v>3</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="I18" s="23"/>
       <c r="J18" s="21">
@@ -7533,20 +10645,20 @@
         <v>0</v>
       </c>
       <c r="M18" s="21" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="N18" s="23"/>
-      <c r="T18" s="52"/>
-      <c r="U18" s="51"/>
-      <c r="V18" s="51"/>
-      <c r="W18" s="51"/>
-    </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="T18" s="15"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+    </row>
+    <row r="19" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B19" s="21">
         <v>15</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="D19" s="21">
         <v>160</v>
@@ -7559,7 +10671,7 @@
         <v>4</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="I19" s="23"/>
       <c r="J19" s="21">
@@ -7572,22 +10684,22 @@
         <v>0</v>
       </c>
       <c r="M19" s="21" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="N19" s="23"/>
-      <c r="P19" s="54"/>
-      <c r="Q19" s="54"/>
-      <c r="T19" s="51"/>
-      <c r="U19" s="51"/>
-      <c r="V19" s="51"/>
-      <c r="W19" s="51"/>
-    </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P19" s="74"/>
+      <c r="Q19" s="74"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+    </row>
+    <row r="20" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B20" s="21">
         <v>16</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="D20" s="21">
         <v>140</v>
@@ -7609,23 +10721,23 @@
         <v>0</v>
       </c>
       <c r="M20" s="21" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="N20" s="23"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="54"/>
-      <c r="R20" s="54"/>
-      <c r="T20" s="51"/>
-      <c r="U20" s="51"/>
-      <c r="V20" s="51"/>
-      <c r="W20" s="51"/>
-    </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P20" s="4"/>
+      <c r="Q20" s="74"/>
+      <c r="R20" s="74"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+    </row>
+    <row r="21" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B21" s="21">
         <v>17</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="D21" s="21">
         <v>170</v>
@@ -7647,23 +10759,23 @@
         <v>1</v>
       </c>
       <c r="M21" s="21" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="N21" s="23"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="T21" s="51"/>
-      <c r="U21" s="51"/>
-      <c r="V21" s="51"/>
-      <c r="W21" s="51"/>
-    </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P21" s="4"/>
+      <c r="Q21" s="74"/>
+      <c r="R21" s="74"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+    </row>
+    <row r="22" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B22" s="21">
         <v>18</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="D22" s="21">
         <v>120</v>
@@ -7685,23 +10797,23 @@
         <v>1</v>
       </c>
       <c r="M22" s="21" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="N22" s="23"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="54"/>
-      <c r="R22" s="54"/>
-      <c r="T22" s="51"/>
-      <c r="U22" s="51"/>
-      <c r="V22" s="51"/>
-      <c r="W22" s="51"/>
-    </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P22" s="4"/>
+      <c r="Q22" s="74"/>
+      <c r="R22" s="74"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+    </row>
+    <row r="23" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B23" s="21">
         <v>19</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="D23" s="21">
         <v>175</v>
@@ -7723,23 +10835,23 @@
         <v>1</v>
       </c>
       <c r="M23" s="21" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="N23" s="23"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="54"/>
-      <c r="R23" s="54"/>
-      <c r="T23" s="51"/>
-      <c r="U23" s="51"/>
-      <c r="V23" s="51"/>
-      <c r="W23" s="51"/>
-    </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P23" s="4"/>
+      <c r="Q23" s="74"/>
+      <c r="R23" s="74"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+    </row>
+    <row r="24" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B24" s="21">
         <v>20</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="D24" s="21">
         <v>186</v>
@@ -7761,18 +10873,18 @@
         <v>1</v>
       </c>
       <c r="M24" s="21" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="N24" s="23"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="54"/>
-      <c r="R24" s="54"/>
-      <c r="T24" s="51"/>
-      <c r="U24" s="51"/>
-      <c r="V24" s="51"/>
-      <c r="W24" s="51"/>
-    </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P24" s="4"/>
+      <c r="Q24" s="74"/>
+      <c r="R24" s="74"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+    </row>
+    <row r="25" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
       <c r="D25" s="23"/>
@@ -7791,11 +10903,11 @@
         <v>1</v>
       </c>
       <c r="M25" s="21" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="N25" s="23"/>
     </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
@@ -7810,16 +10922,16 @@
       <c r="M26" s="23"/>
       <c r="N26" s="23"/>
     </row>
-    <row r="27" spans="2:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="60" t="s">
-        <v>389</v>
+    <row r="27" spans="2:35" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B27" s="52" t="s">
+        <v>378</v>
       </c>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
       <c r="F27" s="23"/>
       <c r="G27" s="23" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
@@ -7829,54 +10941,53 @@
       <c r="M27" s="23"/>
       <c r="N27" s="23"/>
     </row>
-    <row r="28" spans="2:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="61" t="s">
-        <v>391</v>
-      </c>
-      <c r="C28" s="62" t="s">
-        <v>392</v>
-      </c>
-      <c r="D28" s="62" t="s">
-        <v>393</v>
-      </c>
-      <c r="E28" s="62" t="s">
-        <v>394</v>
-      </c>
-      <c r="F28" s="62" t="s">
-        <v>395</v>
-      </c>
-      <c r="G28" s="62" t="s">
-        <v>396</v>
-      </c>
-      <c r="H28" s="63" t="s">
-        <v>397</v>
-      </c>
-      <c r="I28" s="63" t="s">
-        <v>398</v>
+    <row r="28" spans="2:35" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B28" s="53" t="s">
+        <v>380</v>
+      </c>
+      <c r="C28" s="54" t="s">
+        <v>381</v>
+      </c>
+      <c r="D28" s="54" t="s">
+        <v>382</v>
+      </c>
+      <c r="E28" s="54" t="s">
+        <v>383</v>
+      </c>
+      <c r="F28" s="54" t="s">
+        <v>384</v>
+      </c>
+      <c r="G28" s="54" t="s">
+        <v>385</v>
+      </c>
+      <c r="H28" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="I28" s="55" t="s">
+        <v>387</v>
       </c>
       <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
       <c r="L28" s="23"/>
       <c r="M28" s="23"/>
       <c r="N28" s="23"/>
-      <c r="T28" s="52"/>
-      <c r="U28" s="52"/>
-      <c r="X28" s="52"/>
-      <c r="Y28" s="52"/>
-      <c r="AD28" s="55"/>
-    </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="T28" s="15"/>
+      <c r="U28" s="15"/>
+      <c r="X28" s="15"/>
+      <c r="Y28" s="15"/>
+      <c r="AD28" s="47"/>
+    </row>
+    <row r="29" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B29" s="21">
         <v>1</v>
       </c>
-      <c r="C29" s="64" t="s">
-        <v>399</v>
+      <c r="C29" s="56" t="s">
+        <v>388</v>
       </c>
       <c r="D29" s="21">
         <v>20</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="F29" s="21">
         <v>258369741</v>
@@ -7891,37 +11002,36 @@
         <v>1</v>
       </c>
       <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
       <c r="L29" s="23"/>
       <c r="M29" s="23"/>
       <c r="N29" s="23"/>
-      <c r="P29" s="51"/>
-      <c r="T29" s="53"/>
-      <c r="U29" s="53"/>
-      <c r="V29" s="53"/>
-      <c r="X29" s="51"/>
-      <c r="Y29" s="51"/>
-      <c r="AA29" s="56"/>
-      <c r="AB29" s="51"/>
-      <c r="AC29" s="51"/>
-      <c r="AD29" s="56"/>
-      <c r="AF29" s="56"/>
-      <c r="AG29" s="51"/>
-      <c r="AH29" s="51"/>
-      <c r="AI29" s="56"/>
-    </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P29" s="4"/>
+      <c r="T29" s="23"/>
+      <c r="U29" s="23"/>
+      <c r="V29" s="23"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
+      <c r="AA29" s="48"/>
+      <c r="AB29" s="4"/>
+      <c r="AC29" s="4"/>
+      <c r="AD29" s="48"/>
+      <c r="AF29" s="48"/>
+      <c r="AG29" s="4"/>
+      <c r="AH29" s="4"/>
+      <c r="AI29" s="48"/>
+    </row>
+    <row r="30" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B30" s="21">
         <v>2</v>
       </c>
-      <c r="C30" s="64" t="s">
-        <v>401</v>
+      <c r="C30" s="56" t="s">
+        <v>390</v>
       </c>
       <c r="D30" s="21">
         <v>20</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="F30" s="21">
         <v>258369741</v>
@@ -7936,38 +11046,37 @@
         <v>2</v>
       </c>
       <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
       <c r="L30" s="23"/>
       <c r="M30" s="23"/>
       <c r="N30" s="23"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
-      <c r="T30" s="53"/>
-      <c r="U30" s="53"/>
-      <c r="V30" s="53"/>
-      <c r="X30" s="51"/>
-      <c r="Y30" s="51"/>
-      <c r="AA30" s="56"/>
-      <c r="AB30" s="57"/>
-      <c r="AC30" s="51"/>
-      <c r="AD30" s="56"/>
-      <c r="AF30" s="56"/>
-      <c r="AG30" s="57"/>
-      <c r="AH30" s="51"/>
-      <c r="AI30" s="56"/>
-    </row>
-    <row r="31" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="T30" s="23"/>
+      <c r="U30" s="23"/>
+      <c r="V30" s="23"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="AA30" s="48"/>
+      <c r="AB30" s="49"/>
+      <c r="AC30" s="4"/>
+      <c r="AD30" s="48"/>
+      <c r="AF30" s="48"/>
+      <c r="AG30" s="49"/>
+      <c r="AH30" s="4"/>
+      <c r="AI30" s="48"/>
+    </row>
+    <row r="31" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B31" s="21">
         <v>3</v>
       </c>
-      <c r="C31" s="64" t="s">
-        <v>403</v>
+      <c r="C31" s="56" t="s">
+        <v>392</v>
       </c>
       <c r="D31" s="21">
         <v>20</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="F31" s="21">
         <v>258369741</v>
@@ -7982,38 +11091,37 @@
         <v>3</v>
       </c>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
       <c r="L31" s="23"/>
       <c r="M31" s="23"/>
       <c r="N31" s="23"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="51"/>
-      <c r="T31" s="53"/>
-      <c r="U31" s="53"/>
-      <c r="V31" s="53"/>
-      <c r="X31" s="51"/>
-      <c r="Y31" s="51"/>
-      <c r="AA31" s="56"/>
-      <c r="AB31" s="57"/>
-      <c r="AC31" s="51"/>
-      <c r="AD31" s="56"/>
-      <c r="AF31" s="56"/>
-      <c r="AG31" s="57"/>
-      <c r="AH31" s="51"/>
-      <c r="AI31" s="56"/>
-    </row>
-    <row r="32" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4"/>
+      <c r="AA31" s="48"/>
+      <c r="AB31" s="49"/>
+      <c r="AC31" s="4"/>
+      <c r="AD31" s="48"/>
+      <c r="AF31" s="48"/>
+      <c r="AG31" s="49"/>
+      <c r="AH31" s="4"/>
+      <c r="AI31" s="48"/>
+    </row>
+    <row r="32" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B32" s="21">
         <v>4</v>
       </c>
-      <c r="C32" s="64" t="s">
-        <v>405</v>
+      <c r="C32" s="56" t="s">
+        <v>394</v>
       </c>
       <c r="D32" s="21">
         <v>30</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="F32" s="21">
         <v>258369741</v>
@@ -8028,38 +11136,37 @@
         <v>4</v>
       </c>
       <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
       <c r="L32" s="23"/>
       <c r="M32" s="23"/>
       <c r="N32" s="23"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="51"/>
-      <c r="T32" s="53"/>
-      <c r="U32" s="53"/>
-      <c r="V32" s="53"/>
-      <c r="X32" s="51"/>
-      <c r="Y32" s="51"/>
-      <c r="AA32" s="56"/>
-      <c r="AB32" s="57"/>
-      <c r="AC32" s="51"/>
-      <c r="AD32" s="56"/>
-      <c r="AF32" s="56"/>
-      <c r="AG32" s="57"/>
-      <c r="AH32" s="51"/>
-      <c r="AI32" s="56"/>
-    </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P32" s="4"/>
+      <c r="Q32" s="4"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="23"/>
+      <c r="V32" s="23"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+      <c r="AA32" s="48"/>
+      <c r="AB32" s="49"/>
+      <c r="AC32" s="4"/>
+      <c r="AD32" s="48"/>
+      <c r="AF32" s="48"/>
+      <c r="AG32" s="49"/>
+      <c r="AH32" s="4"/>
+      <c r="AI32" s="48"/>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B33" s="21">
         <v>5</v>
       </c>
-      <c r="C33" s="64" t="s">
-        <v>407</v>
+      <c r="C33" s="56" t="s">
+        <v>396</v>
       </c>
       <c r="D33" s="21">
         <v>30</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="F33" s="21">
         <v>258369741</v>
@@ -8074,36 +11181,35 @@
         <v>5</v>
       </c>
       <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
       <c r="L33" s="23"/>
       <c r="M33" s="23"/>
       <c r="N33" s="23"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="51"/>
-      <c r="T33" s="53"/>
-      <c r="U33" s="53"/>
-      <c r="V33" s="53"/>
-      <c r="AA33" s="56"/>
-      <c r="AB33" s="57"/>
-      <c r="AC33" s="51"/>
-      <c r="AD33" s="56"/>
-      <c r="AF33" s="56"/>
-      <c r="AG33" s="57"/>
-      <c r="AH33" s="51"/>
-      <c r="AI33" s="56"/>
-    </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="T33" s="23"/>
+      <c r="U33" s="23"/>
+      <c r="V33" s="23"/>
+      <c r="AA33" s="48"/>
+      <c r="AB33" s="49"/>
+      <c r="AC33" s="4"/>
+      <c r="AD33" s="48"/>
+      <c r="AF33" s="48"/>
+      <c r="AG33" s="49"/>
+      <c r="AH33" s="4"/>
+      <c r="AI33" s="48"/>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B34" s="21">
         <v>6</v>
       </c>
-      <c r="C34" s="64" t="s">
-        <v>401</v>
+      <c r="C34" s="56" t="s">
+        <v>390</v>
       </c>
       <c r="D34" s="21">
         <v>40</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="F34" s="21">
         <v>258369741</v>
@@ -8118,28 +11224,27 @@
         <v>6</v>
       </c>
       <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
       <c r="L34" s="23"/>
       <c r="M34" s="23"/>
       <c r="N34" s="23"/>
-      <c r="P34" s="51"/>
-      <c r="Q34" s="51"/>
-      <c r="T34" s="58"/>
-      <c r="U34" s="58"/>
-      <c r="V34" s="53"/>
-    </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="T34" s="50"/>
+      <c r="U34" s="50"/>
+      <c r="V34" s="23"/>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B35" s="21">
         <v>7</v>
       </c>
-      <c r="C35" s="64" t="s">
-        <v>403</v>
+      <c r="C35" s="56" t="s">
+        <v>392</v>
       </c>
       <c r="D35" s="21">
         <v>40</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="F35" s="21">
         <v>258369741</v>
@@ -8154,25 +11259,24 @@
         <v>7</v>
       </c>
       <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
       <c r="L35" s="23"/>
       <c r="M35" s="23"/>
       <c r="N35" s="23"/>
-      <c r="P35" s="51"/>
-      <c r="Q35" s="51"/>
-    </row>
-    <row r="36" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+    </row>
+    <row r="36" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B36" s="21">
         <v>8</v>
       </c>
-      <c r="C36" s="64" t="s">
-        <v>407</v>
+      <c r="C36" s="56" t="s">
+        <v>396</v>
       </c>
       <c r="D36" s="21">
         <v>50</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="F36" s="21">
         <v>258369741</v>
@@ -8187,23 +11291,22 @@
         <v>8</v>
       </c>
       <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
       <c r="L36" s="23"/>
       <c r="M36" s="23"/>
       <c r="N36" s="23"/>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B37" s="21">
         <v>9</v>
       </c>
-      <c r="C37" s="64" t="s">
-        <v>407</v>
+      <c r="C37" s="56" t="s">
+        <v>396</v>
       </c>
       <c r="D37" s="21">
         <v>50</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="F37" s="21">
         <v>258369741</v>
@@ -8222,20 +11325,20 @@
       <c r="L37" s="23"/>
       <c r="M37" s="23"/>
       <c r="N37" s="23"/>
-      <c r="P37" s="52"/>
-    </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="P37" s="15"/>
+    </row>
+    <row r="38" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B38" s="21">
         <v>10</v>
       </c>
-      <c r="C38" s="64" t="s">
-        <v>407</v>
+      <c r="C38" s="56" t="s">
+        <v>396</v>
       </c>
       <c r="D38" s="21">
         <v>20</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="F38" s="21">
         <v>258369741</v>
@@ -8255,18 +11358,18 @@
       <c r="M38" s="23"/>
       <c r="N38" s="23"/>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B39" s="21">
         <v>11</v>
       </c>
-      <c r="C39" s="64" t="s">
-        <v>414</v>
+      <c r="C39" s="56" t="s">
+        <v>403</v>
       </c>
       <c r="D39" s="21">
         <v>30</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="F39" s="21">
         <v>258369741</v>
@@ -8286,18 +11389,18 @@
       <c r="M39" s="23"/>
       <c r="N39" s="23"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B40" s="21">
         <v>12</v>
       </c>
-      <c r="C40" s="64" t="s">
-        <v>416</v>
+      <c r="C40" s="56" t="s">
+        <v>405</v>
       </c>
       <c r="D40" s="21">
         <v>20</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="F40" s="21">
         <v>258369741</v>
@@ -8317,18 +11420,18 @@
       <c r="M40" s="23"/>
       <c r="N40" s="23"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B41" s="21">
         <v>13</v>
       </c>
-      <c r="C41" s="64" t="s">
-        <v>418</v>
+      <c r="C41" s="56" t="s">
+        <v>407</v>
       </c>
       <c r="D41" s="21">
         <v>40</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="F41" s="21">
         <v>258369741</v>
@@ -8347,9 +11450,9 @@
       <c r="L41" s="23"/>
       <c r="M41" s="23"/>
       <c r="N41" s="23"/>
-      <c r="AA41" s="72"/>
-    </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="AA41" s="61"/>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B42" s="23"/>
       <c r="C42" s="23"/>
       <c r="D42" s="23"/>
@@ -8363,18 +11466,18 @@
       <c r="L42" s="23"/>
       <c r="M42" s="23"/>
       <c r="N42" s="23"/>
-      <c r="AA42" s="73"/>
-      <c r="AB42" s="73"/>
-      <c r="AC42" s="73"/>
-      <c r="AD42" s="73"/>
-      <c r="AE42" s="73"/>
-      <c r="AF42" s="73"/>
-      <c r="AG42" s="73"/>
-      <c r="AH42" s="73"/>
-    </row>
-    <row r="43" spans="2:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="60" t="s">
-        <v>420</v>
+      <c r="AA42" s="62"/>
+      <c r="AB42" s="62"/>
+      <c r="AC42" s="62"/>
+      <c r="AD42" s="62"/>
+      <c r="AE42" s="62"/>
+      <c r="AF42" s="62"/>
+      <c r="AG42" s="62"/>
+      <c r="AH42" s="62"/>
+    </row>
+    <row r="43" spans="2:35" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B43" s="52" t="s">
+        <v>409</v>
       </c>
       <c r="C43" s="23"/>
       <c r="D43" s="23"/>
@@ -8389,57 +11492,57 @@
       <c r="M43" s="23"/>
       <c r="N43" s="23"/>
     </row>
-    <row r="44" spans="2:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="61" t="s">
-        <v>421</v>
-      </c>
-      <c r="C44" s="62" t="s">
-        <v>422</v>
-      </c>
-      <c r="D44" s="62" t="s">
-        <v>423</v>
-      </c>
-      <c r="E44" s="62" t="s">
-        <v>424</v>
-      </c>
-      <c r="F44" s="62" t="s">
-        <v>425</v>
-      </c>
-      <c r="G44" s="65" t="s">
-        <v>426</v>
-      </c>
-      <c r="H44" s="75" t="s">
-        <v>427</v>
-      </c>
-      <c r="I44" s="74"/>
-      <c r="J44" s="74"/>
+    <row r="44" spans="2:35" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B44" s="53" t="s">
+        <v>410</v>
+      </c>
+      <c r="C44" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="D44" s="54" t="s">
+        <v>412</v>
+      </c>
+      <c r="E44" s="54" t="s">
+        <v>413</v>
+      </c>
+      <c r="F44" s="54" t="s">
+        <v>414</v>
+      </c>
+      <c r="G44" s="57" t="s">
+        <v>415</v>
+      </c>
+      <c r="H44" s="64" t="s">
+        <v>416</v>
+      </c>
+      <c r="I44" s="63"/>
+      <c r="J44" s="63"/>
       <c r="K44" s="23"/>
       <c r="L44" s="23"/>
       <c r="M44" s="23"/>
       <c r="N44" s="23"/>
-      <c r="O44" s="51"/>
-    </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="O44" s="4"/>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B45" s="21">
         <v>1</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>428</v>
-      </c>
-      <c r="D45" s="64" t="s">
-        <v>429</v>
+        <v>417</v>
+      </c>
+      <c r="D45" s="56" t="s">
+        <v>418</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="F45" s="21">
         <v>123456789</v>
       </c>
       <c r="G45" s="21" t="s">
-        <v>430</v>
-      </c>
-      <c r="H45" s="70" t="s">
-        <v>431</v>
+        <v>419</v>
+      </c>
+      <c r="H45" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I45" s="23"/>
       <c r="J45" s="23"/>
@@ -8447,32 +11550,32 @@
       <c r="L45" s="23"/>
       <c r="M45" s="23"/>
       <c r="N45" s="23"/>
-      <c r="O45" s="53"/>
-      <c r="P45" s="53"/>
-      <c r="Q45" s="53"/>
-      <c r="R45" s="53"/>
-    </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="O45" s="23"/>
+      <c r="P45" s="23"/>
+      <c r="Q45" s="23"/>
+      <c r="R45" s="23"/>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B46" s="21">
         <v>2</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="F46" s="21">
         <v>123456789</v>
       </c>
       <c r="G46" s="21" t="s">
-        <v>434</v>
-      </c>
-      <c r="H46" s="70" t="s">
-        <v>431</v>
+        <v>423</v>
+      </c>
+      <c r="H46" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I46" s="23"/>
       <c r="J46" s="23"/>
@@ -8480,35 +11583,35 @@
       <c r="L46" s="23"/>
       <c r="M46" s="23"/>
       <c r="N46" s="23"/>
-      <c r="O46" s="53"/>
-      <c r="P46" s="53"/>
-      <c r="Q46" s="59"/>
-      <c r="R46" s="59"/>
-      <c r="T46" s="53"/>
-      <c r="U46" s="53"/>
-      <c r="V46" s="53"/>
-    </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="O46" s="23"/>
+      <c r="P46" s="23"/>
+      <c r="Q46" s="51"/>
+      <c r="R46" s="51"/>
+      <c r="T46" s="23"/>
+      <c r="U46" s="23"/>
+      <c r="V46" s="23"/>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B47" s="21">
         <v>3</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="F47" s="21">
         <v>123456789</v>
       </c>
       <c r="G47" s="21" t="s">
-        <v>437</v>
-      </c>
-      <c r="H47" s="70" t="s">
-        <v>431</v>
+        <v>426</v>
+      </c>
+      <c r="H47" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I47" s="23"/>
       <c r="J47" s="23"/>
@@ -8516,35 +11619,35 @@
       <c r="L47" s="23"/>
       <c r="M47" s="23"/>
       <c r="N47" s="23"/>
-      <c r="O47" s="53"/>
-      <c r="P47" s="53"/>
-      <c r="Q47" s="59"/>
-      <c r="R47" s="59"/>
-      <c r="T47" s="53"/>
-      <c r="U47" s="53"/>
-      <c r="V47" s="53"/>
-    </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="O47" s="23"/>
+      <c r="P47" s="23"/>
+      <c r="Q47" s="51"/>
+      <c r="R47" s="51"/>
+      <c r="T47" s="23"/>
+      <c r="U47" s="23"/>
+      <c r="V47" s="23"/>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B48" s="21">
         <v>4</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="F48" s="21">
         <v>123456789</v>
       </c>
       <c r="G48" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="H48" s="70" t="s">
-        <v>431</v>
+        <v>429</v>
+      </c>
+      <c r="H48" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I48" s="23"/>
       <c r="J48" s="23"/>
@@ -8552,37 +11655,37 @@
       <c r="L48" s="23"/>
       <c r="M48" s="23"/>
       <c r="N48" s="23"/>
-      <c r="O48" s="53"/>
-      <c r="P48" s="53"/>
-      <c r="Q48" s="59"/>
-      <c r="R48" s="59"/>
-      <c r="T48" s="53"/>
-      <c r="U48" s="53"/>
-      <c r="V48" s="53"/>
-      <c r="AE48" s="56"/>
-      <c r="AF48" s="56"/>
-    </row>
-    <row r="49" spans="2:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O48" s="23"/>
+      <c r="P48" s="23"/>
+      <c r="Q48" s="51"/>
+      <c r="R48" s="51"/>
+      <c r="T48" s="23"/>
+      <c r="U48" s="23"/>
+      <c r="V48" s="23"/>
+      <c r="AE48" s="48"/>
+      <c r="AF48" s="48"/>
+    </row>
+    <row r="49" spans="2:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="21">
         <v>5</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="F49" s="21">
         <v>123456789</v>
       </c>
       <c r="G49" s="21" t="s">
-        <v>443</v>
-      </c>
-      <c r="H49" s="70" t="s">
-        <v>431</v>
+        <v>432</v>
+      </c>
+      <c r="H49" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I49" s="23"/>
       <c r="J49" s="23"/>
@@ -8590,37 +11693,37 @@
       <c r="L49" s="23"/>
       <c r="M49" s="23"/>
       <c r="N49" s="23"/>
-      <c r="O49" s="53"/>
-      <c r="P49" s="53"/>
-      <c r="Q49" s="59"/>
-      <c r="R49" s="59"/>
-      <c r="T49" s="53"/>
-      <c r="U49" s="53"/>
-      <c r="V49" s="53"/>
-      <c r="AE49" s="56"/>
-      <c r="AF49" s="56"/>
-    </row>
-    <row r="50" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="O49" s="23"/>
+      <c r="P49" s="23"/>
+      <c r="Q49" s="51"/>
+      <c r="R49" s="51"/>
+      <c r="T49" s="23"/>
+      <c r="U49" s="23"/>
+      <c r="V49" s="23"/>
+      <c r="AE49" s="48"/>
+      <c r="AF49" s="48"/>
+    </row>
+    <row r="50" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B50" s="21">
         <v>6</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="F50" s="21">
         <v>123456789</v>
       </c>
       <c r="G50" s="21" t="s">
-        <v>446</v>
-      </c>
-      <c r="H50" s="70" t="s">
-        <v>431</v>
+        <v>435</v>
+      </c>
+      <c r="H50" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I50" s="23"/>
       <c r="J50" s="23"/>
@@ -8628,34 +11731,34 @@
       <c r="L50" s="23"/>
       <c r="M50" s="23"/>
       <c r="N50" s="23"/>
-      <c r="O50" s="53"/>
-      <c r="P50" s="53"/>
-      <c r="Q50" s="59"/>
-      <c r="R50" s="59"/>
-      <c r="AE50" s="56"/>
-      <c r="AF50" s="56"/>
-    </row>
-    <row r="51" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="O50" s="23"/>
+      <c r="P50" s="23"/>
+      <c r="Q50" s="51"/>
+      <c r="R50" s="51"/>
+      <c r="AE50" s="48"/>
+      <c r="AF50" s="48"/>
+    </row>
+    <row r="51" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B51" s="21">
         <v>7</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="F51" s="21">
         <v>123456789</v>
       </c>
       <c r="G51" s="21" t="s">
-        <v>449</v>
-      </c>
-      <c r="H51" s="70" t="s">
-        <v>431</v>
+        <v>438</v>
+      </c>
+      <c r="H51" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I51" s="23"/>
       <c r="J51" s="23"/>
@@ -8663,34 +11766,34 @@
       <c r="L51" s="23"/>
       <c r="M51" s="23"/>
       <c r="N51" s="23"/>
-      <c r="O51" s="53"/>
-      <c r="P51" s="53"/>
-      <c r="Q51" s="59"/>
-      <c r="R51" s="59"/>
-      <c r="AE51" s="56"/>
-      <c r="AF51" s="56"/>
-    </row>
-    <row r="52" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="O51" s="23"/>
+      <c r="P51" s="23"/>
+      <c r="Q51" s="51"/>
+      <c r="R51" s="51"/>
+      <c r="AE51" s="48"/>
+      <c r="AF51" s="48"/>
+    </row>
+    <row r="52" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B52" s="21">
         <v>8</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="F52" s="21">
         <v>123456789</v>
       </c>
       <c r="G52" s="21" t="s">
-        <v>452</v>
-      </c>
-      <c r="H52" s="70" t="s">
-        <v>431</v>
+        <v>441</v>
+      </c>
+      <c r="H52" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I52" s="23"/>
       <c r="J52" s="23"/>
@@ -8698,34 +11801,34 @@
       <c r="L52" s="23"/>
       <c r="M52" s="23"/>
       <c r="N52" s="23"/>
-      <c r="O52" s="53"/>
-      <c r="P52" s="53"/>
-      <c r="Q52" s="59"/>
-      <c r="R52" s="59"/>
-      <c r="AE52" s="56"/>
-      <c r="AF52" s="56"/>
-    </row>
-    <row r="53" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="O52" s="23"/>
+      <c r="P52" s="23"/>
+      <c r="Q52" s="51"/>
+      <c r="R52" s="51"/>
+      <c r="AE52" s="48"/>
+      <c r="AF52" s="48"/>
+    </row>
+    <row r="53" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B53" s="21">
         <v>9</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="F53" s="21">
         <v>123456789</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>455</v>
-      </c>
-      <c r="H53" s="70" t="s">
-        <v>431</v>
+        <v>444</v>
+      </c>
+      <c r="H53" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I53" s="23"/>
       <c r="J53" s="23"/>
@@ -8733,32 +11836,32 @@
       <c r="L53" s="23"/>
       <c r="M53" s="23"/>
       <c r="N53" s="23"/>
-      <c r="O53" s="53"/>
-      <c r="P53" s="53"/>
-      <c r="Q53" s="59"/>
-      <c r="R53" s="59"/>
-    </row>
-    <row r="54" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="O53" s="23"/>
+      <c r="P53" s="23"/>
+      <c r="Q53" s="51"/>
+      <c r="R53" s="51"/>
+    </row>
+    <row r="54" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B54" s="21">
         <v>10</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="F54" s="21">
         <v>123456789</v>
       </c>
       <c r="G54" s="21" t="s">
-        <v>458</v>
-      </c>
-      <c r="H54" s="70" t="s">
-        <v>431</v>
+        <v>447</v>
+      </c>
+      <c r="H54" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I54" s="23"/>
       <c r="J54" s="23"/>
@@ -8766,12 +11869,12 @@
       <c r="L54" s="23"/>
       <c r="M54" s="23"/>
       <c r="N54" s="23"/>
-      <c r="O54" s="53"/>
-      <c r="P54" s="53"/>
-      <c r="Q54" s="59"/>
-      <c r="R54" s="59"/>
-    </row>
-    <row r="55" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="O54" s="23"/>
+      <c r="P54" s="23"/>
+      <c r="Q54" s="51"/>
+      <c r="R54" s="51"/>
+    </row>
+    <row r="55" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
       <c r="D55" s="23"/>
@@ -8785,14 +11888,14 @@
       <c r="L55" s="23"/>
       <c r="M55" s="23"/>
       <c r="N55" s="23"/>
-      <c r="O55" s="53"/>
-      <c r="P55" s="53"/>
-      <c r="Q55" s="59"/>
-      <c r="R55" s="59"/>
-    </row>
-    <row r="56" spans="2:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B56" s="60" t="s">
-        <v>459</v>
+      <c r="O55" s="23"/>
+      <c r="P55" s="23"/>
+      <c r="Q55" s="51"/>
+      <c r="R55" s="51"/>
+    </row>
+    <row r="56" spans="2:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B56" s="52" t="s">
+        <v>448</v>
       </c>
       <c r="C56" s="23"/>
       <c r="D56" s="23"/>
@@ -8806,67 +11909,67 @@
       <c r="L56" s="23"/>
       <c r="M56" s="23"/>
       <c r="N56" s="23"/>
-      <c r="O56" s="53"/>
-      <c r="P56" s="53"/>
-      <c r="Q56" s="59"/>
-      <c r="R56" s="59"/>
-    </row>
-    <row r="57" spans="2:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="61" t="s">
-        <v>460</v>
-      </c>
-      <c r="C57" s="62" t="s">
-        <v>461</v>
-      </c>
-      <c r="D57" s="62" t="s">
-        <v>462</v>
-      </c>
-      <c r="E57" s="62" t="s">
-        <v>463</v>
-      </c>
-      <c r="F57" s="62" t="s">
-        <v>464</v>
-      </c>
-      <c r="G57" s="62" t="s">
-        <v>465</v>
-      </c>
-      <c r="H57" s="62" t="s">
-        <v>466</v>
-      </c>
-      <c r="I57" s="63" t="s">
-        <v>467</v>
+      <c r="O56" s="23"/>
+      <c r="P56" s="23"/>
+      <c r="Q56" s="51"/>
+      <c r="R56" s="51"/>
+    </row>
+    <row r="57" spans="2:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B57" s="53" t="s">
+        <v>449</v>
+      </c>
+      <c r="C57" s="54" t="s">
+        <v>450</v>
+      </c>
+      <c r="D57" s="54" t="s">
+        <v>451</v>
+      </c>
+      <c r="E57" s="54" t="s">
+        <v>452</v>
+      </c>
+      <c r="F57" s="54" t="s">
+        <v>453</v>
+      </c>
+      <c r="G57" s="54" t="s">
+        <v>454</v>
+      </c>
+      <c r="H57" s="54" t="s">
+        <v>455</v>
+      </c>
+      <c r="I57" s="55" t="s">
+        <v>456</v>
       </c>
       <c r="J57" s="23"/>
       <c r="K57" s="23"/>
       <c r="L57" s="23"/>
       <c r="M57" s="23"/>
       <c r="N57" s="23"/>
-      <c r="O57" s="53"/>
-      <c r="P57" s="53"/>
-      <c r="Q57" s="59"/>
-      <c r="R57" s="59"/>
-    </row>
-    <row r="58" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="O57" s="23"/>
+      <c r="P57" s="23"/>
+      <c r="Q57" s="51"/>
+      <c r="R57" s="51"/>
+    </row>
+    <row r="58" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B58" s="21">
         <v>1</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>468</v>
-      </c>
-      <c r="D58" s="64" t="s">
-        <v>469</v>
+        <v>457</v>
+      </c>
+      <c r="D58" s="56" t="s">
+        <v>458</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="F58" s="21">
         <v>123456789</v>
       </c>
       <c r="G58" s="21" t="s">
-        <v>470</v>
-      </c>
-      <c r="H58" s="70" t="s">
-        <v>431</v>
+        <v>459</v>
+      </c>
+      <c r="H58" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I58" s="21">
         <v>1</v>
@@ -8876,32 +11979,32 @@
       <c r="L58" s="23"/>
       <c r="M58" s="23"/>
       <c r="N58" s="23"/>
-      <c r="O58" s="53"/>
-      <c r="P58" s="53"/>
-      <c r="Q58" s="59"/>
-      <c r="R58" s="59"/>
-    </row>
-    <row r="59" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="O58" s="23"/>
+      <c r="P58" s="23"/>
+      <c r="Q58" s="51"/>
+      <c r="R58" s="51"/>
+    </row>
+    <row r="59" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B59" s="21">
         <v>2</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="F59" s="21">
         <v>123456789</v>
       </c>
       <c r="G59" s="21" t="s">
-        <v>473</v>
-      </c>
-      <c r="H59" s="70" t="s">
-        <v>431</v>
+        <v>462</v>
+      </c>
+      <c r="H59" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I59" s="21">
         <v>1</v>
@@ -8911,32 +12014,32 @@
       <c r="L59" s="23"/>
       <c r="M59" s="23"/>
       <c r="N59" s="23"/>
-      <c r="O59" s="53"/>
-      <c r="P59" s="53"/>
-      <c r="Q59" s="59"/>
-      <c r="R59" s="59"/>
-    </row>
-    <row r="60" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="O59" s="23"/>
+      <c r="P59" s="23"/>
+      <c r="Q59" s="51"/>
+      <c r="R59" s="51"/>
+    </row>
+    <row r="60" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B60" s="21">
         <v>3</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>474</v>
-      </c>
-      <c r="D60" s="64" t="s">
-        <v>475</v>
+        <v>463</v>
+      </c>
+      <c r="D60" s="56" t="s">
+        <v>464</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="F60" s="21">
         <v>123456789</v>
       </c>
       <c r="G60" s="21" t="s">
-        <v>476</v>
-      </c>
-      <c r="H60" s="70" t="s">
-        <v>431</v>
+        <v>465</v>
+      </c>
+      <c r="H60" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I60" s="21">
         <v>2</v>
@@ -8946,32 +12049,32 @@
       <c r="L60" s="23"/>
       <c r="M60" s="23"/>
       <c r="N60" s="23"/>
-      <c r="O60" s="53"/>
-      <c r="P60" s="53"/>
-      <c r="Q60" s="59"/>
-      <c r="R60" s="59"/>
-    </row>
-    <row r="61" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="O60" s="23"/>
+      <c r="P60" s="23"/>
+      <c r="Q60" s="51"/>
+      <c r="R60" s="51"/>
+    </row>
+    <row r="61" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B61" s="21">
         <v>4</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="F61" s="21">
         <v>123456789</v>
       </c>
       <c r="G61" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="H61" s="70" t="s">
-        <v>431</v>
+        <v>468</v>
+      </c>
+      <c r="H61" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I61" s="21">
         <v>1</v>
@@ -8981,32 +12084,32 @@
       <c r="L61" s="23"/>
       <c r="M61" s="23"/>
       <c r="N61" s="23"/>
-      <c r="O61" s="53"/>
-      <c r="P61" s="53"/>
-      <c r="Q61" s="59"/>
-      <c r="R61" s="59"/>
-    </row>
-    <row r="62" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="O61" s="23"/>
+      <c r="P61" s="23"/>
+      <c r="Q61" s="51"/>
+      <c r="R61" s="51"/>
+    </row>
+    <row r="62" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B62" s="21">
         <v>5</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>480</v>
-      </c>
-      <c r="D62" s="64" t="s">
-        <v>481</v>
+        <v>469</v>
+      </c>
+      <c r="D62" s="56" t="s">
+        <v>470</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="F62" s="21">
         <v>123456789</v>
       </c>
       <c r="G62" s="21" t="s">
-        <v>482</v>
-      </c>
-      <c r="H62" s="70" t="s">
-        <v>431</v>
+        <v>471</v>
+      </c>
+      <c r="H62" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I62" s="21">
         <v>1</v>
@@ -9017,27 +12120,27 @@
       <c r="M62" s="23"/>
       <c r="N62" s="23"/>
     </row>
-    <row r="63" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B63" s="21">
         <v>6</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="E63" s="21" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="F63" s="21">
         <v>123456789</v>
       </c>
       <c r="G63" s="21" t="s">
-        <v>485</v>
-      </c>
-      <c r="H63" s="70" t="s">
-        <v>431</v>
+        <v>474</v>
+      </c>
+      <c r="H63" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I63" s="21">
         <v>1</v>
@@ -9048,27 +12151,27 @@
       <c r="M63" s="23"/>
       <c r="N63" s="23"/>
     </row>
-    <row r="64" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B64" s="21">
         <v>7</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>486</v>
-      </c>
-      <c r="D64" s="64" t="s">
-        <v>487</v>
+        <v>475</v>
+      </c>
+      <c r="D64" s="56" t="s">
+        <v>476</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="F64" s="21">
         <v>123456789</v>
       </c>
       <c r="G64" s="21" t="s">
-        <v>488</v>
-      </c>
-      <c r="H64" s="70" t="s">
-        <v>431</v>
+        <v>477</v>
+      </c>
+      <c r="H64" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I64" s="21">
         <v>2</v>
@@ -9079,27 +12182,27 @@
       <c r="M64" s="23"/>
       <c r="N64" s="23"/>
     </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B65" s="21">
         <v>8</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="E65" s="21" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="F65" s="21">
         <v>123456789</v>
       </c>
       <c r="G65" s="21" t="s">
-        <v>491</v>
-      </c>
-      <c r="H65" s="70" t="s">
-        <v>431</v>
+        <v>480</v>
+      </c>
+      <c r="H65" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I65" s="21">
         <v>3</v>
@@ -9110,27 +12213,27 @@
       <c r="M65" s="23"/>
       <c r="N65" s="23"/>
     </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B66" s="21">
         <v>9</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>492</v>
-      </c>
-      <c r="D66" s="64" t="s">
-        <v>493</v>
+        <v>481</v>
+      </c>
+      <c r="D66" s="56" t="s">
+        <v>482</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="F66" s="21">
         <v>123456789</v>
       </c>
       <c r="G66" s="21" t="s">
-        <v>494</v>
-      </c>
-      <c r="H66" s="70" t="s">
-        <v>431</v>
+        <v>483</v>
+      </c>
+      <c r="H66" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I66" s="21">
         <v>1</v>
@@ -9141,27 +12244,27 @@
       <c r="M66" s="23"/>
       <c r="N66" s="23"/>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B67" s="21">
         <v>10</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="E67" s="21" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="F67" s="21">
         <v>123456789</v>
       </c>
       <c r="G67" s="21" t="s">
-        <v>497</v>
-      </c>
-      <c r="H67" s="70" t="s">
-        <v>431</v>
+        <v>486</v>
+      </c>
+      <c r="H67" s="60" t="s">
+        <v>420</v>
       </c>
       <c r="I67" s="21">
         <v>4</v>
@@ -9172,7 +12275,7 @@
       <c r="M67" s="23"/>
       <c r="N67" s="23"/>
     </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B68" s="23"/>
       <c r="C68" s="23"/>
       <c r="D68" s="23"/>
@@ -9187,7 +12290,7 @@
       <c r="M68" s="23"/>
       <c r="N68" s="23"/>
     </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B69" s="23"/>
       <c r="C69" s="23"/>
       <c r="D69" s="23"/>
@@ -9202,9 +12305,9 @@
       <c r="M69" s="23"/>
       <c r="N69" s="23"/>
     </row>
-    <row r="70" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="66" t="s">
-        <v>498</v>
+    <row r="70" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B70" s="58" t="s">
+        <v>487</v>
       </c>
       <c r="C70" s="23"/>
       <c r="D70" s="23"/>
@@ -9219,21 +12322,21 @@
       <c r="M70" s="23"/>
       <c r="N70" s="23"/>
     </row>
-    <row r="71" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B71" s="61" t="s">
-        <v>499</v>
-      </c>
-      <c r="C71" s="67" t="s">
-        <v>500</v>
-      </c>
-      <c r="D71" s="67" t="s">
-        <v>501</v>
-      </c>
-      <c r="E71" s="62" t="s">
-        <v>502</v>
-      </c>
-      <c r="F71" s="62" t="s">
-        <v>503</v>
+    <row r="71" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B71" s="53" t="s">
+        <v>488</v>
+      </c>
+      <c r="C71" s="59" t="s">
+        <v>489</v>
+      </c>
+      <c r="D71" s="59" t="s">
+        <v>490</v>
+      </c>
+      <c r="E71" s="54" t="s">
+        <v>491</v>
+      </c>
+      <c r="F71" s="54" t="s">
+        <v>492</v>
       </c>
       <c r="G71" s="23"/>
       <c r="H71" s="23"/>
@@ -9243,11 +12346,11 @@
       <c r="L71" s="23"/>
       <c r="M71" s="23"/>
       <c r="N71" s="23"/>
-      <c r="Q71" s="51"/>
-      <c r="W71" s="52"/>
-      <c r="X71" s="52"/>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="Q71" s="4"/>
+      <c r="W71" s="15"/>
+      <c r="X71" s="15"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B72" s="23"/>
       <c r="C72" s="23"/>
       <c r="D72" s="23"/>
@@ -9261,18 +12364,18 @@
       <c r="L72" s="23"/>
       <c r="M72" s="23"/>
       <c r="N72" s="23"/>
-      <c r="Q72" s="51"/>
-      <c r="R72" s="51"/>
-      <c r="W72" s="51"/>
-      <c r="X72" s="51"/>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B73" s="23"/>
-      <c r="C73" s="49" t="s">
-        <v>504</v>
-      </c>
-      <c r="D73" s="49"/>
-      <c r="E73" s="49"/>
+      <c r="C73" s="75" t="s">
+        <v>493</v>
+      </c>
+      <c r="D73" s="75"/>
+      <c r="E73" s="75"/>
       <c r="F73" s="23"/>
       <c r="G73" s="23"/>
       <c r="H73" s="23"/>
@@ -9282,16 +12385,16 @@
       <c r="L73" s="23"/>
       <c r="M73" s="23"/>
       <c r="N73" s="23"/>
-      <c r="Q73" s="51"/>
-      <c r="R73" s="51"/>
-      <c r="W73" s="51"/>
-      <c r="X73" s="51"/>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="Q73" s="4"/>
+      <c r="R73" s="4"/>
+      <c r="W73" s="4"/>
+      <c r="X73" s="4"/>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B74" s="23"/>
-      <c r="C74" s="49"/>
-      <c r="D74" s="49"/>
-      <c r="E74" s="49"/>
+      <c r="C74" s="75"/>
+      <c r="D74" s="75"/>
+      <c r="E74" s="75"/>
       <c r="F74" s="23"/>
       <c r="G74" s="23"/>
       <c r="H74" s="23"/>
@@ -9301,12 +12404,12 @@
       <c r="L74" s="23"/>
       <c r="M74" s="23"/>
       <c r="N74" s="23"/>
-      <c r="Q74" s="51"/>
-      <c r="R74" s="51"/>
-      <c r="W74" s="51"/>
-      <c r="X74" s="51"/>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="Q74" s="4"/>
+      <c r="R74" s="4"/>
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B75" s="23"/>
       <c r="C75" s="23"/>
       <c r="D75" s="23"/>
@@ -9320,14 +12423,14 @@
       <c r="L75" s="23"/>
       <c r="M75" s="23"/>
       <c r="N75" s="23"/>
-      <c r="Q75" s="51"/>
-      <c r="R75" s="51"/>
-      <c r="W75" s="51"/>
-      <c r="X75" s="51"/>
-    </row>
-    <row r="76" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B76" s="66" t="s">
-        <v>505</v>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+    </row>
+    <row r="76" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B76" s="58" t="s">
+        <v>494</v>
       </c>
       <c r="C76" s="23"/>
       <c r="D76" s="23"/>
@@ -9341,21 +12444,21 @@
       <c r="L76" s="23"/>
       <c r="M76" s="23"/>
       <c r="N76" s="23"/>
-      <c r="Q76" s="51"/>
-      <c r="R76" s="51"/>
-    </row>
-    <row r="77" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B77" s="61" t="s">
-        <v>506</v>
-      </c>
-      <c r="C77" s="61" t="s">
-        <v>507</v>
-      </c>
-      <c r="D77" s="61" t="s">
-        <v>508</v>
-      </c>
-      <c r="E77" s="62" t="s">
-        <v>509</v>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+    </row>
+    <row r="77" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B77" s="53" t="s">
+        <v>495</v>
+      </c>
+      <c r="C77" s="53" t="s">
+        <v>496</v>
+      </c>
+      <c r="D77" s="53" t="s">
+        <v>497</v>
+      </c>
+      <c r="E77" s="54" t="s">
+        <v>498</v>
       </c>
       <c r="F77" s="23"/>
       <c r="G77" s="23"/>
@@ -9366,10 +12469,10 @@
       <c r="L77" s="23"/>
       <c r="M77" s="23"/>
       <c r="N77" s="23"/>
-      <c r="Q77" s="51"/>
-      <c r="R77" s="51"/>
-    </row>
-    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+    </row>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B78" s="23"/>
       <c r="C78" s="23"/>
       <c r="D78" s="23"/>
@@ -9384,12 +12487,12 @@
       <c r="M78" s="23"/>
       <c r="N78" s="23"/>
     </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B79" s="23"/>
-      <c r="C79" s="49" t="s">
-        <v>504</v>
-      </c>
-      <c r="D79" s="49"/>
+      <c r="C79" s="75" t="s">
+        <v>493</v>
+      </c>
+      <c r="D79" s="75"/>
       <c r="E79" s="23"/>
       <c r="F79" s="23"/>
       <c r="G79" s="23"/>
@@ -9401,10 +12504,10 @@
       <c r="M79" s="23"/>
       <c r="N79" s="23"/>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B80" s="23"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
+      <c r="C80" s="75"/>
+      <c r="D80" s="75"/>
       <c r="E80" s="23"/>
       <c r="F80" s="23"/>
       <c r="G80" s="23"/>
@@ -9416,7 +12519,7 @@
       <c r="M80" s="23"/>
       <c r="N80" s="23"/>
     </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B81" s="23"/>
       <c r="C81" s="23"/>
       <c r="D81" s="23"/>
@@ -9431,7 +12534,7 @@
       <c r="M81" s="23"/>
       <c r="N81" s="23"/>
     </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B82" s="23"/>
       <c r="C82" s="23"/>
       <c r="D82" s="23"/>
@@ -9446,9 +12549,9 @@
       <c r="M82" s="23"/>
       <c r="N82" s="23"/>
     </row>
-    <row r="83" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B83" s="60" t="s">
-        <v>510</v>
+    <row r="83" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B83" s="52" t="s">
+        <v>499</v>
       </c>
       <c r="C83" s="23"/>
       <c r="D83" s="23"/>
@@ -9463,24 +12566,24 @@
       <c r="M83" s="23"/>
       <c r="N83" s="23"/>
     </row>
-    <row r="84" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B84" s="61" t="s">
-        <v>511</v>
-      </c>
-      <c r="C84" s="65" t="s">
-        <v>512</v>
-      </c>
-      <c r="D84" s="65" t="s">
-        <v>513</v>
-      </c>
-      <c r="E84" s="65" t="s">
-        <v>514</v>
-      </c>
-      <c r="F84" s="62" t="s">
-        <v>515</v>
-      </c>
-      <c r="G84" s="62" t="s">
-        <v>516</v>
+    <row r="84" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B84" s="53" t="s">
+        <v>500</v>
+      </c>
+      <c r="C84" s="57" t="s">
+        <v>501</v>
+      </c>
+      <c r="D84" s="57" t="s">
+        <v>502</v>
+      </c>
+      <c r="E84" s="57" t="s">
+        <v>503</v>
+      </c>
+      <c r="F84" s="54" t="s">
+        <v>504</v>
+      </c>
+      <c r="G84" s="54" t="s">
+        <v>505</v>
       </c>
       <c r="H84" s="23"/>
       <c r="I84" s="23"/>
@@ -9490,9 +12593,9 @@
       <c r="M84" s="23"/>
       <c r="N84" s="23"/>
     </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B85" s="23" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="C85" s="23"/>
       <c r="D85" s="23"/>
@@ -9507,14 +12610,14 @@
       <c r="M85" s="23"/>
       <c r="N85" s="23"/>
     </row>
-    <row r="86" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B86" s="23"/>
-      <c r="C86" s="50" t="s">
-        <v>518</v>
-      </c>
-      <c r="D86" s="49"/>
-      <c r="E86" s="49"/>
-      <c r="F86" s="49"/>
+      <c r="C86" s="77" t="s">
+        <v>507</v>
+      </c>
+      <c r="D86" s="75"/>
+      <c r="E86" s="75"/>
+      <c r="F86" s="75"/>
       <c r="G86" s="23"/>
       <c r="H86" s="23"/>
       <c r="I86" s="23"/>
@@ -9524,12 +12627,12 @@
       <c r="M86" s="23"/>
       <c r="N86" s="23"/>
     </row>
-    <row r="87" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B87" s="23"/>
-      <c r="C87" s="49"/>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="49"/>
+      <c r="C87" s="75"/>
+      <c r="D87" s="75"/>
+      <c r="E87" s="75"/>
+      <c r="F87" s="75"/>
       <c r="G87" s="23"/>
       <c r="H87" s="23"/>
       <c r="I87" s="23"/>
@@ -9539,12 +12642,12 @@
       <c r="M87" s="23"/>
       <c r="N87" s="23"/>
     </row>
-    <row r="88" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B88" s="23"/>
-      <c r="C88" s="49"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="49"/>
+      <c r="C88" s="75"/>
+      <c r="D88" s="75"/>
+      <c r="E88" s="75"/>
+      <c r="F88" s="75"/>
       <c r="G88" s="23"/>
       <c r="H88" s="23"/>
       <c r="I88" s="23"/>
@@ -9554,12 +12657,12 @@
       <c r="M88" s="23"/>
       <c r="N88" s="23"/>
     </row>
-    <row r="89" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B89" s="23"/>
-      <c r="C89" s="49"/>
-      <c r="D89" s="49"/>
-      <c r="E89" s="49"/>
-      <c r="F89" s="49"/>
+      <c r="C89" s="75"/>
+      <c r="D89" s="75"/>
+      <c r="E89" s="75"/>
+      <c r="F89" s="75"/>
       <c r="G89" s="23"/>
       <c r="H89" s="23"/>
       <c r="I89" s="23"/>
@@ -9569,7 +12672,7 @@
       <c r="M89" s="23"/>
       <c r="N89" s="23"/>
     </row>
-    <row r="90" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B90" s="23"/>
       <c r="C90" s="23"/>
       <c r="D90" s="23"/>
@@ -9584,9 +12687,9 @@
       <c r="M90" s="23"/>
       <c r="N90" s="23"/>
     </row>
-    <row r="91" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B91" s="60" t="s">
-        <v>519</v>
+    <row r="91" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B91" s="52" t="s">
+        <v>508</v>
       </c>
       <c r="C91" s="23"/>
       <c r="D91" s="23"/>
@@ -9601,12 +12704,12 @@
       <c r="M91" s="23"/>
       <c r="N91" s="23"/>
     </row>
-    <row r="92" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B92" s="61" t="s">
-        <v>520</v>
-      </c>
-      <c r="C92" s="63" t="s">
-        <v>521</v>
+    <row r="92" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B92" s="53" t="s">
+        <v>509</v>
+      </c>
+      <c r="C92" s="55" t="s">
+        <v>510</v>
       </c>
       <c r="D92" s="23"/>
       <c r="E92" s="23"/>
@@ -9620,11 +12723,11 @@
       <c r="M92" s="23"/>
       <c r="N92" s="23"/>
     </row>
-    <row r="93" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B93" s="68" t="s">
-        <v>522</v>
-      </c>
-      <c r="C93" s="68"/>
+    <row r="93" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B93" s="80" t="s">
+        <v>511</v>
+      </c>
+      <c r="C93" s="80"/>
       <c r="D93" s="23"/>
       <c r="E93" s="23"/>
       <c r="F93" s="23"/>
@@ -9637,9 +12740,9 @@
       <c r="M93" s="23"/>
       <c r="N93" s="23"/>
     </row>
-    <row r="94" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B94" s="49"/>
-      <c r="C94" s="49"/>
+    <row r="94" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B94" s="75"/>
+      <c r="C94" s="75"/>
       <c r="D94" s="23"/>
       <c r="E94" s="23"/>
       <c r="F94" s="23"/>
@@ -9652,9 +12755,9 @@
       <c r="M94" s="23"/>
       <c r="N94" s="23"/>
     </row>
-    <row r="95" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B95" s="49"/>
-      <c r="C95" s="49"/>
+    <row r="95" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B95" s="75"/>
+      <c r="C95" s="75"/>
       <c r="D95" s="23"/>
       <c r="E95" s="23"/>
       <c r="F95" s="23"/>
@@ -9667,7 +12770,7 @@
       <c r="M95" s="23"/>
       <c r="N95" s="23"/>
     </row>
-    <row r="96" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B96" s="23"/>
       <c r="C96" s="23"/>
       <c r="D96" s="23"/>
@@ -9682,9 +12785,9 @@
       <c r="M96" s="23"/>
       <c r="N96" s="23"/>
     </row>
-    <row r="97" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B97" s="60" t="s">
-        <v>523</v>
+    <row r="97" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B97" s="52" t="s">
+        <v>512</v>
       </c>
       <c r="C97" s="23"/>
       <c r="D97" s="23"/>
@@ -9699,19 +12802,19 @@
       <c r="M97" s="23"/>
       <c r="N97" s="23"/>
     </row>
-    <row r="98" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B98" s="61" t="s">
-        <v>524</v>
-      </c>
-      <c r="C98" s="61" t="s">
-        <v>525</v>
-      </c>
-      <c r="D98" s="62" t="s">
-        <v>526</v>
+    <row r="98" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B98" s="53" t="s">
+        <v>513</v>
+      </c>
+      <c r="C98" s="53" t="s">
+        <v>514</v>
+      </c>
+      <c r="D98" s="54" t="s">
+        <v>515</v>
       </c>
       <c r="E98" s="23"/>
-      <c r="F98" s="60" t="s">
-        <v>527</v>
+      <c r="F98" s="52" t="s">
+        <v>516</v>
       </c>
       <c r="G98" s="23"/>
       <c r="H98" s="23"/>
@@ -9722,24 +12825,24 @@
       <c r="M98" s="23"/>
       <c r="N98" s="23"/>
     </row>
-    <row r="99" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B99" s="69" t="s">
-        <v>528</v>
-      </c>
-      <c r="C99" s="69"/>
-      <c r="D99" s="69"/>
+    <row r="99" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B99" s="76" t="s">
+        <v>517</v>
+      </c>
+      <c r="C99" s="76"/>
+      <c r="D99" s="76"/>
       <c r="E99" s="23"/>
-      <c r="F99" s="61" t="s">
-        <v>289</v>
-      </c>
-      <c r="G99" s="61" t="s">
-        <v>529</v>
-      </c>
-      <c r="H99" s="63" t="s">
-        <v>530</v>
-      </c>
-      <c r="I99" s="62" t="s">
-        <v>531</v>
+      <c r="F99" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="G99" s="53" t="s">
+        <v>518</v>
+      </c>
+      <c r="H99" s="55" t="s">
+        <v>519</v>
+      </c>
+      <c r="I99" s="54" t="s">
+        <v>520</v>
       </c>
       <c r="J99" s="23"/>
       <c r="K99" s="23"/>
@@ -9747,10 +12850,10 @@
       <c r="M99" s="23"/>
       <c r="N99" s="23"/>
     </row>
-    <row r="100" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B100" s="69"/>
-      <c r="C100" s="69"/>
-      <c r="D100" s="69"/>
+    <row r="100" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B100" s="76"/>
+      <c r="C100" s="76"/>
+      <c r="D100" s="76"/>
       <c r="E100" s="23"/>
       <c r="F100" s="21"/>
       <c r="G100" s="21"/>
@@ -9762,20 +12865,20 @@
       <c r="M100" s="23"/>
       <c r="N100" s="23"/>
     </row>
-    <row r="101" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B101" s="69"/>
-      <c r="C101" s="69"/>
-      <c r="D101" s="69"/>
+    <row r="101" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B101" s="76"/>
+      <c r="C101" s="76"/>
+      <c r="D101" s="76"/>
       <c r="E101" s="23"/>
-      <c r="F101" s="76" t="s">
-        <v>532</v>
+      <c r="F101" s="65" t="s">
+        <v>521</v>
       </c>
       <c r="G101" s="21"/>
       <c r="H101" s="21" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="I101" s="21" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="J101" s="23"/>
       <c r="K101" s="23"/>
@@ -9783,7 +12886,7 @@
       <c r="M101" s="23"/>
       <c r="N101" s="23"/>
     </row>
-    <row r="102" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B102" s="21">
         <v>1</v>
       </c>
@@ -9794,15 +12897,15 @@
         <v>2</v>
       </c>
       <c r="E102" s="23"/>
-      <c r="F102" s="76" t="s">
-        <v>534</v>
+      <c r="F102" s="65" t="s">
+        <v>523</v>
       </c>
       <c r="G102" s="21"/>
       <c r="H102" s="21" t="s">
-        <v>535</v>
-      </c>
-      <c r="I102" s="64" t="s">
-        <v>536</v>
+        <v>524</v>
+      </c>
+      <c r="I102" s="56" t="s">
+        <v>525</v>
       </c>
       <c r="J102" s="23"/>
       <c r="K102" s="23"/>
@@ -9810,7 +12913,7 @@
       <c r="M102" s="23"/>
       <c r="N102" s="23"/>
     </row>
-    <row r="103" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B103" s="21">
         <v>1</v>
       </c>
@@ -9821,15 +12924,15 @@
         <v>4</v>
       </c>
       <c r="E103" s="23"/>
-      <c r="F103" s="76" t="s">
-        <v>537</v>
+      <c r="F103" s="65" t="s">
+        <v>526</v>
       </c>
       <c r="G103" s="21"/>
       <c r="H103" s="21" t="s">
-        <v>538</v>
-      </c>
-      <c r="I103" s="64" t="s">
-        <v>536</v>
+        <v>527</v>
+      </c>
+      <c r="I103" s="56" t="s">
+        <v>525</v>
       </c>
       <c r="J103" s="23"/>
       <c r="K103" s="23"/>
@@ -9837,7 +12940,7 @@
       <c r="M103" s="23"/>
       <c r="N103" s="23"/>
     </row>
-    <row r="104" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B104" s="21">
         <v>2</v>
       </c>
@@ -9848,15 +12951,15 @@
         <v>2</v>
       </c>
       <c r="E104" s="23"/>
-      <c r="F104" s="76" t="s">
-        <v>539</v>
+      <c r="F104" s="65" t="s">
+        <v>528</v>
       </c>
       <c r="G104" s="21"/>
       <c r="H104" s="21" t="s">
-        <v>540</v>
-      </c>
-      <c r="I104" s="64" t="s">
-        <v>536</v>
+        <v>529</v>
+      </c>
+      <c r="I104" s="56" t="s">
+        <v>525</v>
       </c>
       <c r="J104" s="23"/>
       <c r="K104" s="23"/>
@@ -9864,7 +12967,7 @@
       <c r="M104" s="23"/>
       <c r="N104" s="23"/>
     </row>
-    <row r="105" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B105" s="21">
         <v>2</v>
       </c>
@@ -9875,12 +12978,12 @@
         <v>2</v>
       </c>
       <c r="E105" s="23"/>
-      <c r="F105" s="76" t="s">
-        <v>541</v>
+      <c r="F105" s="65" t="s">
+        <v>530</v>
       </c>
       <c r="G105" s="21"/>
       <c r="H105" s="21" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="I105" s="21"/>
       <c r="J105" s="23"/>
@@ -9889,7 +12992,7 @@
       <c r="M105" s="23"/>
       <c r="N105" s="23"/>
     </row>
-    <row r="106" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B106" s="21">
         <v>3</v>
       </c>
@@ -9910,7 +13013,7 @@
       <c r="M106" s="23"/>
       <c r="N106" s="23"/>
     </row>
-    <row r="107" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B107" s="21">
         <v>3</v>
       </c>
@@ -9931,7 +13034,7 @@
       <c r="M107" s="23"/>
       <c r="N107" s="23"/>
     </row>
-    <row r="108" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B108" s="21">
         <v>4</v>
       </c>
@@ -9952,7 +13055,7 @@
       <c r="M108" s="23"/>
       <c r="N108" s="23"/>
     </row>
-    <row r="109" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B109" s="21">
         <v>4</v>
       </c>
@@ -9973,7 +13076,7 @@
       <c r="M109" s="23"/>
       <c r="N109" s="23"/>
     </row>
-    <row r="110" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B110" s="21">
         <v>5</v>
       </c>
@@ -9994,7 +13097,7 @@
       <c r="M110" s="23"/>
       <c r="N110" s="23"/>
     </row>
-    <row r="111" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B111" s="21">
         <v>5</v>
       </c>
@@ -10015,7 +13118,7 @@
       <c r="M111" s="23"/>
       <c r="N111" s="23"/>
     </row>
-    <row r="112" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B112" s="21">
         <v>5</v>
       </c>
@@ -10036,7 +13139,7 @@
       <c r="M112" s="23"/>
       <c r="N112" s="23"/>
     </row>
-    <row r="113" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B113" s="21">
         <v>5</v>
       </c>
@@ -10057,7 +13160,7 @@
       <c r="M113" s="23"/>
       <c r="N113" s="23"/>
     </row>
-    <row r="114" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B114" s="21">
         <v>6</v>
       </c>
@@ -10078,7 +13181,7 @@
       <c r="M114" s="23"/>
       <c r="N114" s="23"/>
     </row>
-    <row r="115" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B115" s="21">
         <v>7</v>
       </c>
@@ -10099,7 +13202,7 @@
       <c r="M115" s="23"/>
       <c r="N115" s="23"/>
     </row>
-    <row r="116" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B116" s="21">
         <v>8</v>
       </c>
@@ -10120,7 +13223,7 @@
       <c r="M116" s="23"/>
       <c r="N116" s="23"/>
     </row>
-    <row r="117" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B117" s="21">
         <v>8</v>
       </c>
@@ -10141,7 +13244,7 @@
       <c r="M117" s="23"/>
       <c r="N117" s="23"/>
     </row>
-    <row r="118" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B118" s="21">
         <v>8</v>
       </c>
@@ -10162,7 +13265,7 @@
       <c r="M118" s="23"/>
       <c r="N118" s="23"/>
     </row>
-    <row r="119" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B119" s="21">
         <v>9</v>
       </c>
@@ -10183,7 +13286,7 @@
       <c r="M119" s="23"/>
       <c r="N119" s="23"/>
     </row>
-    <row r="120" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B120" s="21">
         <v>9</v>
       </c>
@@ -10204,7 +13307,7 @@
       <c r="M120" s="23"/>
       <c r="N120" s="23"/>
     </row>
-    <row r="121" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B121" s="21">
         <v>9</v>
       </c>
@@ -10225,7 +13328,7 @@
       <c r="M121" s="23"/>
       <c r="N121" s="23"/>
     </row>
-    <row r="122" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B122" s="21">
         <v>9</v>
       </c>
@@ -10246,7 +13349,7 @@
       <c r="M122" s="23"/>
       <c r="N122" s="23"/>
     </row>
-    <row r="123" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B123" s="21">
         <v>9</v>
       </c>
@@ -10267,7 +13370,7 @@
       <c r="M123" s="23"/>
       <c r="N123" s="23"/>
     </row>
-    <row r="124" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B124" s="21">
         <v>10</v>
       </c>
@@ -10288,7 +13391,7 @@
       <c r="M124" s="23"/>
       <c r="N124" s="23"/>
     </row>
-    <row r="125" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B125" s="21">
         <v>10</v>
       </c>
@@ -10309,7 +13412,7 @@
       <c r="M125" s="23"/>
       <c r="N125" s="23"/>
     </row>
-    <row r="126" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B126" s="21">
         <v>11</v>
       </c>
@@ -10330,7 +13433,7 @@
       <c r="M126" s="23"/>
       <c r="N126" s="23"/>
     </row>
-    <row r="127" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B127" s="21">
         <v>11</v>
       </c>
@@ -10351,7 +13454,7 @@
       <c r="M127" s="23"/>
       <c r="N127" s="23"/>
     </row>
-    <row r="128" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B128" s="21">
         <v>11</v>
       </c>
@@ -10372,7 +13475,7 @@
       <c r="M128" s="23"/>
       <c r="N128" s="23"/>
     </row>
-    <row r="129" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B129" s="21">
         <v>11</v>
       </c>
@@ -10393,7 +13496,7 @@
       <c r="M129" s="23"/>
       <c r="N129" s="23"/>
     </row>
-    <row r="130" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B130" s="21">
         <v>11</v>
       </c>
@@ -10414,7 +13517,7 @@
       <c r="M130" s="23"/>
       <c r="N130" s="23"/>
     </row>
-    <row r="131" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B131" s="21">
         <v>11</v>
       </c>
@@ -10435,7 +13538,7 @@
       <c r="M131" s="23"/>
       <c r="N131" s="23"/>
     </row>
-    <row r="132" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B132" s="21">
         <v>12</v>
       </c>
@@ -10456,7 +13559,7 @@
       <c r="M132" s="23"/>
       <c r="N132" s="23"/>
     </row>
-    <row r="133" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B133" s="21">
         <v>13</v>
       </c>
@@ -10477,7 +13580,7 @@
       <c r="M133" s="23"/>
       <c r="N133" s="23"/>
     </row>
-    <row r="134" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B134" s="21">
         <v>13</v>
       </c>
@@ -10498,7 +13601,7 @@
       <c r="M134" s="23"/>
       <c r="N134" s="23"/>
     </row>
-    <row r="135" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B135" s="23"/>
       <c r="C135" s="23"/>
       <c r="D135" s="23"/>

--- a/1. Database Design/Java23 QuyenPhan Database Design.xlsx
+++ b/1. Database Design/Java23 QuyenPhan Database Design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java23\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9244EE11-2682-4302-A5BC-A0EE2C86A733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2DA501-580C-443E-9607-72818A602B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="588" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <sheet name="B3. Mô hình quan hệ" sheetId="6" r:id="rId4"/>
     <sheet name="B4. Mô hình vật lý" sheetId="4" r:id="rId5"/>
     <sheet name="B5. Tạo dữ liệu mẫu" sheetId="7" r:id="rId6"/>
-    <sheet name=" Tạo dữ liệu mẫu" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -372,176 +371,8 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={AEBDE81C-C7EB-44D3-9FD1-1E7BD5E6786F}</author>
-    <author>tc={A0119B23-EB2B-4378-9CB4-0DAA4A44D5D7}</author>
-    <author>tc={24AF3A3A-F5AA-436C-9C80-F09CF400C36D}</author>
-    <author>tc={19BF21FC-50B2-486E-8D1B-3B13A7DA5ACB}</author>
-    <author>tc={3184D4F8-8F30-4EE9-9B85-39F0B1698953}</author>
-    <author>Quyen Ngoc Phan</author>
-    <author>tc={617068EA-E7BF-491D-BCB0-789585B6E8BF}</author>
-    <author>tc={FA5DB468-2A8C-4989-A235-495D9D65D27F}</author>
-    <author>tc={6B12C570-F8EA-4C79-8537-EEC76B43FCDD}</author>
-    <author>tc={961FA70D-089B-4E54-85E9-4C652A974B69}</author>
-  </authors>
-  <commentList>
-    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{AEBDE81C-C7EB-44D3-9FD1-1E7BD5E6786F}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Các sản phầm mua vào đều chung giá, k quan tâm kích cỡ, màu sắc, chất liệu</t>
-      </text>
-    </comment>
-    <comment ref="K5" authorId="1" shapeId="0" xr:uid="{A0119B23-EB2B-4378-9CB4-0DAA4A44D5D7}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Chờ xác nhận, Đang đóng gói, Đóng gói hoàn thành chờ vận chuyển, Đang vận chuyển, Giao hàng thành công, Giao hàng thất bại, Hủy đơn hàng</t>
-      </text>
-    </comment>
-    <comment ref="H15" authorId="2" shapeId="0" xr:uid="{24AF3A3A-F5AA-436C-9C80-F09CF400C36D}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Tiền mặt, thẻ tín dụng, thẻ ghi nợ, ví điện tử</t>
-      </text>
-    </comment>
-    <comment ref="B56" authorId="3" shapeId="0" xr:uid="{19BF21FC-50B2-486E-8D1B-3B13A7DA5ACB}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Không cần thuộc phòng ban, làm được mọi chức năng</t>
-      </text>
-    </comment>
-    <comment ref="I57" authorId="4" shapeId="0" xr:uid="{3184D4F8-8F30-4EE9-9B85-39F0B1698953}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    NhanVien, Quan Ly</t>
-      </text>
-    </comment>
-    <comment ref="C71" authorId="5" shapeId="0" xr:uid="{3F9683E3-A7BE-4CA9-B83D-D4542BA4E5E6}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quyen Ngoc Phan:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Lưu KDL DATE
-VD: 25/03 --&gt; tương ứng với ngày 25/03 0H0</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D71" authorId="5" shapeId="0" xr:uid="{C4075EF3-5442-4784-99BE-A001DD114D26}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quyen Ngoc Phan:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Lưu KDL DATE
-VD: 28/03 --&gt; tương ứng với ngày 28/3 23H59H59
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E71" authorId="6" shapeId="0" xr:uid="{617068EA-E7BF-491D-BCB0-789585B6E8BF}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Số lượng bán
-</t>
-      </text>
-    </comment>
-    <comment ref="F71" authorId="7" shapeId="0" xr:uid="{FA5DB468-2A8C-4989-A235-495D9D65D27F}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Doanh thu cho mặt hàng theo giai đoạn</t>
-      </text>
-    </comment>
-    <comment ref="B76" authorId="5" shapeId="0" xr:uid="{6B8FFBD9-357F-4A90-A4AD-ADE4BF3B41A9}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quyen Ngoc Phan:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Bảng doanh thu, lưu doanh thu bán hàng từ ngày from đến ngày until số tiền bao nhiêu
-Chưa xử lý lưu trữ danh sách mặt hàng, đơn hàng</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E84" authorId="8" shapeId="0" xr:uid="{6B12C570-F8EA-4C79-8537-EEC76B43FCDD}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Có rất nhiều màu sắc color, rgb, hexa -&gt; sử dụng varchar để lưu chứ k tạo 1 bảng riêng</t>
-      </text>
-    </comment>
-    <comment ref="G84" authorId="9" shapeId="0" xr:uid="{961FA70D-089B-4E54-85E9-4C652A974B69}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Số lượng hàng còn lại ở thời điểm hiện tại</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="506">
   <si>
     <t>MatHang</t>
   </si>
@@ -1513,9 +1344,6 @@
     <t>C08_EMPLOYEE_DOB</t>
   </si>
   <si>
-    <t>C08_TITLE_ID</t>
-  </si>
-  <si>
     <t>T15_BILL</t>
   </si>
   <si>
@@ -1624,66 +1452,27 @@
     <t>file://img04</t>
   </si>
   <si>
-    <t>C01_BUY_PRICE</t>
-  </si>
-  <si>
-    <t>T02_ITEMGROUP</t>
-  </si>
-  <si>
-    <t>T05_ORDER_STATUS</t>
-  </si>
-  <si>
-    <t>T08_TITLE</t>
-  </si>
-  <si>
     <t>Áo 1</t>
   </si>
   <si>
-    <t>C02_ITEMGROUP_ID</t>
-  </si>
-  <si>
-    <t>C02_ITEMGROUP_NAME</t>
-  </si>
-  <si>
-    <t>C05_ORDER_STATUS_ID</t>
-  </si>
-  <si>
-    <t>C05_ORDER_STATUS_DESC</t>
-  </si>
-  <si>
-    <t>C08_TITLE_NAME</t>
-  </si>
-  <si>
     <t>Áo 2</t>
   </si>
   <si>
     <t>Áo</t>
   </si>
   <si>
-    <t>Chờ xác nhận</t>
-  </si>
-  <si>
-    <t>Nhân viên</t>
-  </si>
-  <si>
     <t>Áo 3</t>
   </si>
   <si>
     <t>Quần</t>
   </si>
   <si>
-    <t>Trưởng bộ phận</t>
-  </si>
-  <si>
     <t>Quần 4</t>
   </si>
   <si>
     <t>Giày</t>
   </si>
   <si>
-    <t>Đóng gói hoàn thành</t>
-  </si>
-  <si>
     <t>Giám đốc</t>
   </si>
   <si>
@@ -1693,72 +1482,33 @@
     <t>Dép</t>
   </si>
   <si>
-    <t>Đang vận chuyển</t>
-  </si>
-  <si>
-    <t>Chủ sở hữu</t>
-  </si>
-  <si>
     <t>Giày 6</t>
   </si>
   <si>
     <t>Mũ</t>
   </si>
   <si>
-    <t>Giao hàng thành công</t>
-  </si>
-  <si>
     <t>Giày 7</t>
   </si>
   <si>
     <t>Thắt lưng</t>
   </si>
   <si>
-    <t>Giao hàng thất bại</t>
-  </si>
-  <si>
     <t>Giày 8</t>
   </si>
   <si>
     <t>Túi xách</t>
   </si>
   <si>
-    <t>Hủy đơn hàng</t>
-  </si>
-  <si>
     <t>Giày 9</t>
   </si>
   <si>
     <t>Giày 10</t>
   </si>
   <si>
-    <t>T04_PAYMENT_METHOD</t>
-  </si>
-  <si>
-    <t>T06_SIZE</t>
-  </si>
-  <si>
     <t>Giép 11</t>
   </si>
   <si>
-    <t>C04_PMETHOD_ID</t>
-  </si>
-  <si>
-    <t>C04_PMETHOD_DESC</t>
-  </si>
-  <si>
-    <t>C06_SIZE_ID</t>
-  </si>
-  <si>
-    <t>C06_SIZE_NAME</t>
-  </si>
-  <si>
-    <t>C06_GENDER</t>
-  </si>
-  <si>
-    <t>C06_SIZE_DESC</t>
-  </si>
-  <si>
     <t>Áo 12</t>
   </si>
   <si>
@@ -1828,36 +1578,6 @@
     <t>Size 'XXL' cho Nam</t>
   </si>
   <si>
-    <t>T03_ORDER</t>
-  </si>
-  <si>
-    <t>Dùng công thức để tính</t>
-  </si>
-  <si>
-    <t>C03_ORDER_ID</t>
-  </si>
-  <si>
-    <t>C03_ORDER_TIME</t>
-  </si>
-  <si>
-    <t>C03_DELIVERY_FEE</t>
-  </si>
-  <si>
-    <t>C03_DELIVERY_ADDRESS</t>
-  </si>
-  <si>
-    <t>C03_RECEIVER_PHONE</t>
-  </si>
-  <si>
-    <t>C03_TOTAL_OF_MONEY</t>
-  </si>
-  <si>
-    <t>C03_PMETHOD_ID</t>
-  </si>
-  <si>
-    <t>C03_CUSTOMER_ID</t>
-  </si>
-  <si>
     <t>10.04.2024 08:10:20</t>
   </si>
   <si>
@@ -1921,33 +1641,6 @@
     <t>Địa chỉ 13</t>
   </si>
   <si>
-    <t>T11_CUSTOMER</t>
-  </si>
-  <si>
-    <t>C11_CUSTOMER_ID</t>
-  </si>
-  <si>
-    <t>C11_CUSTOMER_NAME</t>
-  </si>
-  <si>
-    <t>C11_CUSTOMER_EMAIL</t>
-  </si>
-  <si>
-    <t>C11_CUSTOMER_ADDRESS</t>
-  </si>
-  <si>
-    <t>C11_CUSTOMER_PHONE</t>
-  </si>
-  <si>
-    <t>C11_CUSTOMER_USERNAME</t>
-  </si>
-  <si>
-    <t>C11_CUSTOMER_PASSWORD</t>
-  </si>
-  <si>
-    <t>Lê Tèo</t>
-  </si>
-  <si>
     <t>c1@gmal.com</t>
   </si>
   <si>
@@ -1957,147 +1650,81 @@
     <t>$2a$12$w0bs0MW/O3nTyMhuv0r1jOjq2gOaxLxkZgms7u/khHRmtCh3S/Hpu</t>
   </si>
   <si>
-    <t>Văn An</t>
-  </si>
-  <si>
     <t>c2@gmal.com</t>
   </si>
   <si>
     <t>c2auto</t>
   </si>
   <si>
-    <t>Nguyễn A</t>
-  </si>
-  <si>
     <t>c3@gmal.com</t>
   </si>
   <si>
     <t>c3def</t>
   </si>
   <si>
-    <t>Phan Tuấn</t>
-  </si>
-  <si>
     <t>c4@gmal.com</t>
   </si>
   <si>
     <t>c4auto</t>
   </si>
   <si>
-    <t>Hoàng Tiên</t>
-  </si>
-  <si>
     <t>c5@gmal.com</t>
   </si>
   <si>
     <t>c5def</t>
   </si>
   <si>
-    <t>Phạm Ngọc</t>
-  </si>
-  <si>
     <t>c6@gmal.com</t>
   </si>
   <si>
     <t>c6auto</t>
   </si>
   <si>
-    <t>Đoạn Tú</t>
-  </si>
-  <si>
     <t>c7@gmal.com</t>
   </si>
   <si>
     <t>c7def</t>
   </si>
   <si>
-    <t>Hoàng B</t>
-  </si>
-  <si>
     <t>c8@gmal.com</t>
   </si>
   <si>
     <t>c8auto</t>
   </si>
   <si>
-    <t>Lê Huân</t>
-  </si>
-  <si>
     <t>c9@gmal.com</t>
   </si>
   <si>
     <t>c9def</t>
   </si>
   <si>
-    <t>Nam Ban</t>
-  </si>
-  <si>
     <t>c10@gmal.com</t>
   </si>
   <si>
     <t>c10auto</t>
   </si>
   <si>
-    <t>T07_EMPLOYEE</t>
-  </si>
-  <si>
-    <t>C07_EMPLOYEE_ID</t>
-  </si>
-  <si>
-    <t>C07_EMPLOYEE_NAME</t>
-  </si>
-  <si>
-    <t>C07_EMPLOYEE_EMAIL</t>
-  </si>
-  <si>
-    <t>C07_EMPLOYEE_ADDRESS</t>
-  </si>
-  <si>
-    <t>C07_EMPLOYEE_PHONE</t>
-  </si>
-  <si>
-    <t>C07_EMPLOYEE_USERNAME</t>
-  </si>
-  <si>
-    <t>C07_EMPLOYEE_PASSWORD</t>
-  </si>
-  <si>
-    <t>C07_TITLE_ID</t>
-  </si>
-  <si>
     <t>Nhân viên 1</t>
   </si>
   <si>
-    <t>nv1@gmal.com</t>
-  </si>
-  <si>
     <t>nv1def</t>
   </si>
   <si>
     <t>Nhân viên 2</t>
   </si>
   <si>
-    <t>nv2@gmal.com</t>
-  </si>
-  <si>
     <t>nv2auto</t>
   </si>
   <si>
     <t>Nhân viên 3</t>
   </si>
   <si>
-    <t>nv3@gmal.com</t>
-  </si>
-  <si>
     <t>nv3def</t>
   </si>
   <si>
     <t>Nhân viên 4</t>
   </si>
   <si>
-    <t>nv4@gmal.com</t>
-  </si>
-  <si>
     <t>nv4auto</t>
   </si>
   <si>
@@ -2113,184 +1740,37 @@
     <t>Nhân viên 6</t>
   </si>
   <si>
-    <t>nv6@gmal.com</t>
-  </si>
-  <si>
     <t>nv6auto</t>
   </si>
   <si>
     <t>Nhân viên 7</t>
   </si>
   <si>
-    <t>nv7@gmal.com</t>
-  </si>
-  <si>
     <t>nv7def</t>
   </si>
   <si>
     <t>Nhân viên 8</t>
   </si>
   <si>
-    <t>nv8@gmal.com</t>
-  </si>
-  <si>
     <t>nv8auto</t>
   </si>
   <si>
     <t>Nhân viên 9</t>
   </si>
   <si>
-    <t>nv9@gmal.com</t>
-  </si>
-  <si>
     <t>nv9def</t>
   </si>
   <si>
     <t>Nhân viên 10</t>
   </si>
   <si>
-    <t>nv10@gmal.com</t>
-  </si>
-  <si>
     <t>nv10auto</t>
   </si>
   <si>
-    <t>T09_ITEM_STATISTIC</t>
-  </si>
-  <si>
-    <t>C09_ITEM_ID</t>
-  </si>
-  <si>
-    <t>C09_DATE_FROM</t>
-  </si>
-  <si>
-    <t>C09_DATE_UNTIL</t>
-  </si>
-  <si>
-    <t>C09_SALES_AMOUNT</t>
-  </si>
-  <si>
-    <t>C09_REVENUE</t>
-  </si>
-  <si>
-    <t>Bài tập phần DML - Tạo câu truy vấn để xử lý</t>
-  </si>
-  <si>
-    <t>T10_REVENUE</t>
-  </si>
-  <si>
-    <t>C10_RID</t>
-  </si>
-  <si>
-    <t>C10_DATE_FROM</t>
-  </si>
-  <si>
-    <t>C10_DATE_UNITIL</t>
-  </si>
-  <si>
-    <t>C10_TOTAL_OF_MONEY</t>
-  </si>
-  <si>
-    <t>T12_ITEM_DETAIL</t>
-  </si>
-  <si>
-    <t>C12_ITEM_DETAIL_ID</t>
-  </si>
-  <si>
-    <t>C12_ITEM_ID</t>
-  </si>
-  <si>
-    <t>C12_SIZE_ID</t>
-  </si>
-  <si>
-    <t>C12_COLOR</t>
-  </si>
-  <si>
-    <t>C12_SALES_PRICE</t>
-  </si>
-  <si>
-    <t>C12_AMOUNT</t>
-  </si>
-  <si>
     <t>Fake 100 rows</t>
   </si>
   <si>
-    <t>Sử dụng dữ liệu từ các bảng ITEM, SIZE
----
-ITEM, SIZE có ID lẻ: AMOUNT = 125, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5
-ITEM, SIZE có ID chẵn: AMOUNT = 280, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5 + 20</t>
-  </si>
-  <si>
-    <t>T13_GALLERY</t>
-  </si>
-  <si>
-    <t>C13_PATH</t>
-  </si>
-  <si>
-    <t>C13_ITEM_ID</t>
-  </si>
-  <si>
-    <t>Sử dụng ITEM ID từ bảng ITEM và fake default path</t>
-  </si>
-  <si>
-    <t>T14_ORDER_DETAIL</t>
-  </si>
-  <si>
-    <t>C14_ORDER_ID</t>
-  </si>
-  <si>
-    <t>C14_ITEM_DETAIL_ID</t>
-  </si>
-  <si>
-    <t>C14_AMOUNT</t>
-  </si>
-  <si>
-    <t>T15_ORDER_STATUS_DETAIL</t>
-  </si>
-  <si>
     <t>Large amount of data</t>
-  </si>
-  <si>
-    <t>C15_ORDER_STATUS_ID</t>
-  </si>
-  <si>
-    <t>C15_EMPLOYEE_ID</t>
-  </si>
-  <si>
-    <t>C15_LAST_UPDATED</t>
-  </si>
-  <si>
-    <t>-- 1. Đơn hàng từ 1 - 5 --&gt; Giao thành công (trạng thái từ 1 - 5)</t>
-  </si>
-  <si>
-    <t>SYSDATE - [max(STATUS_ID) - ORDER_STATUS_Id]</t>
-  </si>
-  <si>
-    <t>-- 2 Đơn hàng từ 6 - 8 --&gt; Đóng gói thành công (trạng thái từ 1 - 3)</t>
-  </si>
-  <si>
-    <t>Nhân Viên 2</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>-- 3. Đơn hàng từ 9 - 10 --&gt; Đang giao hàng (trạng thái từ 1 - 4)</t>
-  </si>
-  <si>
-    <t>Nhân Viên 3</t>
-  </si>
-  <si>
-    <t>-- 4. Đơn hàng từ 11 - 12 --&gt; Hủy đơn hàng (trạng thái 7)</t>
-  </si>
-  <si>
-    <t>Nhân Viên 4</t>
-  </si>
-  <si>
-    <t>-- 4. Đơn hàng từ 13  --&gt; Giao hàng thất bại (trạng thái 1,2,3,4,6)</t>
-  </si>
-  <si>
-    <t>Nhân Viên 5</t>
   </si>
   <si>
     <t>C06_CREATED_BY</t>
@@ -2427,15 +1907,6 @@
     <t>Nhân viên 13</t>
   </si>
   <si>
-    <t>nv11@gmal.com</t>
-  </si>
-  <si>
-    <t>nv12@gmal.com</t>
-  </si>
-  <si>
-    <t>nv13@gmal.com</t>
-  </si>
-  <si>
     <t>nv11auto</t>
   </si>
   <si>
@@ -2541,12 +2012,54 @@
   <si>
     <t>random 1 2 3 4 5</t>
   </si>
+  <si>
+    <t xml:space="preserve"> - employee_id(year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - employee_id(day)</t>
+  </si>
+  <si>
+    <t>nv1@gmail.com</t>
+  </si>
+  <si>
+    <t>nv2@gmail.com</t>
+  </si>
+  <si>
+    <t>nv3@gmail.com</t>
+  </si>
+  <si>
+    <t>nv4@gmail.com</t>
+  </si>
+  <si>
+    <t>nv6@gmail.com</t>
+  </si>
+  <si>
+    <t>nv7@gmail.com</t>
+  </si>
+  <si>
+    <t>nv8@gmail.com</t>
+  </si>
+  <si>
+    <t>nv9@gmail.com</t>
+  </si>
+  <si>
+    <t>nv10@gmail.com</t>
+  </si>
+  <si>
+    <t>nv11@gmail.com</t>
+  </si>
+  <si>
+    <t>nv12@gmail.com</t>
+  </si>
+  <si>
+    <t>nv13@gmail.com</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2593,22 +2106,7 @@
     <font>
       <strike/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2725,14 +2223,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FF7030A0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
@@ -2840,9 +2330,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2897,7 +2387,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2911,106 +2401,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3023,14 +2481,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3053,11 +2514,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3082,15 +2540,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>33169</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>165721</xdr:rowOff>
+      <xdr:colOff>42134</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>58144</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1181057</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>10374</xdr:rowOff>
+      <xdr:colOff>1190022</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>64163</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3113,7 +2571,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1037216" y="2102097"/>
+          <a:off x="1046181" y="2693768"/>
           <a:ext cx="3666970" cy="2767148"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3450,39 +2908,6 @@
 </ThreadedComments>
 </file>
 
-<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D4" dT="2024-03-19T12:47:34.71" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{AEBDE81C-C7EB-44D3-9FD1-1E7BD5E6786F}">
-    <text>Các sản phầm mua vào đều chung giá, k quan tâm kích cỡ, màu sắc, chất liệu</text>
-  </threadedComment>
-  <threadedComment ref="K5" dT="2024-04-06T14:25:21.49" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{A0119B23-EB2B-4378-9CB4-0DAA4A44D5D7}">
-    <text>Chờ xác nhận, Đang đóng gói, Đóng gói hoàn thành chờ vận chuyển, Đang vận chuyển, Giao hàng thành công, Giao hàng thất bại, Hủy đơn hàng</text>
-  </threadedComment>
-  <threadedComment ref="H15" dT="2024-04-06T14:23:17.00" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{24AF3A3A-F5AA-436C-9C80-F09CF400C36D}">
-    <text>Tiền mặt, thẻ tín dụng, thẻ ghi nợ, ví điện tử</text>
-  </threadedComment>
-  <threadedComment ref="B56" dT="2024-03-19T13:48:38.72" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{19BF21FC-50B2-486E-8D1B-3B13A7DA5ACB}">
-    <text>Không cần thuộc phòng ban, làm được mọi chức năng</text>
-  </threadedComment>
-  <threadedComment ref="I57" dT="2024-03-19T13:49:56.69" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{3184D4F8-8F30-4EE9-9B85-39F0B1698953}">
-    <text>NhanVien, Quan Ly</text>
-  </threadedComment>
-  <threadedComment ref="E71" dT="2024-04-02T13:49:52.63" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{617068EA-E7BF-491D-BCB0-789585B6E8BF}">
-    <text xml:space="preserve">Số lượng bán
-</text>
-  </threadedComment>
-  <threadedComment ref="F71" dT="2024-04-02T13:55:15.51" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{FA5DB468-2A8C-4989-A235-495D9D65D27F}">
-    <text>Doanh thu cho mặt hàng theo giai đoạn</text>
-  </threadedComment>
-  <threadedComment ref="E84" dT="2024-04-02T12:50:53.71" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{6B12C570-F8EA-4C79-8537-EEC76B43FCDD}">
-    <text>Có rất nhiều màu sắc color, rgb, hexa -&gt; sử dụng varchar để lưu chứ k tạo 1 bảng riêng</text>
-  </threadedComment>
-  <threadedComment ref="G84" dT="2024-04-02T13:53:18.17" personId="{A812FB81-B3B8-4886-9A89-2A0AED0B8B34}" id="{961FA70D-089B-4E54-85E9-4C652A974B69}">
-    <text>Số lượng hàng còn lại ở thời điểm hiện tại</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A4:L24"/>
@@ -5098,12 +4523,12 @@
       <c r="Q13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="R13" s="73" t="s">
+      <c r="R13" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="S13" s="73"/>
-      <c r="T13" s="73"/>
-      <c r="U13" s="73"/>
+      <c r="S13" s="62"/>
+      <c r="T13" s="62"/>
+      <c r="U13" s="62"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D14" s="4"/>
@@ -5116,10 +4541,10 @@
       <c r="Q14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="R14" s="73"/>
-      <c r="S14" s="73"/>
-      <c r="T14" s="73"/>
-      <c r="U14" s="73"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="62"/>
+      <c r="T14" s="62"/>
+      <c r="U14" s="62"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
@@ -6190,7 +5615,7 @@
     <col min="13" max="13" width="27.6640625" customWidth="1"/>
     <col min="14" max="14" width="30.88671875" customWidth="1"/>
     <col min="15" max="17" width="22.6640625" customWidth="1"/>
-    <col min="18" max="18" width="24.109375" customWidth="1"/>
+    <col min="18" max="18" width="26.33203125" customWidth="1"/>
     <col min="19" max="19" width="35.109375" customWidth="1"/>
     <col min="20" max="20" width="21.5546875" customWidth="1"/>
     <col min="21" max="22" width="12.6640625" customWidth="1"/>
@@ -6202,33 +5627,30 @@
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
     </row>
     <row r="3" spans="2:20" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D3" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="E3" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
       <c r="R3" s="23" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="69" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="69" t="s">
         <v>196</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="69" t="s">
         <v>205</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="69" t="s">
         <v>214</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -6240,11 +5662,11 @@
       <c r="H4" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="69" t="s">
         <v>266</v>
       </c>
       <c r="J4" s="1"/>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="69" t="s">
         <v>244</v>
       </c>
       <c r="L4" s="1" t="s">
@@ -6258,19 +5680,19 @@
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>284</v>
+        <v>306</v>
+      </c>
+      <c r="R4" s="69" t="s">
+        <v>288</v>
+      </c>
+      <c r="S4" s="69" t="s">
+        <v>297</v>
+      </c>
+      <c r="T4" s="69" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6281,7 +5703,7 @@
         <v>197</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>215</v>
@@ -6313,19 +5735,19 @@
       </c>
       <c r="O5" s="36"/>
       <c r="P5" s="36" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q5" s="36" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R5" s="36" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="S5" s="36" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T5" s="30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6368,19 +5790,19 @@
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q6" s="36" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S6" s="36" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6415,24 +5837,24 @@
       <c r="N7" s="34"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="R7" s="38" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>533</v>
+        <v>417</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>202</v>
@@ -6460,12 +5882,12 @@
       <c r="N8" s="34"/>
       <c r="O8" s="2"/>
       <c r="P8" s="38" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T8" s="2"/>
     </row>
@@ -6496,7 +5918,7 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="38" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="T9" s="2"/>
     </row>
@@ -6542,7 +5964,7 @@
         <v>243</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>567</v>
+        <v>451</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -6563,13 +5985,13 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="28" t="s">
-        <v>532</v>
+        <v>416</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>540</v>
+        <v>424</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>568</v>
+        <v>452</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -6590,10 +6012,10 @@
       <c r="E13" s="2"/>
       <c r="F13" s="13"/>
       <c r="H13" s="2" t="s">
-        <v>541</v>
+        <v>425</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>569</v>
+        <v>453</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -6615,10 +6037,10 @@
       <c r="F14" s="2"/>
       <c r="G14" s="28"/>
       <c r="H14" s="2" t="s">
-        <v>542</v>
+        <v>426</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>570</v>
+        <v>454</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -6788,12 +6210,12 @@
       <c r="I25" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="J25" s="74" t="s">
+      <c r="J25" s="63" t="s">
         <v>209</v>
       </c>
-      <c r="K25" s="74"/>
+      <c r="K25" s="63"/>
       <c r="N25" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
@@ -6952,7 +6374,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H33" s="39" t="s">
         <v>227</v>
@@ -7019,7 +6441,7 @@
         <v>219</v>
       </c>
       <c r="H35" s="39" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I35" s="15">
         <v>9</v>
@@ -7267,42 +6689,42 @@
     </row>
     <row r="49" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E49" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="50" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="51" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E51" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="53" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E53" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="54" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E54" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="56" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E56" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="57" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E57" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="58" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E58" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -7333,19 +6755,19 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B3" s="52" t="s">
-        <v>534</v>
+      <c r="B3" s="47" t="s">
+        <v>418</v>
       </c>
       <c r="C3" s="23"/>
     </row>
     <row r="4" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="53" t="s">
-        <v>535</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>536</v>
-      </c>
-      <c r="G4" s="52" t="s">
+      <c r="B4" s="48" t="s">
+        <v>419</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>420</v>
+      </c>
+      <c r="G4" s="47" t="s">
         <v>196</v>
       </c>
       <c r="H4" s="23"/>
@@ -7357,18 +6779,18 @@
         <v>1</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="G5" s="53" t="s">
+        <v>311</v>
+      </c>
+      <c r="G5" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="H5" s="54" t="s">
+      <c r="H5" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="I5" s="54" t="s">
+      <c r="I5" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="J5" s="54" t="s">
+      <c r="J5" s="49" t="s">
         <v>202</v>
       </c>
     </row>
@@ -7377,7 +6799,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="G6" s="21">
         <v>1</v>
@@ -7389,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>357</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
@@ -7397,7 +6819,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G7" s="21">
         <v>2</v>
@@ -7409,7 +6831,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
@@ -7417,7 +6839,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="G8" s="21">
         <v>3</v>
@@ -7429,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>363</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
@@ -7437,7 +6859,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="G9" s="21">
         <v>4</v>
@@ -7449,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>366</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
@@ -7457,7 +6879,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="G10" s="21">
         <v>5</v>
@@ -7469,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>368</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
@@ -7477,10 +6899,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="G11" s="21">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>129</v>
@@ -7489,7 +6911,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>370</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
@@ -7503,7 +6925,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
@@ -7517,11 +6939,11 @@
         <v>1</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="47" t="s">
         <v>189</v>
       </c>
       <c r="C14" s="23"/>
@@ -7537,21 +6959,21 @@
         <v>1</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="48" t="s">
         <v>190</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="C15" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="D15" s="55" t="s">
+      <c r="D15" s="50" t="s">
         <v>217</v>
       </c>
-      <c r="E15" s="55" t="s">
-        <v>533</v>
+      <c r="E15" s="50" t="s">
+        <v>417</v>
       </c>
       <c r="G15" s="21">
         <v>10</v>
@@ -7563,7 +6985,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
@@ -7571,7 +6993,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D16" s="21">
         <v>1</v>
@@ -7583,7 +7005,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="D17" s="21">
         <v>1</v>
@@ -7591,7 +7013,7 @@
       <c r="E17" s="21">
         <v>1</v>
       </c>
-      <c r="G17" s="52" t="s">
+      <c r="G17" s="47" t="s">
         <v>221</v>
       </c>
       <c r="H17" s="23"/>
@@ -7601,7 +7023,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="D18" s="21">
         <v>1</v>
@@ -7609,13 +7031,13 @@
       <c r="E18" s="21">
         <v>2</v>
       </c>
-      <c r="G18" s="53" t="s">
+      <c r="G18" s="48" t="s">
         <v>222</v>
       </c>
-      <c r="H18" s="53" t="s">
-        <v>538</v>
-      </c>
-      <c r="I18" s="54" t="s">
+      <c r="H18" s="48" t="s">
+        <v>422</v>
+      </c>
+      <c r="I18" s="49" t="s">
         <v>224</v>
       </c>
     </row>
@@ -7624,69 +7046,69 @@
         <v>4</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="D19" s="21">
         <v>2</v>
       </c>
       <c r="E19" s="21"/>
-      <c r="G19" s="79" t="s">
-        <v>539</v>
-      </c>
-      <c r="H19" s="79"/>
-      <c r="I19" s="79"/>
+      <c r="G19" s="68" t="s">
+        <v>423</v>
+      </c>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="21">
         <v>5</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="D20" s="21">
         <v>2</v>
       </c>
       <c r="E20" s="21"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="66"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="21">
         <v>6</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="D21" s="21">
         <v>3</v>
       </c>
       <c r="E21" s="21"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="66"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="21">
         <v>7</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="D22" s="21">
         <v>3</v>
       </c>
       <c r="E22" s="21"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="66"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="21">
         <v>8</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="D23" s="21">
         <v>3</v>
@@ -7698,7 +7120,7 @@
         <v>9</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="D24" s="21">
         <v>3</v>
@@ -7710,7 +7132,7 @@
         <v>10</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="D25" s="21">
         <v>3</v>
@@ -7718,7 +7140,7 @@
       <c r="E25" s="21">
         <v>8</v>
       </c>
-      <c r="G25" s="52" t="s">
+      <c r="G25" s="47" t="s">
         <v>205</v>
       </c>
       <c r="H25" s="23"/>
@@ -7732,28 +7154,28 @@
         <v>11</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="D26" s="21">
         <v>4</v>
       </c>
       <c r="E26" s="21"/>
-      <c r="G26" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="H26" s="57" t="s">
+      <c r="G26" s="48" t="s">
+        <v>280</v>
+      </c>
+      <c r="H26" s="52" t="s">
         <v>200</v>
       </c>
-      <c r="I26" s="57" t="s">
+      <c r="I26" s="52" t="s">
         <v>212</v>
       </c>
-      <c r="J26" s="57" t="s">
+      <c r="J26" s="52" t="s">
         <v>218</v>
       </c>
-      <c r="K26" s="54" t="s">
+      <c r="K26" s="49" t="s">
         <v>213</v>
       </c>
-      <c r="L26" s="54" t="s">
+      <c r="L26" s="49" t="s">
         <v>228</v>
       </c>
     </row>
@@ -7762,14 +7184,14 @@
         <v>12</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="D27" s="21">
         <v>1</v>
       </c>
       <c r="E27" s="21"/>
       <c r="G27" s="23" t="s">
-        <v>506</v>
+        <v>414</v>
       </c>
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
@@ -7782,19 +7204,19 @@
         <v>13</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="D28" s="21">
         <v>4</v>
       </c>
       <c r="E28" s="21"/>
       <c r="G28" s="23"/>
-      <c r="H28" s="77" t="s">
-        <v>537</v>
-      </c>
-      <c r="I28" s="77"/>
-      <c r="J28" s="77"/>
-      <c r="K28" s="77"/>
+      <c r="H28" s="66" t="s">
+        <v>421</v>
+      </c>
+      <c r="I28" s="66"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="66"/>
       <c r="L28" s="23"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
@@ -7802,17 +7224,17 @@
         <v>14</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>361</v>
+        <v>334</v>
       </c>
       <c r="D29" s="21">
         <v>5</v>
       </c>
       <c r="E29" s="21"/>
       <c r="G29" s="23"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="77"/>
-      <c r="K29" s="77"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="66"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="66"/>
       <c r="L29" s="23"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
@@ -7820,17 +7242,17 @@
         <v>15</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>364</v>
+        <v>337</v>
       </c>
       <c r="D30" s="21">
         <v>5</v>
       </c>
       <c r="E30" s="21"/>
       <c r="G30" s="23"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="77"/>
-      <c r="J30" s="77"/>
-      <c r="K30" s="77"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
       <c r="L30" s="23"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
@@ -7838,17 +7260,17 @@
         <v>16</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>367</v>
+        <v>340</v>
       </c>
       <c r="D31" s="21">
         <v>6</v>
       </c>
       <c r="E31" s="21"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="77"/>
-      <c r="J31" s="77"/>
-      <c r="K31" s="77"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
       <c r="L31" s="23"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
@@ -7856,83 +7278,83 @@
         <v>17</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>369</v>
+        <v>342</v>
       </c>
       <c r="D32" s="21">
         <v>6</v>
       </c>
       <c r="E32" s="21"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77"/>
-      <c r="J32" s="77"/>
-      <c r="K32" s="77"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="66"/>
+      <c r="J32" s="66"/>
+      <c r="K32" s="66"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="21">
         <v>18</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="D33" s="21">
         <v>5</v>
       </c>
       <c r="E33" s="21"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="77"/>
-      <c r="J33" s="77"/>
-      <c r="K33" s="77"/>
+      <c r="H33" s="66"/>
+      <c r="I33" s="66"/>
+      <c r="J33" s="66"/>
+      <c r="K33" s="66"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="21">
         <v>19</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="D34" s="21">
         <v>7</v>
       </c>
-      <c r="E34" s="21">
-        <v>20</v>
-      </c>
-      <c r="H34" s="77"/>
-      <c r="I34" s="77"/>
-      <c r="J34" s="77"/>
-      <c r="K34" s="77"/>
+      <c r="E34" s="21"/>
+      <c r="H34" s="66"/>
+      <c r="I34" s="66"/>
+      <c r="J34" s="66"/>
+      <c r="K34" s="66"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="21">
         <v>20</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="D35" s="21">
         <v>7</v>
       </c>
-      <c r="E35" s="21"/>
+      <c r="E35" s="21">
+        <v>19</v>
+      </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="D37" s="66" t="s">
-        <v>543</v>
+      <c r="D37" s="54" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>544</v>
+        <v>428</v>
       </c>
     </row>
     <row r="39" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B39" s="52" t="s">
+      <c r="B39" s="47" t="s">
         <v>244</v>
       </c>
       <c r="D39" t="s">
-        <v>545</v>
+        <v>429</v>
       </c>
     </row>
     <row r="40" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B40" s="53" t="s">
+      <c r="B40" s="48" t="s">
         <v>245</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -7944,7 +7366,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>548</v>
+        <v>432</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.3">
@@ -7952,7 +7374,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>546</v>
+        <v>430</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.3">
@@ -7960,7 +7382,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>547</v>
+        <v>431</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.3">
@@ -7968,7 +7390,7 @@
         <v>4</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>549</v>
+        <v>433</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.3">
@@ -7976,7 +7398,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>550</v>
+        <v>434</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">
@@ -7984,7 +7406,7 @@
         <v>6</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>551</v>
+        <v>435</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.3">
@@ -7992,7 +7414,7 @@
         <v>7</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>598</v>
+        <v>479</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.3">
@@ -8000,16 +7422,16 @@
         <v>8</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B51" s="52" t="s">
+      <c r="B51" s="47" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B52" s="53" t="s">
+      <c r="B52" s="48" t="s">
         <v>237</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -8031,14 +7453,14 @@
         <v>243</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="J52" s="78" t="s">
-        <v>541</v>
-      </c>
-      <c r="K52" s="78"/>
+        <v>424</v>
+      </c>
+      <c r="J52" s="67" t="s">
+        <v>425</v>
+      </c>
+      <c r="K52" s="67"/>
       <c r="L52" s="2" t="s">
-        <v>542</v>
+        <v>426</v>
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.3">
@@ -8046,26 +7468,26 @@
         <v>1</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>557</v>
+        <v>441</v>
       </c>
       <c r="D53" s="21">
         <v>123456789</v>
       </c>
-      <c r="E53" s="56" t="s">
-        <v>418</v>
+      <c r="E53" s="51" t="s">
+        <v>372</v>
       </c>
       <c r="F53" s="21"/>
       <c r="G53" s="21"/>
       <c r="H53" s="21" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="I53" s="21" t="s">
-        <v>419</v>
-      </c>
-      <c r="J53" s="68" t="s">
-        <v>552</v>
-      </c>
-      <c r="K53" s="67"/>
+        <v>373</v>
+      </c>
+      <c r="J53" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="K53" s="55"/>
       <c r="L53" s="3">
         <v>1</v>
       </c>
@@ -8075,28 +7497,28 @@
         <v>2</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>558</v>
+        <v>442</v>
       </c>
       <c r="D54" s="21">
         <v>123456789</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>422</v>
+        <v>375</v>
       </c>
       <c r="F54" s="21"/>
       <c r="G54" s="21" t="s">
-        <v>554</v>
+        <v>438</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>391</v>
+        <v>354</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>423</v>
-      </c>
-      <c r="J54" s="68" t="s">
-        <v>552</v>
-      </c>
-      <c r="K54" s="67"/>
+        <v>376</v>
+      </c>
+      <c r="J54" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="K54" s="55"/>
       <c r="L54" s="3">
         <v>1</v>
       </c>
@@ -8106,28 +7528,28 @@
         <v>3</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>559</v>
+        <v>443</v>
       </c>
       <c r="D55" s="21">
         <v>123456789</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>425</v>
+        <v>377</v>
       </c>
       <c r="F55" s="21"/>
       <c r="G55" s="21" t="s">
-        <v>556</v>
+        <v>440</v>
       </c>
       <c r="H55" s="21" t="s">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>426</v>
-      </c>
-      <c r="J55" s="68" t="s">
-        <v>552</v>
-      </c>
-      <c r="K55" s="67"/>
+        <v>378</v>
+      </c>
+      <c r="J55" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="K55" s="55"/>
       <c r="L55" s="3">
         <v>1</v>
       </c>
@@ -8137,28 +7559,28 @@
         <v>4</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>560</v>
+        <v>444</v>
       </c>
       <c r="D56" s="21">
         <v>123456789</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>428</v>
+        <v>379</v>
       </c>
       <c r="F56" s="21"/>
       <c r="G56" s="21" t="s">
-        <v>555</v>
+        <v>439</v>
       </c>
       <c r="H56" s="21" t="s">
-        <v>395</v>
+        <v>358</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>429</v>
-      </c>
-      <c r="J56" s="68" t="s">
-        <v>552</v>
-      </c>
-      <c r="K56" s="67"/>
+        <v>380</v>
+      </c>
+      <c r="J56" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="K56" s="55"/>
       <c r="L56" s="3">
         <v>1</v>
       </c>
@@ -8168,28 +7590,28 @@
         <v>5</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>561</v>
+        <v>445</v>
       </c>
       <c r="D57" s="21">
         <v>123456789</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>431</v>
+        <v>381</v>
       </c>
       <c r="F57" s="21" t="s">
-        <v>553</v>
+        <v>437</v>
       </c>
       <c r="G57" s="21"/>
       <c r="H57" s="21" t="s">
-        <v>397</v>
+        <v>360</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>432</v>
-      </c>
-      <c r="J57" s="68" t="s">
-        <v>552</v>
-      </c>
-      <c r="K57" s="67"/>
+        <v>382</v>
+      </c>
+      <c r="J57" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="K57" s="55"/>
       <c r="L57" s="3">
         <v>1</v>
       </c>
@@ -8199,26 +7621,26 @@
         <v>6</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>562</v>
+        <v>446</v>
       </c>
       <c r="D58" s="21">
         <v>123456789</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>434</v>
+        <v>383</v>
       </c>
       <c r="F58" s="21"/>
       <c r="G58" s="21"/>
       <c r="H58" s="21" t="s">
-        <v>398</v>
+        <v>361</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>435</v>
-      </c>
-      <c r="J58" s="68" t="s">
-        <v>552</v>
-      </c>
-      <c r="K58" s="67"/>
+        <v>384</v>
+      </c>
+      <c r="J58" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="K58" s="55"/>
       <c r="L58" s="3">
         <v>1</v>
       </c>
@@ -8228,26 +7650,26 @@
         <v>7</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>563</v>
+        <v>447</v>
       </c>
       <c r="D59" s="21">
         <v>123456789</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>437</v>
+        <v>385</v>
       </c>
       <c r="F59" s="21"/>
       <c r="G59" s="21"/>
       <c r="H59" s="21" t="s">
-        <v>399</v>
+        <v>362</v>
       </c>
       <c r="I59" s="21" t="s">
-        <v>438</v>
-      </c>
-      <c r="J59" s="68" t="s">
-        <v>552</v>
-      </c>
-      <c r="K59" s="67"/>
+        <v>386</v>
+      </c>
+      <c r="J59" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="K59" s="55"/>
       <c r="L59" s="3">
         <v>1</v>
       </c>
@@ -8257,26 +7679,26 @@
         <v>8</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>564</v>
+        <v>448</v>
       </c>
       <c r="D60" s="21">
         <v>123456789</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>440</v>
+        <v>387</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
       <c r="H60" s="21" t="s">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="I60" s="21" t="s">
-        <v>441</v>
-      </c>
-      <c r="J60" s="68" t="s">
-        <v>552</v>
-      </c>
-      <c r="K60" s="67"/>
+        <v>388</v>
+      </c>
+      <c r="J60" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="K60" s="55"/>
       <c r="L60" s="3">
         <v>1</v>
       </c>
@@ -8286,26 +7708,26 @@
         <v>9</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>565</v>
+        <v>449</v>
       </c>
       <c r="D61" s="21">
         <v>123456789</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>443</v>
+        <v>389</v>
       </c>
       <c r="F61" s="21"/>
       <c r="G61" s="21"/>
       <c r="H61" s="21" t="s">
-        <v>401</v>
+        <v>364</v>
       </c>
       <c r="I61" s="21" t="s">
-        <v>444</v>
-      </c>
-      <c r="J61" s="68" t="s">
-        <v>552</v>
-      </c>
-      <c r="K61" s="67"/>
+        <v>390</v>
+      </c>
+      <c r="J61" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="K61" s="55"/>
       <c r="L61" s="3">
         <v>1</v>
       </c>
@@ -8315,26 +7737,26 @@
         <v>10</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>566</v>
+        <v>450</v>
       </c>
       <c r="D62" s="21">
         <v>123456789</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>446</v>
+        <v>391</v>
       </c>
       <c r="F62" s="21"/>
       <c r="G62" s="21"/>
       <c r="H62" s="21" t="s">
-        <v>402</v>
+        <v>365</v>
       </c>
       <c r="I62" s="21" t="s">
-        <v>447</v>
-      </c>
-      <c r="J62" s="68" t="s">
-        <v>552</v>
-      </c>
-      <c r="K62" s="67"/>
+        <v>392</v>
+      </c>
+      <c r="J62" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="K62" s="55"/>
       <c r="L62" s="3">
         <v>1</v>
       </c>
@@ -8343,12 +7765,12 @@
       <c r="L63" s="4"/>
     </row>
     <row r="65" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B65" s="52" t="s">
+      <c r="B65" s="47" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="66" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B66" s="53" t="s">
+      <c r="B66" s="48" t="s">
         <v>267</v>
       </c>
       <c r="C66" s="2" t="s">
@@ -8367,17 +7789,17 @@
         <v>272</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="I66" s="78" t="s">
-        <v>568</v>
-      </c>
-      <c r="J66" s="78"/>
+        <v>451</v>
+      </c>
+      <c r="I66" s="67" t="s">
+        <v>452</v>
+      </c>
+      <c r="J66" s="67"/>
       <c r="K66" s="2" t="s">
-        <v>569</v>
+        <v>453</v>
       </c>
       <c r="L66" s="38" t="s">
-        <v>570</v>
+        <v>454</v>
       </c>
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.3">
@@ -8385,21 +7807,21 @@
         <v>1</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="D67" s="21">
         <v>123456789</v>
       </c>
-      <c r="E67" s="56" t="s">
-        <v>458</v>
+      <c r="E67" s="51" t="s">
+        <v>494</v>
       </c>
       <c r="F67" s="21"/>
       <c r="G67" s="21"/>
       <c r="H67" s="21" t="s">
-        <v>459</v>
-      </c>
-      <c r="I67" s="69" t="s">
-        <v>420</v>
+        <v>394</v>
+      </c>
+      <c r="I67" s="57" t="s">
+        <v>374</v>
       </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3">
@@ -8414,23 +7836,23 @@
         <v>2</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>460</v>
+        <v>395</v>
       </c>
       <c r="D68" s="21">
         <v>123456789</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>461</v>
+        <v>495</v>
       </c>
       <c r="F68" s="21"/>
       <c r="G68" s="21" t="s">
-        <v>554</v>
+        <v>438</v>
       </c>
       <c r="H68" s="21" t="s">
-        <v>462</v>
-      </c>
-      <c r="I68" s="60" t="s">
-        <v>420</v>
+        <v>396</v>
+      </c>
+      <c r="I68" s="53" t="s">
+        <v>374</v>
       </c>
       <c r="J68" s="3"/>
       <c r="K68" s="3">
@@ -8445,23 +7867,23 @@
         <v>3</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>463</v>
+        <v>397</v>
       </c>
       <c r="D69" s="21">
         <v>123456789</v>
       </c>
-      <c r="E69" s="56" t="s">
-        <v>464</v>
+      <c r="E69" s="51" t="s">
+        <v>496</v>
       </c>
       <c r="F69" s="21"/>
       <c r="G69" s="21" t="s">
-        <v>556</v>
+        <v>492</v>
       </c>
       <c r="H69" s="21" t="s">
-        <v>465</v>
-      </c>
-      <c r="I69" s="60" t="s">
-        <v>420</v>
+        <v>398</v>
+      </c>
+      <c r="I69" s="53" t="s">
+        <v>374</v>
       </c>
       <c r="J69" s="3"/>
       <c r="K69" s="3">
@@ -8476,23 +7898,23 @@
         <v>4</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>466</v>
+        <v>399</v>
       </c>
       <c r="D70" s="21">
         <v>123456789</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="F70" s="21"/>
       <c r="G70" s="21" t="s">
-        <v>555</v>
+        <v>493</v>
       </c>
       <c r="H70" s="21" t="s">
-        <v>468</v>
-      </c>
-      <c r="I70" s="60" t="s">
-        <v>420</v>
+        <v>400</v>
+      </c>
+      <c r="I70" s="53" t="s">
+        <v>374</v>
       </c>
       <c r="J70" s="3"/>
       <c r="K70" s="3">
@@ -8507,23 +7929,23 @@
         <v>5</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>469</v>
+        <v>401</v>
       </c>
       <c r="D71" s="21">
         <v>123456789</v>
       </c>
-      <c r="E71" s="56" t="s">
-        <v>470</v>
+      <c r="E71" s="51" t="s">
+        <v>402</v>
       </c>
       <c r="F71" s="21" t="s">
-        <v>553</v>
+        <v>437</v>
       </c>
       <c r="G71" s="21"/>
       <c r="H71" s="21" t="s">
-        <v>471</v>
-      </c>
-      <c r="I71" s="60" t="s">
-        <v>420</v>
+        <v>403</v>
+      </c>
+      <c r="I71" s="53" t="s">
+        <v>374</v>
       </c>
       <c r="J71" s="3"/>
       <c r="K71" s="3">
@@ -8538,21 +7960,21 @@
         <v>6</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>472</v>
+        <v>404</v>
       </c>
       <c r="D72" s="21">
         <v>123456789</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="F72" s="21"/>
       <c r="G72" s="21"/>
       <c r="H72" s="21" t="s">
-        <v>474</v>
-      </c>
-      <c r="I72" s="60" t="s">
-        <v>420</v>
+        <v>405</v>
+      </c>
+      <c r="I72" s="53" t="s">
+        <v>374</v>
       </c>
       <c r="J72" s="3"/>
       <c r="K72" s="3">
@@ -8567,21 +7989,21 @@
         <v>7</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>475</v>
+        <v>406</v>
       </c>
       <c r="D73" s="21">
         <v>123456789</v>
       </c>
-      <c r="E73" s="56" t="s">
-        <v>476</v>
+      <c r="E73" s="51" t="s">
+        <v>499</v>
       </c>
       <c r="F73" s="21"/>
       <c r="G73" s="21"/>
       <c r="H73" s="21" t="s">
-        <v>477</v>
-      </c>
-      <c r="I73" s="60" t="s">
-        <v>420</v>
+        <v>407</v>
+      </c>
+      <c r="I73" s="53" t="s">
+        <v>374</v>
       </c>
       <c r="J73" s="3"/>
       <c r="K73" s="3">
@@ -8596,21 +8018,21 @@
         <v>8</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>478</v>
+        <v>408</v>
       </c>
       <c r="D74" s="21">
         <v>123456789</v>
       </c>
       <c r="E74" s="21" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="F74" s="21"/>
       <c r="G74" s="21"/>
       <c r="H74" s="21" t="s">
-        <v>480</v>
-      </c>
-      <c r="I74" s="60" t="s">
-        <v>420</v>
+        <v>409</v>
+      </c>
+      <c r="I74" s="53" t="s">
+        <v>374</v>
       </c>
       <c r="J74" s="3"/>
       <c r="K74" s="3">
@@ -8625,21 +8047,21 @@
         <v>9</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>481</v>
+        <v>410</v>
       </c>
       <c r="D75" s="21">
         <v>123456789</v>
       </c>
-      <c r="E75" s="56" t="s">
-        <v>482</v>
+      <c r="E75" s="51" t="s">
+        <v>501</v>
       </c>
       <c r="F75" s="21"/>
       <c r="G75" s="21"/>
       <c r="H75" s="21" t="s">
-        <v>483</v>
-      </c>
-      <c r="I75" s="60" t="s">
-        <v>420</v>
+        <v>411</v>
+      </c>
+      <c r="I75" s="53" t="s">
+        <v>374</v>
       </c>
       <c r="J75" s="3"/>
       <c r="K75" s="3">
@@ -8654,21 +8076,21 @@
         <v>10</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>484</v>
+        <v>412</v>
       </c>
       <c r="D76" s="21">
         <v>123456789</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="F76" s="21"/>
       <c r="G76" s="21"/>
       <c r="H76" s="21" t="s">
-        <v>486</v>
-      </c>
-      <c r="I76" s="60" t="s">
-        <v>420</v>
+        <v>413</v>
+      </c>
+      <c r="I76" s="53" t="s">
+        <v>374</v>
       </c>
       <c r="J76" s="3"/>
       <c r="K76" s="3">
@@ -8683,21 +8105,21 @@
         <v>11</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>571</v>
+        <v>455</v>
       </c>
       <c r="D77" s="21">
         <v>123456789</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>574</v>
+        <v>503</v>
       </c>
       <c r="F77" s="21"/>
       <c r="G77" s="21"/>
       <c r="H77" s="21" t="s">
-        <v>577</v>
-      </c>
-      <c r="I77" s="60" t="s">
-        <v>420</v>
+        <v>458</v>
+      </c>
+      <c r="I77" s="53" t="s">
+        <v>374</v>
       </c>
       <c r="J77" s="3"/>
       <c r="K77" s="3">
@@ -8712,21 +8134,21 @@
         <v>12</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>572</v>
+        <v>456</v>
       </c>
       <c r="D78" s="21">
         <v>123456789</v>
       </c>
-      <c r="E78" s="56" t="s">
-        <v>575</v>
+      <c r="E78" s="51" t="s">
+        <v>504</v>
       </c>
       <c r="F78" s="21"/>
       <c r="G78" s="21"/>
       <c r="H78" s="21" t="s">
-        <v>578</v>
-      </c>
-      <c r="I78" s="60" t="s">
-        <v>420</v>
+        <v>459</v>
+      </c>
+      <c r="I78" s="53" t="s">
+        <v>374</v>
       </c>
       <c r="J78" s="3"/>
       <c r="K78" s="3">
@@ -8741,21 +8163,21 @@
         <v>13</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>573</v>
+        <v>457</v>
       </c>
       <c r="D79" s="21">
         <v>123456789</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>576</v>
+        <v>505</v>
       </c>
       <c r="F79" s="21"/>
       <c r="G79" s="21"/>
       <c r="H79" s="21" t="s">
-        <v>579</v>
-      </c>
-      <c r="I79" s="60" t="s">
-        <v>420</v>
+        <v>460</v>
+      </c>
+      <c r="I79" s="53" t="s">
+        <v>374</v>
       </c>
       <c r="J79" s="3"/>
       <c r="K79" s="3">
@@ -8766,17 +8188,17 @@
       </c>
     </row>
     <row r="82" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B82" s="52" t="s">
+      <c r="B82" s="47" t="s">
         <v>261</v>
       </c>
       <c r="C82" s="23"/>
     </row>
     <row r="83" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B83" s="53" t="s">
-        <v>580</v>
-      </c>
-      <c r="C83" s="54" t="s">
-        <v>581</v>
+      <c r="B83" s="48" t="s">
+        <v>461</v>
+      </c>
+      <c r="C83" s="49" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
@@ -8784,7 +8206,7 @@
         <v>1</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>356</v>
+        <v>329</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
@@ -8792,7 +8214,7 @@
         <v>2</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>359</v>
+        <v>332</v>
       </c>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
@@ -8800,7 +8222,7 @@
         <v>3</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>362</v>
+        <v>335</v>
       </c>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
@@ -8808,19 +8230,19 @@
         <v>4</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>365</v>
+        <v>338</v>
       </c>
     </row>
     <row r="88" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B88" s="54"/>
+      <c r="B88" s="49"/>
     </row>
     <row r="89" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B89" s="52" t="s">
+      <c r="B89" s="47" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="90" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B90" s="53" t="s">
+      <c r="B90" s="48" t="s">
         <v>230</v>
       </c>
       <c r="C90" s="21" t="s">
@@ -8842,7 +8264,7 @@
         <v>264</v>
       </c>
       <c r="I90" s="28" t="s">
-        <v>532</v>
+        <v>416</v>
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
@@ -8850,19 +8272,19 @@
         <v>1</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>582</v>
+        <v>463</v>
       </c>
       <c r="D91" s="21">
         <v>258369741</v>
       </c>
       <c r="E91" s="21" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="F91" s="21">
         <v>1</v>
       </c>
-      <c r="G91" s="56" t="s">
-        <v>388</v>
+      <c r="G91" s="51" t="s">
+        <v>351</v>
       </c>
       <c r="H91" s="21">
         <v>1</v>
@@ -8876,19 +8298,19 @@
         <v>2</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>583</v>
+        <v>464</v>
       </c>
       <c r="D92" s="21">
         <v>258369741</v>
       </c>
       <c r="E92" s="21" t="s">
-        <v>391</v>
+        <v>354</v>
       </c>
       <c r="F92" s="21">
         <v>2</v>
       </c>
-      <c r="G92" s="56" t="s">
-        <v>390</v>
+      <c r="G92" s="51" t="s">
+        <v>353</v>
       </c>
       <c r="H92" s="21">
         <v>1</v>
@@ -8902,19 +8324,19 @@
         <v>3</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>584</v>
+        <v>465</v>
       </c>
       <c r="D93" s="21">
         <v>258369741</v>
       </c>
       <c r="E93" s="21" t="s">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="F93" s="21">
         <v>3</v>
       </c>
-      <c r="G93" s="56" t="s">
-        <v>392</v>
+      <c r="G93" s="51" t="s">
+        <v>355</v>
       </c>
       <c r="H93" s="21">
         <v>2</v>
@@ -8928,19 +8350,19 @@
         <v>4</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>585</v>
+        <v>466</v>
       </c>
       <c r="D94" s="21">
         <v>258369741</v>
       </c>
       <c r="E94" s="21" t="s">
-        <v>395</v>
+        <v>358</v>
       </c>
       <c r="F94" s="21">
         <v>4</v>
       </c>
-      <c r="G94" s="56" t="s">
-        <v>394</v>
+      <c r="G94" s="51" t="s">
+        <v>357</v>
       </c>
       <c r="H94" s="21">
         <v>2</v>
@@ -8954,19 +8376,19 @@
         <v>5</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>586</v>
+        <v>467</v>
       </c>
       <c r="D95" s="21">
         <v>258369741</v>
       </c>
       <c r="E95" s="21" t="s">
-        <v>397</v>
+        <v>360</v>
       </c>
       <c r="F95" s="21">
         <v>5</v>
       </c>
-      <c r="G95" s="56" t="s">
-        <v>396</v>
+      <c r="G95" s="51" t="s">
+        <v>359</v>
       </c>
       <c r="H95" s="21">
         <v>3</v>
@@ -8980,19 +8402,19 @@
         <v>6</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>587</v>
+        <v>468</v>
       </c>
       <c r="D96" s="21">
         <v>258369741</v>
       </c>
       <c r="E96" s="21" t="s">
-        <v>398</v>
+        <v>361</v>
       </c>
       <c r="F96" s="21">
         <v>6</v>
       </c>
-      <c r="G96" s="56" t="s">
-        <v>390</v>
+      <c r="G96" s="51" t="s">
+        <v>353</v>
       </c>
       <c r="H96" s="21">
         <v>3</v>
@@ -9006,19 +8428,19 @@
         <v>7</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>588</v>
+        <v>469</v>
       </c>
       <c r="D97" s="21">
         <v>258369741</v>
       </c>
       <c r="E97" s="21" t="s">
-        <v>399</v>
+        <v>362</v>
       </c>
       <c r="F97" s="21">
         <v>7</v>
       </c>
-      <c r="G97" s="56" t="s">
-        <v>392</v>
+      <c r="G97" s="51" t="s">
+        <v>355</v>
       </c>
       <c r="H97" s="21">
         <v>4</v>
@@ -9032,19 +8454,19 @@
         <v>8</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>589</v>
+        <v>470</v>
       </c>
       <c r="D98" s="21">
         <v>258369741</v>
       </c>
       <c r="E98" s="21" t="s">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="F98" s="21">
         <v>8</v>
       </c>
-      <c r="G98" s="56" t="s">
-        <v>396</v>
+      <c r="G98" s="51" t="s">
+        <v>359</v>
       </c>
       <c r="H98" s="21">
         <v>4</v>
@@ -9058,19 +8480,19 @@
         <v>9</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>590</v>
+        <v>471</v>
       </c>
       <c r="D99" s="21">
         <v>258369741</v>
       </c>
       <c r="E99" s="21" t="s">
-        <v>401</v>
+        <v>364</v>
       </c>
       <c r="F99" s="21">
         <v>1</v>
       </c>
-      <c r="G99" s="56" t="s">
-        <v>396</v>
+      <c r="G99" s="51" t="s">
+        <v>359</v>
       </c>
       <c r="H99" s="21">
         <v>4</v>
@@ -9084,19 +8506,19 @@
         <v>10</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>591</v>
+        <v>472</v>
       </c>
       <c r="D100" s="21">
         <v>258369741</v>
       </c>
       <c r="E100" s="21" t="s">
-        <v>402</v>
+        <v>365</v>
       </c>
       <c r="F100" s="21">
         <v>2</v>
       </c>
-      <c r="G100" s="56" t="s">
-        <v>396</v>
+      <c r="G100" s="51" t="s">
+        <v>359</v>
       </c>
       <c r="H100" s="21">
         <v>4</v>
@@ -9107,25 +8529,25 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
-        <v>596</v>
-      </c>
-      <c r="B101" s="72">
+        <v>477</v>
+      </c>
+      <c r="B101" s="60">
         <v>11</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>592</v>
+        <v>473</v>
       </c>
       <c r="D101" s="21">
         <v>258369741</v>
       </c>
       <c r="E101" s="21" t="s">
-        <v>404</v>
+        <v>367</v>
       </c>
       <c r="F101" s="21">
         <v>9</v>
       </c>
-      <c r="G101" s="56" t="s">
-        <v>403</v>
+      <c r="G101" s="51" t="s">
+        <v>366</v>
       </c>
       <c r="H101" s="21">
         <v>3</v>
@@ -9136,25 +8558,25 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="23" t="s">
-        <v>596</v>
-      </c>
-      <c r="B102" s="72">
+        <v>477</v>
+      </c>
+      <c r="B102" s="60">
         <v>12</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>593</v>
+        <v>474</v>
       </c>
       <c r="D102" s="21">
         <v>258369741</v>
       </c>
       <c r="E102" s="21" t="s">
-        <v>406</v>
+        <v>369</v>
       </c>
       <c r="F102" s="21">
         <v>10</v>
       </c>
-      <c r="G102" s="56" t="s">
-        <v>405</v>
+      <c r="G102" s="51" t="s">
+        <v>368</v>
       </c>
       <c r="H102" s="21">
         <v>3</v>
@@ -9165,25 +8587,25 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="23" t="s">
-        <v>596</v>
-      </c>
-      <c r="B103" s="72">
+        <v>477</v>
+      </c>
+      <c r="B103" s="60">
         <v>13</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>594</v>
+        <v>475</v>
       </c>
       <c r="D103" s="21">
         <v>258369741</v>
       </c>
       <c r="E103" s="21" t="s">
-        <v>408</v>
+        <v>371</v>
       </c>
       <c r="F103" s="21">
         <v>5</v>
       </c>
-      <c r="G103" s="56" t="s">
-        <v>407</v>
+      <c r="G103" s="51" t="s">
+        <v>370</v>
       </c>
       <c r="H103" s="21">
         <v>1</v>
@@ -9193,69 +8615,69 @@
       </c>
     </row>
     <row r="107" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B107" s="52" t="s">
+      <c r="B107" s="47" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B108" s="48" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B108" s="53" t="s">
+      <c r="C108" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="D108" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="E108" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="E108" s="38" t="s">
-        <v>278</v>
-      </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B110" s="77" t="s">
-        <v>595</v>
-      </c>
-      <c r="C110" s="75"/>
-      <c r="D110" s="75"/>
-      <c r="E110" s="75"/>
+      <c r="B110" s="66" t="s">
+        <v>476</v>
+      </c>
+      <c r="C110" s="64"/>
+      <c r="D110" s="64"/>
+      <c r="E110" s="64"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B111" s="75"/>
-      <c r="C111" s="75"/>
-      <c r="D111" s="75"/>
-      <c r="E111" s="75"/>
+      <c r="B111" s="64"/>
+      <c r="C111" s="64"/>
+      <c r="D111" s="64"/>
+      <c r="E111" s="64"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B112" s="75"/>
-      <c r="C112" s="75"/>
-      <c r="D112" s="75"/>
-      <c r="E112" s="75"/>
+      <c r="B112" s="64"/>
+      <c r="C112" s="64"/>
+      <c r="D112" s="64"/>
+      <c r="E112" s="64"/>
     </row>
     <row r="113" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="75"/>
-      <c r="C113" s="75"/>
-      <c r="D113" s="75"/>
-      <c r="E113" s="75"/>
+      <c r="B113" s="64"/>
+      <c r="C113" s="64"/>
+      <c r="D113" s="64"/>
+      <c r="E113" s="64"/>
       <c r="F113" s="23"/>
       <c r="G113" s="23"/>
       <c r="H113" s="23"/>
       <c r="I113" s="23"/>
     </row>
     <row r="114" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B114" s="75"/>
-      <c r="C114" s="75"/>
-      <c r="D114" s="75"/>
-      <c r="E114" s="75"/>
-      <c r="F114" s="70"/>
-      <c r="G114" s="70"/>
-      <c r="H114" s="71"/>
-      <c r="I114" s="71"/>
+      <c r="B114" s="64"/>
+      <c r="C114" s="64"/>
+      <c r="D114" s="64"/>
+      <c r="E114" s="64"/>
+      <c r="F114" s="58"/>
+      <c r="G114" s="58"/>
+      <c r="H114" s="59"/>
+      <c r="I114" s="59"/>
     </row>
     <row r="115" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B115" s="75"/>
-      <c r="C115" s="75"/>
-      <c r="D115" s="75"/>
-      <c r="E115" s="75"/>
+      <c r="B115" s="64"/>
+      <c r="C115" s="64"/>
+      <c r="D115" s="64"/>
+      <c r="E115" s="64"/>
       <c r="G115" s="23"/>
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.3">
@@ -9267,43 +8689,43 @@
       <c r="G117" s="23"/>
     </row>
     <row r="118" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B118" s="52" t="s">
-        <v>307</v>
+      <c r="B118" s="47" t="s">
+        <v>306</v>
       </c>
       <c r="C118" s="23"/>
       <c r="D118" s="23"/>
       <c r="G118" s="23"/>
     </row>
     <row r="119" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B119" s="53" t="s">
-        <v>280</v>
-      </c>
-      <c r="C119" s="53" t="s">
+      <c r="B119" s="48" t="s">
+        <v>279</v>
+      </c>
+      <c r="C119" s="48" t="s">
+        <v>281</v>
+      </c>
+      <c r="D119" s="49" t="s">
         <v>282</v>
       </c>
-      <c r="D119" s="54" t="s">
-        <v>283</v>
-      </c>
       <c r="G119" s="23"/>
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B120" s="76" t="s">
-        <v>517</v>
-      </c>
-      <c r="C120" s="76"/>
-      <c r="D120" s="76"/>
+      <c r="B120" s="65" t="s">
+        <v>415</v>
+      </c>
+      <c r="C120" s="65"/>
+      <c r="D120" s="65"/>
       <c r="G120" s="23"/>
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B121" s="76"/>
-      <c r="C121" s="76"/>
-      <c r="D121" s="76"/>
+      <c r="B121" s="65"/>
+      <c r="C121" s="65"/>
+      <c r="D121" s="65"/>
       <c r="G121" s="23"/>
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B122" s="76"/>
-      <c r="C122" s="76"/>
-      <c r="D122" s="76"/>
+      <c r="B122" s="65"/>
+      <c r="C122" s="65"/>
+      <c r="D122" s="65"/>
       <c r="G122" s="23"/>
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.3">
@@ -9676,18 +9098,18 @@
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B159" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B160" s="36" t="s">
+        <v>289</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="D160" s="38" t="s">
         <v>291</v>
-      </c>
-      <c r="D160" s="38" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.3">
@@ -9722,11 +9144,11 @@
       <c r="B165" s="21">
         <v>5</v>
       </c>
-      <c r="C165" s="56" t="s">
-        <v>597</v>
+      <c r="C165" s="51" t="s">
+        <v>478</v>
       </c>
       <c r="D165" s="21" t="s">
-        <v>553</v>
+        <v>437</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.3">
@@ -9734,8 +9156,8 @@
         <v>6</v>
       </c>
       <c r="C166" s="21"/>
-      <c r="D166" s="56" t="s">
-        <v>599</v>
+      <c r="D166" s="51" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.3">
@@ -9768,18 +9190,18 @@
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B173" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B174" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C174" s="2" t="s">
+      <c r="D174" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.3">
@@ -9787,7 +9209,7 @@
         <v>1</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>600</v>
+        <v>481</v>
       </c>
       <c r="D175" s="3">
         <v>12345</v>
@@ -9798,7 +9220,7 @@
         <v>2</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>601</v>
+        <v>482</v>
       </c>
       <c r="D176" s="3">
         <v>23456</v>
@@ -9809,7 +9231,7 @@
         <v>3</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>602</v>
+        <v>483</v>
       </c>
       <c r="D177" s="3">
         <v>34567</v>
@@ -9820,7 +9242,7 @@
         <v>4</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>603</v>
+        <v>484</v>
       </c>
       <c r="D178" s="3">
         <v>72727</v>
@@ -9831,7 +9253,7 @@
         <v>5</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>604</v>
+        <v>485</v>
       </c>
       <c r="D179" s="3">
         <v>28282</v>
@@ -9839,7 +9261,7 @@
     </row>
     <row r="182" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B182" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C182" s="23"/>
       <c r="D182" s="23"/>
@@ -9848,36 +9270,36 @@
     </row>
     <row r="183" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B183" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="C183" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="C183" s="36" t="s">
+      <c r="D183" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D183" s="2" t="s">
+      <c r="E183" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F183" s="38" t="s">
         <v>296</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F183" s="38" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="184" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B184" s="23" t="s">
-        <v>606</v>
+        <v>487</v>
       </c>
       <c r="C184" s="23" t="s">
-        <v>605</v>
+        <v>486</v>
       </c>
       <c r="D184" s="23" t="s">
-        <v>607</v>
+        <v>488</v>
       </c>
       <c r="E184" s="23" t="s">
-        <v>608</v>
+        <v>489</v>
       </c>
       <c r="F184" s="23" t="s">
-        <v>610</v>
+        <v>491</v>
       </c>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.3">
@@ -9956,7 +9378,7 @@
     <row r="192" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B192" s="23"/>
       <c r="C192" s="23" t="s">
-        <v>609</v>
+        <v>490</v>
       </c>
       <c r="D192" s="23"/>
       <c r="E192" s="23"/>
@@ -9987,7 +9409,7 @@
     <row r="195" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B195" s="23"/>
       <c r="C195" s="23" t="s">
-        <v>609</v>
+        <v>490</v>
       </c>
       <c r="D195" s="23"/>
       <c r="E195" s="23"/>
@@ -10007,17 +9429,17 @@
     <row r="197" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B197" s="4"/>
       <c r="C197" s="4" t="s">
-        <v>609</v>
+        <v>490</v>
       </c>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
       <c r="F197" s="4"/>
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B198" s="81">
+      <c r="B198" s="61">
         <v>3</v>
       </c>
-      <c r="C198" s="81">
+      <c r="C198" s="61">
         <v>1</v>
       </c>
       <c r="D198" s="4"/>
@@ -10025,10 +9447,10 @@
       <c r="F198" s="4"/>
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B199" s="81">
+      <c r="B199" s="61">
         <v>6</v>
       </c>
-      <c r="C199" s="81">
+      <c r="C199" s="61">
         <v>5</v>
       </c>
       <c r="D199" s="4"/>
@@ -10036,10 +9458,10 @@
       <c r="F199" s="4"/>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B200" s="81">
+      <c r="B200" s="61">
         <v>9</v>
       </c>
-      <c r="C200" s="81">
+      <c r="C200" s="61">
         <v>10</v>
       </c>
       <c r="D200" s="4"/>
@@ -10062,3576 +9484,8 @@
     <mergeCell ref="G19:I22"/>
     <mergeCell ref="J52:K52"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B3:AI135"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="14" width="28.6640625" customWidth="1"/>
-    <col min="33" max="33" width="17.6640625" customWidth="1"/>
-    <col min="34" max="34" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B3" s="52" t="s">
-        <v>189</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-    </row>
-    <row r="4" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="53" t="s">
-        <v>190</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>191</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>310</v>
-      </c>
-      <c r="E4" s="55" t="s">
-        <v>217</v>
-      </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="52" t="s">
-        <v>311</v>
-      </c>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="52" t="s">
-        <v>312</v>
-      </c>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="52" t="s">
-        <v>313</v>
-      </c>
-      <c r="N4" s="23"/>
-    </row>
-    <row r="5" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="21">
-        <v>1</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="D5" s="21">
-        <v>100</v>
-      </c>
-      <c r="E5" s="21">
-        <v>1</v>
-      </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="53" t="s">
-        <v>315</v>
-      </c>
-      <c r="H5" s="54" t="s">
-        <v>316</v>
-      </c>
-      <c r="I5" s="23"/>
-      <c r="J5" s="53" t="s">
-        <v>317</v>
-      </c>
-      <c r="K5" s="54" t="s">
-        <v>318</v>
-      </c>
-      <c r="L5" s="23"/>
-      <c r="M5" s="53" t="s">
-        <v>273</v>
-      </c>
-      <c r="N5" s="54" t="s">
-        <v>319</v>
-      </c>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-    </row>
-    <row r="6" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B6" s="21">
-        <v>2</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="D6" s="21">
-        <v>60</v>
-      </c>
-      <c r="E6" s="21">
-        <v>1</v>
-      </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="21">
-        <v>1</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="21">
-        <v>1</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>322</v>
-      </c>
-      <c r="L6" s="23"/>
-      <c r="M6" s="21">
-        <v>1</v>
-      </c>
-      <c r="N6" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-    </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B7" s="21">
-        <v>3</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="D7" s="21">
-        <v>80</v>
-      </c>
-      <c r="E7" s="21">
-        <v>1</v>
-      </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="21">
-        <v>2</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="21">
-        <v>2</v>
-      </c>
-      <c r="K7" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="L7" s="23"/>
-      <c r="M7" s="21">
-        <v>2</v>
-      </c>
-      <c r="N7" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-    </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B8" s="21">
-        <v>4</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="D8" s="21">
-        <v>40</v>
-      </c>
-      <c r="E8" s="21">
-        <v>2</v>
-      </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="21">
-        <v>3</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="21">
-        <v>3</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="L8" s="23"/>
-      <c r="M8" s="21">
-        <v>3</v>
-      </c>
-      <c r="N8" s="21" t="s">
-        <v>330</v>
-      </c>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-    </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B9" s="21">
-        <v>5</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>331</v>
-      </c>
-      <c r="D9" s="21">
-        <v>60</v>
-      </c>
-      <c r="E9" s="21">
-        <v>2</v>
-      </c>
-      <c r="F9" s="23"/>
-      <c r="G9" s="21">
-        <v>4</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="21">
-        <v>4</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>333</v>
-      </c>
-      <c r="L9" s="23"/>
-      <c r="M9" s="21">
-        <v>4</v>
-      </c>
-      <c r="N9" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-    </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B10" s="21">
-        <v>6</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="D10" s="21">
-        <v>180</v>
-      </c>
-      <c r="E10" s="21">
-        <v>3</v>
-      </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="21">
-        <v>5</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="21">
-        <v>5</v>
-      </c>
-      <c r="K10" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="P10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-    </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B11" s="21">
-        <v>7</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="D11" s="21">
-        <v>80</v>
-      </c>
-      <c r="E11" s="21">
-        <v>3</v>
-      </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="21">
-        <v>6</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="I11" s="23"/>
-      <c r="J11" s="21">
-        <v>6</v>
-      </c>
-      <c r="K11" s="21" t="s">
-        <v>340</v>
-      </c>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-    </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B12" s="21">
-        <v>8</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="D12" s="21">
-        <v>126</v>
-      </c>
-      <c r="E12" s="21">
-        <v>3</v>
-      </c>
-      <c r="F12" s="23"/>
-      <c r="G12" s="21">
-        <v>7</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="I12" s="23"/>
-      <c r="J12" s="21">
-        <v>7</v>
-      </c>
-      <c r="K12" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-    </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B13" s="21">
-        <v>9</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>344</v>
-      </c>
-      <c r="D13" s="21">
-        <v>142</v>
-      </c>
-      <c r="E13" s="21">
-        <v>3</v>
-      </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-    </row>
-    <row r="14" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="21">
-        <v>10</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="D14" s="21">
-        <v>195</v>
-      </c>
-      <c r="E14" s="21">
-        <v>3</v>
-      </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="52" t="s">
-        <v>346</v>
-      </c>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="52" t="s">
-        <v>347</v>
-      </c>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-    </row>
-    <row r="15" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="21">
-        <v>11</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>348</v>
-      </c>
-      <c r="D15" s="21">
-        <v>180</v>
-      </c>
-      <c r="E15" s="21">
-        <v>4</v>
-      </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="53" t="s">
-        <v>349</v>
-      </c>
-      <c r="H15" s="54" t="s">
-        <v>350</v>
-      </c>
-      <c r="I15" s="23"/>
-      <c r="J15" s="53" t="s">
-        <v>351</v>
-      </c>
-      <c r="K15" s="54" t="s">
-        <v>352</v>
-      </c>
-      <c r="L15" s="54" t="s">
-        <v>353</v>
-      </c>
-      <c r="M15" s="54" t="s">
-        <v>354</v>
-      </c>
-      <c r="N15" s="23"/>
-    </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B16" s="21">
-        <v>12</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="D16" s="21">
-        <v>88</v>
-      </c>
-      <c r="E16" s="21">
-        <v>1</v>
-      </c>
-      <c r="F16" s="23"/>
-      <c r="G16" s="21">
-        <v>1</v>
-      </c>
-      <c r="H16" s="21" t="s">
-        <v>356</v>
-      </c>
-      <c r="I16" s="23"/>
-      <c r="J16" s="21">
-        <v>1</v>
-      </c>
-      <c r="K16" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="L16" s="21">
-        <v>0</v>
-      </c>
-      <c r="M16" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="N16" s="23"/>
-    </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B17" s="21">
-        <v>13</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="D17" s="21">
-        <v>200</v>
-      </c>
-      <c r="E17" s="21">
-        <v>4</v>
-      </c>
-      <c r="F17" s="23"/>
-      <c r="G17" s="21">
-        <v>2</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="I17" s="23"/>
-      <c r="J17" s="21">
-        <v>2</v>
-      </c>
-      <c r="K17" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="L17" s="21">
-        <v>0</v>
-      </c>
-      <c r="M17" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="N17" s="23"/>
-    </row>
-    <row r="18" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B18" s="21">
-        <v>14</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>361</v>
-      </c>
-      <c r="D18" s="21">
-        <v>120</v>
-      </c>
-      <c r="E18" s="21">
-        <v>5</v>
-      </c>
-      <c r="F18" s="23"/>
-      <c r="G18" s="21">
-        <v>3</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="I18" s="23"/>
-      <c r="J18" s="21">
-        <v>3</v>
-      </c>
-      <c r="K18" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="L18" s="21">
-        <v>0</v>
-      </c>
-      <c r="M18" s="21" t="s">
-        <v>363</v>
-      </c>
-      <c r="N18" s="23"/>
-      <c r="T18" s="15"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
-    </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B19" s="21">
-        <v>15</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="D19" s="21">
-        <v>160</v>
-      </c>
-      <c r="E19" s="21">
-        <v>5</v>
-      </c>
-      <c r="F19" s="23"/>
-      <c r="G19" s="21">
-        <v>4</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>365</v>
-      </c>
-      <c r="I19" s="23"/>
-      <c r="J19" s="21">
-        <v>4</v>
-      </c>
-      <c r="K19" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="L19" s="21">
-        <v>0</v>
-      </c>
-      <c r="M19" s="21" t="s">
-        <v>366</v>
-      </c>
-      <c r="N19" s="23"/>
-      <c r="P19" s="74"/>
-      <c r="Q19" s="74"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-    </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B20" s="21">
-        <v>16</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>367</v>
-      </c>
-      <c r="D20" s="21">
-        <v>140</v>
-      </c>
-      <c r="E20" s="21">
-        <v>6</v>
-      </c>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="21">
-        <v>5</v>
-      </c>
-      <c r="K20" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="L20" s="21">
-        <v>0</v>
-      </c>
-      <c r="M20" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="N20" s="23"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="74"/>
-      <c r="R20" s="74"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
-    </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B21" s="21">
-        <v>17</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>369</v>
-      </c>
-      <c r="D21" s="21">
-        <v>170</v>
-      </c>
-      <c r="E21" s="21">
-        <v>6</v>
-      </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="21">
-        <v>6</v>
-      </c>
-      <c r="K21" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="L21" s="21">
-        <v>1</v>
-      </c>
-      <c r="M21" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="N21" s="23"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="74"/>
-      <c r="R21" s="74"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-    </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B22" s="21">
-        <v>18</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="D22" s="21">
-        <v>120</v>
-      </c>
-      <c r="E22" s="21">
-        <v>5</v>
-      </c>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="21">
-        <v>7</v>
-      </c>
-      <c r="K22" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="L22" s="21">
-        <v>1</v>
-      </c>
-      <c r="M22" s="21" t="s">
-        <v>372</v>
-      </c>
-      <c r="N22" s="23"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="74"/>
-      <c r="R22" s="74"/>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
-    </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B23" s="21">
-        <v>19</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="D23" s="21">
-        <v>175</v>
-      </c>
-      <c r="E23" s="21">
-        <v>7</v>
-      </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="21">
-        <v>8</v>
-      </c>
-      <c r="K23" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="L23" s="21">
-        <v>1</v>
-      </c>
-      <c r="M23" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="N23" s="23"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="74"/>
-      <c r="R23" s="74"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4"/>
-      <c r="W23" s="4"/>
-    </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B24" s="21">
-        <v>20</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="D24" s="21">
-        <v>186</v>
-      </c>
-      <c r="E24" s="21">
-        <v>7</v>
-      </c>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="21">
-        <v>9</v>
-      </c>
-      <c r="K24" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="L24" s="21">
-        <v>1</v>
-      </c>
-      <c r="M24" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="N24" s="23"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="74"/>
-      <c r="R24" s="74"/>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="4"/>
-      <c r="W24" s="4"/>
-    </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="21">
-        <v>10</v>
-      </c>
-      <c r="K25" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="L25" s="21">
-        <v>1</v>
-      </c>
-      <c r="M25" s="21" t="s">
-        <v>377</v>
-      </c>
-      <c r="N25" s="23"/>
-    </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-    </row>
-    <row r="27" spans="2:35" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B27" s="52" t="s">
-        <v>378</v>
-      </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23" t="s">
-        <v>379</v>
-      </c>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-    </row>
-    <row r="28" spans="2:35" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="53" t="s">
-        <v>380</v>
-      </c>
-      <c r="C28" s="54" t="s">
-        <v>381</v>
-      </c>
-      <c r="D28" s="54" t="s">
-        <v>382</v>
-      </c>
-      <c r="E28" s="54" t="s">
-        <v>383</v>
-      </c>
-      <c r="F28" s="54" t="s">
-        <v>384</v>
-      </c>
-      <c r="G28" s="54" t="s">
-        <v>385</v>
-      </c>
-      <c r="H28" s="55" t="s">
-        <v>386</v>
-      </c>
-      <c r="I28" s="55" t="s">
-        <v>387</v>
-      </c>
-      <c r="J28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="T28" s="15"/>
-      <c r="U28" s="15"/>
-      <c r="X28" s="15"/>
-      <c r="Y28" s="15"/>
-      <c r="AD28" s="47"/>
-    </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B29" s="21">
-        <v>1</v>
-      </c>
-      <c r="C29" s="56" t="s">
-        <v>388</v>
-      </c>
-      <c r="D29" s="21">
-        <v>20</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="F29" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G29" s="21">
-        <v>0</v>
-      </c>
-      <c r="H29" s="21">
-        <v>1</v>
-      </c>
-      <c r="I29" s="21">
-        <v>1</v>
-      </c>
-      <c r="J29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="23"/>
-      <c r="P29" s="4"/>
-      <c r="T29" s="23"/>
-      <c r="U29" s="23"/>
-      <c r="V29" s="23"/>
-      <c r="X29" s="4"/>
-      <c r="Y29" s="4"/>
-      <c r="AA29" s="48"/>
-      <c r="AB29" s="4"/>
-      <c r="AC29" s="4"/>
-      <c r="AD29" s="48"/>
-      <c r="AF29" s="48"/>
-      <c r="AG29" s="4"/>
-      <c r="AH29" s="4"/>
-      <c r="AI29" s="48"/>
-    </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B30" s="21">
-        <v>2</v>
-      </c>
-      <c r="C30" s="56" t="s">
-        <v>390</v>
-      </c>
-      <c r="D30" s="21">
-        <v>20</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="F30" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G30" s="21">
-        <v>0</v>
-      </c>
-      <c r="H30" s="21">
-        <v>1</v>
-      </c>
-      <c r="I30" s="21">
-        <v>2</v>
-      </c>
-      <c r="J30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
-      <c r="N30" s="23"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="T30" s="23"/>
-      <c r="U30" s="23"/>
-      <c r="V30" s="23"/>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
-      <c r="AA30" s="48"/>
-      <c r="AB30" s="49"/>
-      <c r="AC30" s="4"/>
-      <c r="AD30" s="48"/>
-      <c r="AF30" s="48"/>
-      <c r="AG30" s="49"/>
-      <c r="AH30" s="4"/>
-      <c r="AI30" s="48"/>
-    </row>
-    <row r="31" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B31" s="21">
-        <v>3</v>
-      </c>
-      <c r="C31" s="56" t="s">
-        <v>392</v>
-      </c>
-      <c r="D31" s="21">
-        <v>20</v>
-      </c>
-      <c r="E31" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="F31" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G31" s="21">
-        <v>0</v>
-      </c>
-      <c r="H31" s="21">
-        <v>2</v>
-      </c>
-      <c r="I31" s="21">
-        <v>3</v>
-      </c>
-      <c r="J31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="T31" s="23"/>
-      <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
-      <c r="AA31" s="48"/>
-      <c r="AB31" s="49"/>
-      <c r="AC31" s="4"/>
-      <c r="AD31" s="48"/>
-      <c r="AF31" s="48"/>
-      <c r="AG31" s="49"/>
-      <c r="AH31" s="4"/>
-      <c r="AI31" s="48"/>
-    </row>
-    <row r="32" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B32" s="21">
-        <v>4</v>
-      </c>
-      <c r="C32" s="56" t="s">
-        <v>394</v>
-      </c>
-      <c r="D32" s="21">
-        <v>30</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="F32" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G32" s="21">
-        <v>0</v>
-      </c>
-      <c r="H32" s="21">
-        <v>2</v>
-      </c>
-      <c r="I32" s="21">
-        <v>4</v>
-      </c>
-      <c r="J32" s="23"/>
-      <c r="L32" s="23"/>
-      <c r="M32" s="23"/>
-      <c r="N32" s="23"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="T32" s="23"/>
-      <c r="U32" s="23"/>
-      <c r="V32" s="23"/>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
-      <c r="AA32" s="48"/>
-      <c r="AB32" s="49"/>
-      <c r="AC32" s="4"/>
-      <c r="AD32" s="48"/>
-      <c r="AF32" s="48"/>
-      <c r="AG32" s="49"/>
-      <c r="AH32" s="4"/>
-      <c r="AI32" s="48"/>
-    </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B33" s="21">
-        <v>5</v>
-      </c>
-      <c r="C33" s="56" t="s">
-        <v>396</v>
-      </c>
-      <c r="D33" s="21">
-        <v>30</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="F33" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G33" s="21">
-        <v>0</v>
-      </c>
-      <c r="H33" s="21">
-        <v>3</v>
-      </c>
-      <c r="I33" s="21">
-        <v>5</v>
-      </c>
-      <c r="J33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="23"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="23"/>
-      <c r="V33" s="23"/>
-      <c r="AA33" s="48"/>
-      <c r="AB33" s="49"/>
-      <c r="AC33" s="4"/>
-      <c r="AD33" s="48"/>
-      <c r="AF33" s="48"/>
-      <c r="AG33" s="49"/>
-      <c r="AH33" s="4"/>
-      <c r="AI33" s="48"/>
-    </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B34" s="21">
-        <v>6</v>
-      </c>
-      <c r="C34" s="56" t="s">
-        <v>390</v>
-      </c>
-      <c r="D34" s="21">
-        <v>40</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="F34" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G34" s="21">
-        <v>0</v>
-      </c>
-      <c r="H34" s="21">
-        <v>3</v>
-      </c>
-      <c r="I34" s="21">
-        <v>6</v>
-      </c>
-      <c r="J34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
-      <c r="N34" s="23"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="T34" s="50"/>
-      <c r="U34" s="50"/>
-      <c r="V34" s="23"/>
-    </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B35" s="21">
-        <v>7</v>
-      </c>
-      <c r="C35" s="56" t="s">
-        <v>392</v>
-      </c>
-      <c r="D35" s="21">
-        <v>40</v>
-      </c>
-      <c r="E35" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="F35" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G35" s="21">
-        <v>0</v>
-      </c>
-      <c r="H35" s="21">
-        <v>4</v>
-      </c>
-      <c r="I35" s="21">
-        <v>7</v>
-      </c>
-      <c r="J35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-    </row>
-    <row r="36" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B36" s="21">
-        <v>8</v>
-      </c>
-      <c r="C36" s="56" t="s">
-        <v>396</v>
-      </c>
-      <c r="D36" s="21">
-        <v>50</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="F36" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G36" s="21">
-        <v>0</v>
-      </c>
-      <c r="H36" s="21">
-        <v>4</v>
-      </c>
-      <c r="I36" s="21">
-        <v>8</v>
-      </c>
-      <c r="J36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="23"/>
-    </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B37" s="21">
-        <v>9</v>
-      </c>
-      <c r="C37" s="56" t="s">
-        <v>396</v>
-      </c>
-      <c r="D37" s="21">
-        <v>50</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>401</v>
-      </c>
-      <c r="F37" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G37" s="21">
-        <v>0</v>
-      </c>
-      <c r="H37" s="21">
-        <v>4</v>
-      </c>
-      <c r="I37" s="21">
-        <v>1</v>
-      </c>
-      <c r="J37" s="23"/>
-      <c r="K37" s="23"/>
-      <c r="L37" s="23"/>
-      <c r="M37" s="23"/>
-      <c r="N37" s="23"/>
-      <c r="P37" s="15"/>
-    </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B38" s="21">
-        <v>10</v>
-      </c>
-      <c r="C38" s="56" t="s">
-        <v>396</v>
-      </c>
-      <c r="D38" s="21">
-        <v>20</v>
-      </c>
-      <c r="E38" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="F38" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G38" s="21">
-        <v>0</v>
-      </c>
-      <c r="H38" s="21">
-        <v>4</v>
-      </c>
-      <c r="I38" s="21">
-        <v>2</v>
-      </c>
-      <c r="J38" s="23"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="23"/>
-      <c r="M38" s="23"/>
-      <c r="N38" s="23"/>
-    </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B39" s="21">
-        <v>11</v>
-      </c>
-      <c r="C39" s="56" t="s">
-        <v>403</v>
-      </c>
-      <c r="D39" s="21">
-        <v>30</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>404</v>
-      </c>
-      <c r="F39" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G39" s="21">
-        <v>0</v>
-      </c>
-      <c r="H39" s="21">
-        <v>3</v>
-      </c>
-      <c r="I39" s="21">
-        <v>9</v>
-      </c>
-      <c r="J39" s="23"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="23"/>
-      <c r="N39" s="23"/>
-    </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B40" s="21">
-        <v>12</v>
-      </c>
-      <c r="C40" s="56" t="s">
-        <v>405</v>
-      </c>
-      <c r="D40" s="21">
-        <v>20</v>
-      </c>
-      <c r="E40" s="21" t="s">
-        <v>406</v>
-      </c>
-      <c r="F40" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G40" s="21">
-        <v>0</v>
-      </c>
-      <c r="H40" s="21">
-        <v>3</v>
-      </c>
-      <c r="I40" s="21">
-        <v>10</v>
-      </c>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="23"/>
-    </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B41" s="21">
-        <v>13</v>
-      </c>
-      <c r="C41" s="56" t="s">
-        <v>407</v>
-      </c>
-      <c r="D41" s="21">
-        <v>40</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="F41" s="21">
-        <v>258369741</v>
-      </c>
-      <c r="G41" s="21">
-        <v>0</v>
-      </c>
-      <c r="H41" s="21">
-        <v>1</v>
-      </c>
-      <c r="I41" s="21">
-        <v>5</v>
-      </c>
-      <c r="J41" s="23"/>
-      <c r="K41" s="23"/>
-      <c r="L41" s="23"/>
-      <c r="M41" s="23"/>
-      <c r="N41" s="23"/>
-      <c r="AA41" s="61"/>
-    </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="23"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="23"/>
-      <c r="N42" s="23"/>
-      <c r="AA42" s="62"/>
-      <c r="AB42" s="62"/>
-      <c r="AC42" s="62"/>
-      <c r="AD42" s="62"/>
-      <c r="AE42" s="62"/>
-      <c r="AF42" s="62"/>
-      <c r="AG42" s="62"/>
-      <c r="AH42" s="62"/>
-    </row>
-    <row r="43" spans="2:35" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B43" s="52" t="s">
-        <v>409</v>
-      </c>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="23"/>
-      <c r="L43" s="23"/>
-      <c r="M43" s="23"/>
-      <c r="N43" s="23"/>
-    </row>
-    <row r="44" spans="2:35" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B44" s="53" t="s">
-        <v>410</v>
-      </c>
-      <c r="C44" s="54" t="s">
-        <v>411</v>
-      </c>
-      <c r="D44" s="54" t="s">
-        <v>412</v>
-      </c>
-      <c r="E44" s="54" t="s">
-        <v>413</v>
-      </c>
-      <c r="F44" s="54" t="s">
-        <v>414</v>
-      </c>
-      <c r="G44" s="57" t="s">
-        <v>415</v>
-      </c>
-      <c r="H44" s="64" t="s">
-        <v>416</v>
-      </c>
-      <c r="I44" s="63"/>
-      <c r="J44" s="63"/>
-      <c r="K44" s="23"/>
-      <c r="L44" s="23"/>
-      <c r="M44" s="23"/>
-      <c r="N44" s="23"/>
-      <c r="O44" s="4"/>
-    </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B45" s="21">
-        <v>1</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>417</v>
-      </c>
-      <c r="D45" s="56" t="s">
-        <v>418</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="F45" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G45" s="21" t="s">
-        <v>419</v>
-      </c>
-      <c r="H45" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I45" s="23"/>
-      <c r="J45" s="23"/>
-      <c r="K45" s="23"/>
-      <c r="L45" s="23"/>
-      <c r="M45" s="23"/>
-      <c r="N45" s="23"/>
-      <c r="O45" s="23"/>
-      <c r="P45" s="23"/>
-      <c r="Q45" s="23"/>
-      <c r="R45" s="23"/>
-    </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B46" s="21">
-        <v>2</v>
-      </c>
-      <c r="C46" s="21" t="s">
-        <v>421</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>422</v>
-      </c>
-      <c r="E46" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="F46" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G46" s="21" t="s">
-        <v>423</v>
-      </c>
-      <c r="H46" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I46" s="23"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="23"/>
-      <c r="L46" s="23"/>
-      <c r="M46" s="23"/>
-      <c r="N46" s="23"/>
-      <c r="O46" s="23"/>
-      <c r="P46" s="23"/>
-      <c r="Q46" s="51"/>
-      <c r="R46" s="51"/>
-      <c r="T46" s="23"/>
-      <c r="U46" s="23"/>
-      <c r="V46" s="23"/>
-    </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B47" s="21">
-        <v>3</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>424</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>425</v>
-      </c>
-      <c r="E47" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="F47" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G47" s="21" t="s">
-        <v>426</v>
-      </c>
-      <c r="H47" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I47" s="23"/>
-      <c r="J47" s="23"/>
-      <c r="K47" s="23"/>
-      <c r="L47" s="23"/>
-      <c r="M47" s="23"/>
-      <c r="N47" s="23"/>
-      <c r="O47" s="23"/>
-      <c r="P47" s="23"/>
-      <c r="Q47" s="51"/>
-      <c r="R47" s="51"/>
-      <c r="T47" s="23"/>
-      <c r="U47" s="23"/>
-      <c r="V47" s="23"/>
-    </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B48" s="21">
-        <v>4</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>427</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>428</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="F48" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G48" s="21" t="s">
-        <v>429</v>
-      </c>
-      <c r="H48" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I48" s="23"/>
-      <c r="J48" s="23"/>
-      <c r="K48" s="23"/>
-      <c r="L48" s="23"/>
-      <c r="M48" s="23"/>
-      <c r="N48" s="23"/>
-      <c r="O48" s="23"/>
-      <c r="P48" s="23"/>
-      <c r="Q48" s="51"/>
-      <c r="R48" s="51"/>
-      <c r="T48" s="23"/>
-      <c r="U48" s="23"/>
-      <c r="V48" s="23"/>
-      <c r="AE48" s="48"/>
-      <c r="AF48" s="48"/>
-    </row>
-    <row r="49" spans="2:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="21">
-        <v>5</v>
-      </c>
-      <c r="C49" s="21" t="s">
-        <v>430</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>431</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="F49" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G49" s="21" t="s">
-        <v>432</v>
-      </c>
-      <c r="H49" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I49" s="23"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="23"/>
-      <c r="O49" s="23"/>
-      <c r="P49" s="23"/>
-      <c r="Q49" s="51"/>
-      <c r="R49" s="51"/>
-      <c r="T49" s="23"/>
-      <c r="U49" s="23"/>
-      <c r="V49" s="23"/>
-      <c r="AE49" s="48"/>
-      <c r="AF49" s="48"/>
-    </row>
-    <row r="50" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B50" s="21">
-        <v>6</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>433</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>434</v>
-      </c>
-      <c r="E50" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="F50" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G50" s="21" t="s">
-        <v>435</v>
-      </c>
-      <c r="H50" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I50" s="23"/>
-      <c r="J50" s="23"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="23"/>
-      <c r="M50" s="23"/>
-      <c r="N50" s="23"/>
-      <c r="O50" s="23"/>
-      <c r="P50" s="23"/>
-      <c r="Q50" s="51"/>
-      <c r="R50" s="51"/>
-      <c r="AE50" s="48"/>
-      <c r="AF50" s="48"/>
-    </row>
-    <row r="51" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B51" s="21">
-        <v>7</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>436</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>437</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="F51" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G51" s="21" t="s">
-        <v>438</v>
-      </c>
-      <c r="H51" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I51" s="23"/>
-      <c r="J51" s="23"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="23"/>
-      <c r="M51" s="23"/>
-      <c r="N51" s="23"/>
-      <c r="O51" s="23"/>
-      <c r="P51" s="23"/>
-      <c r="Q51" s="51"/>
-      <c r="R51" s="51"/>
-      <c r="AE51" s="48"/>
-      <c r="AF51" s="48"/>
-    </row>
-    <row r="52" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B52" s="21">
-        <v>8</v>
-      </c>
-      <c r="C52" s="21" t="s">
-        <v>439</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="E52" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="F52" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G52" s="21" t="s">
-        <v>441</v>
-      </c>
-      <c r="H52" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I52" s="23"/>
-      <c r="J52" s="23"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="23"/>
-      <c r="M52" s="23"/>
-      <c r="N52" s="23"/>
-      <c r="O52" s="23"/>
-      <c r="P52" s="23"/>
-      <c r="Q52" s="51"/>
-      <c r="R52" s="51"/>
-      <c r="AE52" s="48"/>
-      <c r="AF52" s="48"/>
-    </row>
-    <row r="53" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B53" s="21">
-        <v>9</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>443</v>
-      </c>
-      <c r="E53" s="21" t="s">
-        <v>401</v>
-      </c>
-      <c r="F53" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G53" s="21" t="s">
-        <v>444</v>
-      </c>
-      <c r="H53" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I53" s="23"/>
-      <c r="J53" s="23"/>
-      <c r="K53" s="23"/>
-      <c r="L53" s="23"/>
-      <c r="M53" s="23"/>
-      <c r="N53" s="23"/>
-      <c r="O53" s="23"/>
-      <c r="P53" s="23"/>
-      <c r="Q53" s="51"/>
-      <c r="R53" s="51"/>
-    </row>
-    <row r="54" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B54" s="21">
-        <v>10</v>
-      </c>
-      <c r="C54" s="21" t="s">
-        <v>445</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>446</v>
-      </c>
-      <c r="E54" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="F54" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G54" s="21" t="s">
-        <v>447</v>
-      </c>
-      <c r="H54" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I54" s="23"/>
-      <c r="J54" s="23"/>
-      <c r="K54" s="23"/>
-      <c r="L54" s="23"/>
-      <c r="M54" s="23"/>
-      <c r="N54" s="23"/>
-      <c r="O54" s="23"/>
-      <c r="P54" s="23"/>
-      <c r="Q54" s="51"/>
-      <c r="R54" s="51"/>
-    </row>
-    <row r="55" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
-      <c r="H55" s="23"/>
-      <c r="I55" s="23"/>
-      <c r="J55" s="23"/>
-      <c r="K55" s="23"/>
-      <c r="L55" s="23"/>
-      <c r="M55" s="23"/>
-      <c r="N55" s="23"/>
-      <c r="O55" s="23"/>
-      <c r="P55" s="23"/>
-      <c r="Q55" s="51"/>
-      <c r="R55" s="51"/>
-    </row>
-    <row r="56" spans="2:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B56" s="52" t="s">
-        <v>448</v>
-      </c>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="23"/>
-      <c r="J56" s="23"/>
-      <c r="K56" s="23"/>
-      <c r="L56" s="23"/>
-      <c r="M56" s="23"/>
-      <c r="N56" s="23"/>
-      <c r="O56" s="23"/>
-      <c r="P56" s="23"/>
-      <c r="Q56" s="51"/>
-      <c r="R56" s="51"/>
-    </row>
-    <row r="57" spans="2:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B57" s="53" t="s">
-        <v>449</v>
-      </c>
-      <c r="C57" s="54" t="s">
-        <v>450</v>
-      </c>
-      <c r="D57" s="54" t="s">
-        <v>451</v>
-      </c>
-      <c r="E57" s="54" t="s">
-        <v>452</v>
-      </c>
-      <c r="F57" s="54" t="s">
-        <v>453</v>
-      </c>
-      <c r="G57" s="54" t="s">
-        <v>454</v>
-      </c>
-      <c r="H57" s="54" t="s">
-        <v>455</v>
-      </c>
-      <c r="I57" s="55" t="s">
-        <v>456</v>
-      </c>
-      <c r="J57" s="23"/>
-      <c r="K57" s="23"/>
-      <c r="L57" s="23"/>
-      <c r="M57" s="23"/>
-      <c r="N57" s="23"/>
-      <c r="O57" s="23"/>
-      <c r="P57" s="23"/>
-      <c r="Q57" s="51"/>
-      <c r="R57" s="51"/>
-    </row>
-    <row r="58" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B58" s="21">
-        <v>1</v>
-      </c>
-      <c r="C58" s="21" t="s">
-        <v>457</v>
-      </c>
-      <c r="D58" s="56" t="s">
-        <v>458</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="F58" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G58" s="21" t="s">
-        <v>459</v>
-      </c>
-      <c r="H58" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I58" s="21">
-        <v>1</v>
-      </c>
-      <c r="J58" s="23"/>
-      <c r="K58" s="23"/>
-      <c r="L58" s="23"/>
-      <c r="M58" s="23"/>
-      <c r="N58" s="23"/>
-      <c r="O58" s="23"/>
-      <c r="P58" s="23"/>
-      <c r="Q58" s="51"/>
-      <c r="R58" s="51"/>
-    </row>
-    <row r="59" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B59" s="21">
-        <v>2</v>
-      </c>
-      <c r="C59" s="21" t="s">
-        <v>460</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>461</v>
-      </c>
-      <c r="E59" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="F59" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G59" s="21" t="s">
-        <v>462</v>
-      </c>
-      <c r="H59" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I59" s="21">
-        <v>1</v>
-      </c>
-      <c r="J59" s="23"/>
-      <c r="K59" s="23"/>
-      <c r="L59" s="23"/>
-      <c r="M59" s="23"/>
-      <c r="N59" s="23"/>
-      <c r="O59" s="23"/>
-      <c r="P59" s="23"/>
-      <c r="Q59" s="51"/>
-      <c r="R59" s="51"/>
-    </row>
-    <row r="60" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B60" s="21">
-        <v>3</v>
-      </c>
-      <c r="C60" s="21" t="s">
-        <v>463</v>
-      </c>
-      <c r="D60" s="56" t="s">
-        <v>464</v>
-      </c>
-      <c r="E60" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="F60" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G60" s="21" t="s">
-        <v>465</v>
-      </c>
-      <c r="H60" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I60" s="21">
-        <v>2</v>
-      </c>
-      <c r="J60" s="23"/>
-      <c r="K60" s="23"/>
-      <c r="L60" s="23"/>
-      <c r="M60" s="23"/>
-      <c r="N60" s="23"/>
-      <c r="O60" s="23"/>
-      <c r="P60" s="23"/>
-      <c r="Q60" s="51"/>
-      <c r="R60" s="51"/>
-    </row>
-    <row r="61" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B61" s="21">
-        <v>4</v>
-      </c>
-      <c r="C61" s="21" t="s">
-        <v>466</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>467</v>
-      </c>
-      <c r="E61" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="F61" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G61" s="21" t="s">
-        <v>468</v>
-      </c>
-      <c r="H61" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I61" s="21">
-        <v>1</v>
-      </c>
-      <c r="J61" s="23"/>
-      <c r="K61" s="23"/>
-      <c r="L61" s="23"/>
-      <c r="M61" s="23"/>
-      <c r="N61" s="23"/>
-      <c r="O61" s="23"/>
-      <c r="P61" s="23"/>
-      <c r="Q61" s="51"/>
-      <c r="R61" s="51"/>
-    </row>
-    <row r="62" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B62" s="21">
-        <v>5</v>
-      </c>
-      <c r="C62" s="21" t="s">
-        <v>469</v>
-      </c>
-      <c r="D62" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="E62" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="F62" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G62" s="21" t="s">
-        <v>471</v>
-      </c>
-      <c r="H62" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I62" s="21">
-        <v>1</v>
-      </c>
-      <c r="J62" s="23"/>
-      <c r="K62" s="23"/>
-      <c r="L62" s="23"/>
-      <c r="M62" s="23"/>
-      <c r="N62" s="23"/>
-    </row>
-    <row r="63" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B63" s="21">
-        <v>6</v>
-      </c>
-      <c r="C63" s="21" t="s">
-        <v>472</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>473</v>
-      </c>
-      <c r="E63" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="F63" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G63" s="21" t="s">
-        <v>474</v>
-      </c>
-      <c r="H63" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I63" s="21">
-        <v>1</v>
-      </c>
-      <c r="J63" s="23"/>
-      <c r="K63" s="23"/>
-      <c r="L63" s="23"/>
-      <c r="M63" s="23"/>
-      <c r="N63" s="23"/>
-    </row>
-    <row r="64" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B64" s="21">
-        <v>7</v>
-      </c>
-      <c r="C64" s="21" t="s">
-        <v>475</v>
-      </c>
-      <c r="D64" s="56" t="s">
-        <v>476</v>
-      </c>
-      <c r="E64" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="F64" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G64" s="21" t="s">
-        <v>477</v>
-      </c>
-      <c r="H64" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I64" s="21">
-        <v>2</v>
-      </c>
-      <c r="J64" s="23"/>
-      <c r="K64" s="23"/>
-      <c r="L64" s="23"/>
-      <c r="M64" s="23"/>
-      <c r="N64" s="23"/>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B65" s="21">
-        <v>8</v>
-      </c>
-      <c r="C65" s="21" t="s">
-        <v>478</v>
-      </c>
-      <c r="D65" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="E65" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="F65" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G65" s="21" t="s">
-        <v>480</v>
-      </c>
-      <c r="H65" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I65" s="21">
-        <v>3</v>
-      </c>
-      <c r="J65" s="23"/>
-      <c r="K65" s="23"/>
-      <c r="L65" s="23"/>
-      <c r="M65" s="23"/>
-      <c r="N65" s="23"/>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B66" s="21">
-        <v>9</v>
-      </c>
-      <c r="C66" s="21" t="s">
-        <v>481</v>
-      </c>
-      <c r="D66" s="56" t="s">
-        <v>482</v>
-      </c>
-      <c r="E66" s="21" t="s">
-        <v>401</v>
-      </c>
-      <c r="F66" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G66" s="21" t="s">
-        <v>483</v>
-      </c>
-      <c r="H66" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I66" s="21">
-        <v>1</v>
-      </c>
-      <c r="J66" s="23"/>
-      <c r="K66" s="23"/>
-      <c r="L66" s="23"/>
-      <c r="M66" s="23"/>
-      <c r="N66" s="23"/>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B67" s="21">
-        <v>10</v>
-      </c>
-      <c r="C67" s="21" t="s">
-        <v>484</v>
-      </c>
-      <c r="D67" s="21" t="s">
-        <v>485</v>
-      </c>
-      <c r="E67" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="F67" s="21">
-        <v>123456789</v>
-      </c>
-      <c r="G67" s="21" t="s">
-        <v>486</v>
-      </c>
-      <c r="H67" s="60" t="s">
-        <v>420</v>
-      </c>
-      <c r="I67" s="21">
-        <v>4</v>
-      </c>
-      <c r="J67" s="23"/>
-      <c r="K67" s="23"/>
-      <c r="L67" s="23"/>
-      <c r="M67" s="23"/>
-      <c r="N67" s="23"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B68" s="23"/>
-      <c r="C68" s="23"/>
-      <c r="D68" s="23"/>
-      <c r="E68" s="23"/>
-      <c r="F68" s="23"/>
-      <c r="G68" s="23"/>
-      <c r="H68" s="23"/>
-      <c r="I68" s="23"/>
-      <c r="J68" s="23"/>
-      <c r="K68" s="23"/>
-      <c r="L68" s="23"/>
-      <c r="M68" s="23"/>
-      <c r="N68" s="23"/>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B69" s="23"/>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
-      <c r="H69" s="23"/>
-      <c r="I69" s="23"/>
-      <c r="J69" s="23"/>
-      <c r="K69" s="23"/>
-      <c r="L69" s="23"/>
-      <c r="M69" s="23"/>
-      <c r="N69" s="23"/>
-    </row>
-    <row r="70" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B70" s="58" t="s">
-        <v>487</v>
-      </c>
-      <c r="C70" s="23"/>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="23"/>
-      <c r="H70" s="23"/>
-      <c r="I70" s="23"/>
-      <c r="J70" s="23"/>
-      <c r="K70" s="23"/>
-      <c r="L70" s="23"/>
-      <c r="M70" s="23"/>
-      <c r="N70" s="23"/>
-    </row>
-    <row r="71" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B71" s="53" t="s">
-        <v>488</v>
-      </c>
-      <c r="C71" s="59" t="s">
-        <v>489</v>
-      </c>
-      <c r="D71" s="59" t="s">
-        <v>490</v>
-      </c>
-      <c r="E71" s="54" t="s">
-        <v>491</v>
-      </c>
-      <c r="F71" s="54" t="s">
-        <v>492</v>
-      </c>
-      <c r="G71" s="23"/>
-      <c r="H71" s="23"/>
-      <c r="I71" s="23"/>
-      <c r="J71" s="23"/>
-      <c r="K71" s="23"/>
-      <c r="L71" s="23"/>
-      <c r="M71" s="23"/>
-      <c r="N71" s="23"/>
-      <c r="Q71" s="4"/>
-      <c r="W71" s="15"/>
-      <c r="X71" s="15"/>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B72" s="23"/>
-      <c r="C72" s="23"/>
-      <c r="D72" s="23"/>
-      <c r="E72" s="23"/>
-      <c r="F72" s="23"/>
-      <c r="G72" s="23"/>
-      <c r="H72" s="23"/>
-      <c r="I72" s="23"/>
-      <c r="J72" s="23"/>
-      <c r="K72" s="23"/>
-      <c r="L72" s="23"/>
-      <c r="M72" s="23"/>
-      <c r="N72" s="23"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
-      <c r="W72" s="4"/>
-      <c r="X72" s="4"/>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B73" s="23"/>
-      <c r="C73" s="75" t="s">
-        <v>493</v>
-      </c>
-      <c r="D73" s="75"/>
-      <c r="E73" s="75"/>
-      <c r="F73" s="23"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="23"/>
-      <c r="I73" s="23"/>
-      <c r="J73" s="23"/>
-      <c r="K73" s="23"/>
-      <c r="L73" s="23"/>
-      <c r="M73" s="23"/>
-      <c r="N73" s="23"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
-      <c r="W73" s="4"/>
-      <c r="X73" s="4"/>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B74" s="23"/>
-      <c r="C74" s="75"/>
-      <c r="D74" s="75"/>
-      <c r="E74" s="75"/>
-      <c r="F74" s="23"/>
-      <c r="G74" s="23"/>
-      <c r="H74" s="23"/>
-      <c r="I74" s="23"/>
-      <c r="J74" s="23"/>
-      <c r="K74" s="23"/>
-      <c r="L74" s="23"/>
-      <c r="M74" s="23"/>
-      <c r="N74" s="23"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4"/>
-      <c r="W74" s="4"/>
-      <c r="X74" s="4"/>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B75" s="23"/>
-      <c r="C75" s="23"/>
-      <c r="D75" s="23"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="23"/>
-      <c r="I75" s="23"/>
-      <c r="J75" s="23"/>
-      <c r="K75" s="23"/>
-      <c r="L75" s="23"/>
-      <c r="M75" s="23"/>
-      <c r="N75" s="23"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
-      <c r="W75" s="4"/>
-      <c r="X75" s="4"/>
-    </row>
-    <row r="76" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B76" s="58" t="s">
-        <v>494</v>
-      </c>
-      <c r="C76" s="23"/>
-      <c r="D76" s="23"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="23"/>
-      <c r="G76" s="23"/>
-      <c r="H76" s="23"/>
-      <c r="I76" s="23"/>
-      <c r="J76" s="23"/>
-      <c r="K76" s="23"/>
-      <c r="L76" s="23"/>
-      <c r="M76" s="23"/>
-      <c r="N76" s="23"/>
-      <c r="Q76" s="4"/>
-      <c r="R76" s="4"/>
-    </row>
-    <row r="77" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B77" s="53" t="s">
-        <v>495</v>
-      </c>
-      <c r="C77" s="53" t="s">
-        <v>496</v>
-      </c>
-      <c r="D77" s="53" t="s">
-        <v>497</v>
-      </c>
-      <c r="E77" s="54" t="s">
-        <v>498</v>
-      </c>
-      <c r="F77" s="23"/>
-      <c r="G77" s="23"/>
-      <c r="H77" s="23"/>
-      <c r="I77" s="23"/>
-      <c r="J77" s="23"/>
-      <c r="K77" s="23"/>
-      <c r="L77" s="23"/>
-      <c r="M77" s="23"/>
-      <c r="N77" s="23"/>
-      <c r="Q77" s="4"/>
-      <c r="R77" s="4"/>
-    </row>
-    <row r="78" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B78" s="23"/>
-      <c r="C78" s="23"/>
-      <c r="D78" s="23"/>
-      <c r="E78" s="23"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="23"/>
-      <c r="J78" s="23"/>
-      <c r="K78" s="23"/>
-      <c r="L78" s="23"/>
-      <c r="M78" s="23"/>
-      <c r="N78" s="23"/>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B79" s="23"/>
-      <c r="C79" s="75" t="s">
-        <v>493</v>
-      </c>
-      <c r="D79" s="75"/>
-      <c r="E79" s="23"/>
-      <c r="F79" s="23"/>
-      <c r="G79" s="23"/>
-      <c r="H79" s="23"/>
-      <c r="I79" s="23"/>
-      <c r="J79" s="23"/>
-      <c r="K79" s="23"/>
-      <c r="L79" s="23"/>
-      <c r="M79" s="23"/>
-      <c r="N79" s="23"/>
-    </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B80" s="23"/>
-      <c r="C80" s="75"/>
-      <c r="D80" s="75"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="23"/>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
-      <c r="I80" s="23"/>
-      <c r="J80" s="23"/>
-      <c r="K80" s="23"/>
-      <c r="L80" s="23"/>
-      <c r="M80" s="23"/>
-      <c r="N80" s="23"/>
-    </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B81" s="23"/>
-      <c r="C81" s="23"/>
-      <c r="D81" s="23"/>
-      <c r="E81" s="23"/>
-      <c r="F81" s="23"/>
-      <c r="G81" s="23"/>
-      <c r="H81" s="23"/>
-      <c r="I81" s="23"/>
-      <c r="J81" s="23"/>
-      <c r="K81" s="23"/>
-      <c r="L81" s="23"/>
-      <c r="M81" s="23"/>
-      <c r="N81" s="23"/>
-    </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B82" s="23"/>
-      <c r="C82" s="23"/>
-      <c r="D82" s="23"/>
-      <c r="E82" s="23"/>
-      <c r="F82" s="23"/>
-      <c r="G82" s="23"/>
-      <c r="H82" s="23"/>
-      <c r="I82" s="23"/>
-      <c r="J82" s="23"/>
-      <c r="K82" s="23"/>
-      <c r="L82" s="23"/>
-      <c r="M82" s="23"/>
-      <c r="N82" s="23"/>
-    </row>
-    <row r="83" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B83" s="52" t="s">
-        <v>499</v>
-      </c>
-      <c r="C83" s="23"/>
-      <c r="D83" s="23"/>
-      <c r="E83" s="23"/>
-      <c r="F83" s="23"/>
-      <c r="G83" s="23"/>
-      <c r="H83" s="23"/>
-      <c r="I83" s="23"/>
-      <c r="J83" s="23"/>
-      <c r="K83" s="23"/>
-      <c r="L83" s="23"/>
-      <c r="M83" s="23"/>
-      <c r="N83" s="23"/>
-    </row>
-    <row r="84" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B84" s="53" t="s">
-        <v>500</v>
-      </c>
-      <c r="C84" s="57" t="s">
-        <v>501</v>
-      </c>
-      <c r="D84" s="57" t="s">
-        <v>502</v>
-      </c>
-      <c r="E84" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="F84" s="54" t="s">
-        <v>504</v>
-      </c>
-      <c r="G84" s="54" t="s">
-        <v>505</v>
-      </c>
-      <c r="H84" s="23"/>
-      <c r="I84" s="23"/>
-      <c r="J84" s="23"/>
-      <c r="K84" s="23"/>
-      <c r="L84" s="23"/>
-      <c r="M84" s="23"/>
-      <c r="N84" s="23"/>
-    </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B85" s="23" t="s">
-        <v>506</v>
-      </c>
-      <c r="C85" s="23"/>
-      <c r="D85" s="23"/>
-      <c r="E85" s="23"/>
-      <c r="F85" s="23"/>
-      <c r="G85" s="23"/>
-      <c r="H85" s="23"/>
-      <c r="I85" s="23"/>
-      <c r="J85" s="23"/>
-      <c r="K85" s="23"/>
-      <c r="L85" s="23"/>
-      <c r="M85" s="23"/>
-      <c r="N85" s="23"/>
-    </row>
-    <row r="86" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B86" s="23"/>
-      <c r="C86" s="77" t="s">
-        <v>507</v>
-      </c>
-      <c r="D86" s="75"/>
-      <c r="E86" s="75"/>
-      <c r="F86" s="75"/>
-      <c r="G86" s="23"/>
-      <c r="H86" s="23"/>
-      <c r="I86" s="23"/>
-      <c r="J86" s="23"/>
-      <c r="K86" s="23"/>
-      <c r="L86" s="23"/>
-      <c r="M86" s="23"/>
-      <c r="N86" s="23"/>
-    </row>
-    <row r="87" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B87" s="23"/>
-      <c r="C87" s="75"/>
-      <c r="D87" s="75"/>
-      <c r="E87" s="75"/>
-      <c r="F87" s="75"/>
-      <c r="G87" s="23"/>
-      <c r="H87" s="23"/>
-      <c r="I87" s="23"/>
-      <c r="J87" s="23"/>
-      <c r="K87" s="23"/>
-      <c r="L87" s="23"/>
-      <c r="M87" s="23"/>
-      <c r="N87" s="23"/>
-    </row>
-    <row r="88" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B88" s="23"/>
-      <c r="C88" s="75"/>
-      <c r="D88" s="75"/>
-      <c r="E88" s="75"/>
-      <c r="F88" s="75"/>
-      <c r="G88" s="23"/>
-      <c r="H88" s="23"/>
-      <c r="I88" s="23"/>
-      <c r="J88" s="23"/>
-      <c r="K88" s="23"/>
-      <c r="L88" s="23"/>
-      <c r="M88" s="23"/>
-      <c r="N88" s="23"/>
-    </row>
-    <row r="89" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B89" s="23"/>
-      <c r="C89" s="75"/>
-      <c r="D89" s="75"/>
-      <c r="E89" s="75"/>
-      <c r="F89" s="75"/>
-      <c r="G89" s="23"/>
-      <c r="H89" s="23"/>
-      <c r="I89" s="23"/>
-      <c r="J89" s="23"/>
-      <c r="K89" s="23"/>
-      <c r="L89" s="23"/>
-      <c r="M89" s="23"/>
-      <c r="N89" s="23"/>
-    </row>
-    <row r="90" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B90" s="23"/>
-      <c r="C90" s="23"/>
-      <c r="D90" s="23"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="23"/>
-      <c r="G90" s="23"/>
-      <c r="H90" s="23"/>
-      <c r="I90" s="23"/>
-      <c r="J90" s="23"/>
-      <c r="K90" s="23"/>
-      <c r="L90" s="23"/>
-      <c r="M90" s="23"/>
-      <c r="N90" s="23"/>
-    </row>
-    <row r="91" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B91" s="52" t="s">
-        <v>508</v>
-      </c>
-      <c r="C91" s="23"/>
-      <c r="D91" s="23"/>
-      <c r="E91" s="23"/>
-      <c r="F91" s="23"/>
-      <c r="G91" s="23"/>
-      <c r="H91" s="23"/>
-      <c r="I91" s="23"/>
-      <c r="J91" s="23"/>
-      <c r="K91" s="23"/>
-      <c r="L91" s="23"/>
-      <c r="M91" s="23"/>
-      <c r="N91" s="23"/>
-    </row>
-    <row r="92" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B92" s="53" t="s">
-        <v>509</v>
-      </c>
-      <c r="C92" s="55" t="s">
-        <v>510</v>
-      </c>
-      <c r="D92" s="23"/>
-      <c r="E92" s="23"/>
-      <c r="F92" s="23"/>
-      <c r="G92" s="23"/>
-      <c r="H92" s="23"/>
-      <c r="I92" s="23"/>
-      <c r="J92" s="23"/>
-      <c r="K92" s="23"/>
-      <c r="L92" s="23"/>
-      <c r="M92" s="23"/>
-      <c r="N92" s="23"/>
-    </row>
-    <row r="93" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B93" s="80" t="s">
-        <v>511</v>
-      </c>
-      <c r="C93" s="80"/>
-      <c r="D93" s="23"/>
-      <c r="E93" s="23"/>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
-      <c r="H93" s="23"/>
-      <c r="I93" s="23"/>
-      <c r="J93" s="23"/>
-      <c r="K93" s="23"/>
-      <c r="L93" s="23"/>
-      <c r="M93" s="23"/>
-      <c r="N93" s="23"/>
-    </row>
-    <row r="94" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B94" s="75"/>
-      <c r="C94" s="75"/>
-      <c r="D94" s="23"/>
-      <c r="E94" s="23"/>
-      <c r="F94" s="23"/>
-      <c r="G94" s="23"/>
-      <c r="H94" s="23"/>
-      <c r="I94" s="23"/>
-      <c r="J94" s="23"/>
-      <c r="K94" s="23"/>
-      <c r="L94" s="23"/>
-      <c r="M94" s="23"/>
-      <c r="N94" s="23"/>
-    </row>
-    <row r="95" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B95" s="75"/>
-      <c r="C95" s="75"/>
-      <c r="D95" s="23"/>
-      <c r="E95" s="23"/>
-      <c r="F95" s="23"/>
-      <c r="G95" s="23"/>
-      <c r="H95" s="23"/>
-      <c r="I95" s="23"/>
-      <c r="J95" s="23"/>
-      <c r="K95" s="23"/>
-      <c r="L95" s="23"/>
-      <c r="M95" s="23"/>
-      <c r="N95" s="23"/>
-    </row>
-    <row r="96" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B96" s="23"/>
-      <c r="C96" s="23"/>
-      <c r="D96" s="23"/>
-      <c r="E96" s="23"/>
-      <c r="F96" s="23"/>
-      <c r="G96" s="23"/>
-      <c r="H96" s="23"/>
-      <c r="I96" s="23"/>
-      <c r="J96" s="23"/>
-      <c r="K96" s="23"/>
-      <c r="L96" s="23"/>
-      <c r="M96" s="23"/>
-      <c r="N96" s="23"/>
-    </row>
-    <row r="97" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B97" s="52" t="s">
-        <v>512</v>
-      </c>
-      <c r="C97" s="23"/>
-      <c r="D97" s="23"/>
-      <c r="E97" s="23"/>
-      <c r="F97" s="23"/>
-      <c r="G97" s="23"/>
-      <c r="H97" s="23"/>
-      <c r="I97" s="23"/>
-      <c r="J97" s="23"/>
-      <c r="K97" s="23"/>
-      <c r="L97" s="23"/>
-      <c r="M97" s="23"/>
-      <c r="N97" s="23"/>
-    </row>
-    <row r="98" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B98" s="53" t="s">
-        <v>513</v>
-      </c>
-      <c r="C98" s="53" t="s">
-        <v>514</v>
-      </c>
-      <c r="D98" s="54" t="s">
-        <v>515</v>
-      </c>
-      <c r="E98" s="23"/>
-      <c r="F98" s="52" t="s">
-        <v>516</v>
-      </c>
-      <c r="G98" s="23"/>
-      <c r="H98" s="23"/>
-      <c r="I98" s="23"/>
-      <c r="J98" s="23"/>
-      <c r="K98" s="23"/>
-      <c r="L98" s="23"/>
-      <c r="M98" s="23"/>
-      <c r="N98" s="23"/>
-    </row>
-    <row r="99" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B99" s="76" t="s">
-        <v>517</v>
-      </c>
-      <c r="C99" s="76"/>
-      <c r="D99" s="76"/>
-      <c r="E99" s="23"/>
-      <c r="F99" s="53" t="s">
-        <v>278</v>
-      </c>
-      <c r="G99" s="53" t="s">
-        <v>518</v>
-      </c>
-      <c r="H99" s="55" t="s">
-        <v>519</v>
-      </c>
-      <c r="I99" s="54" t="s">
-        <v>520</v>
-      </c>
-      <c r="J99" s="23"/>
-      <c r="K99" s="23"/>
-      <c r="L99" s="23"/>
-      <c r="M99" s="23"/>
-      <c r="N99" s="23"/>
-    </row>
-    <row r="100" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B100" s="76"/>
-      <c r="C100" s="76"/>
-      <c r="D100" s="76"/>
-      <c r="E100" s="23"/>
-      <c r="F100" s="21"/>
-      <c r="G100" s="21"/>
-      <c r="H100" s="21"/>
-      <c r="I100" s="21"/>
-      <c r="J100" s="23"/>
-      <c r="K100" s="23"/>
-      <c r="L100" s="23"/>
-      <c r="M100" s="23"/>
-      <c r="N100" s="23"/>
-    </row>
-    <row r="101" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B101" s="76"/>
-      <c r="C101" s="76"/>
-      <c r="D101" s="76"/>
-      <c r="E101" s="23"/>
-      <c r="F101" s="65" t="s">
-        <v>521</v>
-      </c>
-      <c r="G101" s="21"/>
-      <c r="H101" s="21" t="s">
-        <v>457</v>
-      </c>
-      <c r="I101" s="21" t="s">
-        <v>522</v>
-      </c>
-      <c r="J101" s="23"/>
-      <c r="K101" s="23"/>
-      <c r="L101" s="23"/>
-      <c r="M101" s="23"/>
-      <c r="N101" s="23"/>
-    </row>
-    <row r="102" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B102" s="21">
-        <v>1</v>
-      </c>
-      <c r="C102" s="21">
-        <v>1</v>
-      </c>
-      <c r="D102" s="21">
-        <v>2</v>
-      </c>
-      <c r="E102" s="23"/>
-      <c r="F102" s="65" t="s">
-        <v>523</v>
-      </c>
-      <c r="G102" s="21"/>
-      <c r="H102" s="21" t="s">
-        <v>524</v>
-      </c>
-      <c r="I102" s="56" t="s">
-        <v>525</v>
-      </c>
-      <c r="J102" s="23"/>
-      <c r="K102" s="23"/>
-      <c r="L102" s="23"/>
-      <c r="M102" s="23"/>
-      <c r="N102" s="23"/>
-    </row>
-    <row r="103" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B103" s="21">
-        <v>1</v>
-      </c>
-      <c r="C103" s="21">
-        <v>3</v>
-      </c>
-      <c r="D103" s="21">
-        <v>4</v>
-      </c>
-      <c r="E103" s="23"/>
-      <c r="F103" s="65" t="s">
-        <v>526</v>
-      </c>
-      <c r="G103" s="21"/>
-      <c r="H103" s="21" t="s">
-        <v>527</v>
-      </c>
-      <c r="I103" s="56" t="s">
-        <v>525</v>
-      </c>
-      <c r="J103" s="23"/>
-      <c r="K103" s="23"/>
-      <c r="L103" s="23"/>
-      <c r="M103" s="23"/>
-      <c r="N103" s="23"/>
-    </row>
-    <row r="104" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B104" s="21">
-        <v>2</v>
-      </c>
-      <c r="C104" s="21">
-        <v>4</v>
-      </c>
-      <c r="D104" s="21">
-        <v>2</v>
-      </c>
-      <c r="E104" s="23"/>
-      <c r="F104" s="65" t="s">
-        <v>528</v>
-      </c>
-      <c r="G104" s="21"/>
-      <c r="H104" s="21" t="s">
-        <v>529</v>
-      </c>
-      <c r="I104" s="56" t="s">
-        <v>525</v>
-      </c>
-      <c r="J104" s="23"/>
-      <c r="K104" s="23"/>
-      <c r="L104" s="23"/>
-      <c r="M104" s="23"/>
-      <c r="N104" s="23"/>
-    </row>
-    <row r="105" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B105" s="21">
-        <v>2</v>
-      </c>
-      <c r="C105" s="21">
-        <v>5</v>
-      </c>
-      <c r="D105" s="21">
-        <v>2</v>
-      </c>
-      <c r="E105" s="23"/>
-      <c r="F105" s="65" t="s">
-        <v>530</v>
-      </c>
-      <c r="G105" s="21"/>
-      <c r="H105" s="21" t="s">
-        <v>531</v>
-      </c>
-      <c r="I105" s="21"/>
-      <c r="J105" s="23"/>
-      <c r="K105" s="23"/>
-      <c r="L105" s="23"/>
-      <c r="M105" s="23"/>
-      <c r="N105" s="23"/>
-    </row>
-    <row r="106" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B106" s="21">
-        <v>3</v>
-      </c>
-      <c r="C106" s="21">
-        <v>6</v>
-      </c>
-      <c r="D106" s="21">
-        <v>4</v>
-      </c>
-      <c r="E106" s="23"/>
-      <c r="F106" s="21"/>
-      <c r="G106" s="21"/>
-      <c r="H106" s="21"/>
-      <c r="I106" s="21"/>
-      <c r="J106" s="23"/>
-      <c r="K106" s="23"/>
-      <c r="L106" s="23"/>
-      <c r="M106" s="23"/>
-      <c r="N106" s="23"/>
-    </row>
-    <row r="107" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B107" s="21">
-        <v>3</v>
-      </c>
-      <c r="C107" s="21">
-        <v>2</v>
-      </c>
-      <c r="D107" s="21">
-        <v>4</v>
-      </c>
-      <c r="E107" s="23"/>
-      <c r="F107" s="23"/>
-      <c r="G107" s="23"/>
-      <c r="H107" s="23"/>
-      <c r="I107" s="23"/>
-      <c r="J107" s="23"/>
-      <c r="K107" s="23"/>
-      <c r="L107" s="23"/>
-      <c r="M107" s="23"/>
-      <c r="N107" s="23"/>
-    </row>
-    <row r="108" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B108" s="21">
-        <v>4</v>
-      </c>
-      <c r="C108" s="21">
-        <v>8</v>
-      </c>
-      <c r="D108" s="21">
-        <v>2</v>
-      </c>
-      <c r="E108" s="23"/>
-      <c r="F108" s="23"/>
-      <c r="G108" s="23"/>
-      <c r="H108" s="23"/>
-      <c r="I108" s="23"/>
-      <c r="J108" s="23"/>
-      <c r="K108" s="23"/>
-      <c r="L108" s="23"/>
-      <c r="M108" s="23"/>
-      <c r="N108" s="23"/>
-    </row>
-    <row r="109" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B109" s="21">
-        <v>4</v>
-      </c>
-      <c r="C109" s="21">
-        <v>12</v>
-      </c>
-      <c r="D109" s="21">
-        <v>4</v>
-      </c>
-      <c r="E109" s="23"/>
-      <c r="F109" s="23"/>
-      <c r="G109" s="23"/>
-      <c r="H109" s="23"/>
-      <c r="I109" s="23"/>
-      <c r="J109" s="23"/>
-      <c r="K109" s="23"/>
-      <c r="L109" s="23"/>
-      <c r="M109" s="23"/>
-      <c r="N109" s="23"/>
-    </row>
-    <row r="110" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B110" s="21">
-        <v>5</v>
-      </c>
-      <c r="C110" s="21">
-        <v>88</v>
-      </c>
-      <c r="D110" s="21">
-        <v>1</v>
-      </c>
-      <c r="E110" s="23"/>
-      <c r="F110" s="23"/>
-      <c r="G110" s="23"/>
-      <c r="H110" s="23"/>
-      <c r="I110" s="23"/>
-      <c r="J110" s="23"/>
-      <c r="K110" s="23"/>
-      <c r="L110" s="23"/>
-      <c r="M110" s="23"/>
-      <c r="N110" s="23"/>
-    </row>
-    <row r="111" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B111" s="21">
-        <v>5</v>
-      </c>
-      <c r="C111" s="21">
-        <v>22</v>
-      </c>
-      <c r="D111" s="21">
-        <v>3</v>
-      </c>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
-      <c r="G111" s="23"/>
-      <c r="H111" s="23"/>
-      <c r="I111" s="23"/>
-      <c r="J111" s="23"/>
-      <c r="K111" s="23"/>
-      <c r="L111" s="23"/>
-      <c r="M111" s="23"/>
-      <c r="N111" s="23"/>
-    </row>
-    <row r="112" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B112" s="21">
-        <v>5</v>
-      </c>
-      <c r="C112" s="21">
-        <v>11</v>
-      </c>
-      <c r="D112" s="21">
-        <v>1</v>
-      </c>
-      <c r="E112" s="23"/>
-      <c r="F112" s="23"/>
-      <c r="G112" s="23"/>
-      <c r="H112" s="23"/>
-      <c r="I112" s="23"/>
-      <c r="J112" s="23"/>
-      <c r="K112" s="23"/>
-      <c r="L112" s="23"/>
-      <c r="M112" s="23"/>
-      <c r="N112" s="23"/>
-    </row>
-    <row r="113" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B113" s="21">
-        <v>5</v>
-      </c>
-      <c r="C113" s="21">
-        <v>33</v>
-      </c>
-      <c r="D113" s="21">
-        <v>1</v>
-      </c>
-      <c r="E113" s="23"/>
-      <c r="F113" s="23"/>
-      <c r="G113" s="23"/>
-      <c r="H113" s="23"/>
-      <c r="I113" s="23"/>
-      <c r="J113" s="23"/>
-      <c r="K113" s="23"/>
-      <c r="L113" s="23"/>
-      <c r="M113" s="23"/>
-      <c r="N113" s="23"/>
-    </row>
-    <row r="114" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B114" s="21">
-        <v>6</v>
-      </c>
-      <c r="C114" s="21">
-        <v>2</v>
-      </c>
-      <c r="D114" s="21">
-        <v>1</v>
-      </c>
-      <c r="E114" s="23"/>
-      <c r="F114" s="23"/>
-      <c r="G114" s="23"/>
-      <c r="H114" s="23"/>
-      <c r="I114" s="23"/>
-      <c r="J114" s="23"/>
-      <c r="K114" s="23"/>
-      <c r="L114" s="23"/>
-      <c r="M114" s="23"/>
-      <c r="N114" s="23"/>
-    </row>
-    <row r="115" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B115" s="21">
-        <v>7</v>
-      </c>
-      <c r="C115" s="21">
-        <v>1</v>
-      </c>
-      <c r="D115" s="21">
-        <v>2</v>
-      </c>
-      <c r="E115" s="23"/>
-      <c r="F115" s="23"/>
-      <c r="G115" s="23"/>
-      <c r="H115" s="23"/>
-      <c r="I115" s="23"/>
-      <c r="J115" s="23"/>
-      <c r="K115" s="23"/>
-      <c r="L115" s="23"/>
-      <c r="M115" s="23"/>
-      <c r="N115" s="23"/>
-    </row>
-    <row r="116" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B116" s="21">
-        <v>8</v>
-      </c>
-      <c r="C116" s="21">
-        <v>27</v>
-      </c>
-      <c r="D116" s="21">
-        <v>1</v>
-      </c>
-      <c r="E116" s="23"/>
-      <c r="F116" s="23"/>
-      <c r="G116" s="23"/>
-      <c r="H116" s="23"/>
-      <c r="I116" s="23"/>
-      <c r="J116" s="23"/>
-      <c r="K116" s="23"/>
-      <c r="L116" s="23"/>
-      <c r="M116" s="23"/>
-      <c r="N116" s="23"/>
-    </row>
-    <row r="117" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B117" s="21">
-        <v>8</v>
-      </c>
-      <c r="C117" s="21">
-        <v>23</v>
-      </c>
-      <c r="D117" s="21">
-        <v>1</v>
-      </c>
-      <c r="E117" s="23"/>
-      <c r="F117" s="23"/>
-      <c r="G117" s="23"/>
-      <c r="H117" s="23"/>
-      <c r="I117" s="23"/>
-      <c r="J117" s="23"/>
-      <c r="K117" s="23"/>
-      <c r="L117" s="23"/>
-      <c r="M117" s="23"/>
-      <c r="N117" s="23"/>
-    </row>
-    <row r="118" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B118" s="21">
-        <v>8</v>
-      </c>
-      <c r="C118" s="21">
-        <v>98</v>
-      </c>
-      <c r="D118" s="21">
-        <v>2</v>
-      </c>
-      <c r="E118" s="23"/>
-      <c r="F118" s="23"/>
-      <c r="G118" s="23"/>
-      <c r="H118" s="23"/>
-      <c r="I118" s="23"/>
-      <c r="J118" s="23"/>
-      <c r="K118" s="23"/>
-      <c r="L118" s="23"/>
-      <c r="M118" s="23"/>
-      <c r="N118" s="23"/>
-    </row>
-    <row r="119" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B119" s="21">
-        <v>9</v>
-      </c>
-      <c r="C119" s="21">
-        <v>100</v>
-      </c>
-      <c r="D119" s="21">
-        <v>6</v>
-      </c>
-      <c r="E119" s="23"/>
-      <c r="F119" s="23"/>
-      <c r="G119" s="23"/>
-      <c r="H119" s="23"/>
-      <c r="I119" s="23"/>
-      <c r="J119" s="23"/>
-      <c r="K119" s="23"/>
-      <c r="L119" s="23"/>
-      <c r="M119" s="23"/>
-      <c r="N119" s="23"/>
-    </row>
-    <row r="120" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B120" s="21">
-        <v>9</v>
-      </c>
-      <c r="C120" s="21">
-        <v>11</v>
-      </c>
-      <c r="D120" s="21">
-        <v>7</v>
-      </c>
-      <c r="E120" s="23"/>
-      <c r="F120" s="23"/>
-      <c r="G120" s="23"/>
-      <c r="H120" s="23"/>
-      <c r="I120" s="23"/>
-      <c r="J120" s="23"/>
-      <c r="K120" s="23"/>
-      <c r="L120" s="23"/>
-      <c r="M120" s="23"/>
-      <c r="N120" s="23"/>
-    </row>
-    <row r="121" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B121" s="21">
-        <v>9</v>
-      </c>
-      <c r="C121" s="21">
-        <v>45</v>
-      </c>
-      <c r="D121" s="21">
-        <v>2</v>
-      </c>
-      <c r="E121" s="23"/>
-      <c r="F121" s="23"/>
-      <c r="G121" s="23"/>
-      <c r="H121" s="23"/>
-      <c r="I121" s="23"/>
-      <c r="J121" s="23"/>
-      <c r="K121" s="23"/>
-      <c r="L121" s="23"/>
-      <c r="M121" s="23"/>
-      <c r="N121" s="23"/>
-    </row>
-    <row r="122" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B122" s="21">
-        <v>9</v>
-      </c>
-      <c r="C122" s="21">
-        <v>22</v>
-      </c>
-      <c r="D122" s="21">
-        <v>2</v>
-      </c>
-      <c r="E122" s="23"/>
-      <c r="F122" s="23"/>
-      <c r="G122" s="23"/>
-      <c r="H122" s="23"/>
-      <c r="I122" s="23"/>
-      <c r="J122" s="23"/>
-      <c r="K122" s="23"/>
-      <c r="L122" s="23"/>
-      <c r="M122" s="23"/>
-      <c r="N122" s="23"/>
-    </row>
-    <row r="123" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B123" s="21">
-        <v>9</v>
-      </c>
-      <c r="C123" s="21">
-        <v>32</v>
-      </c>
-      <c r="D123" s="21">
-        <v>1</v>
-      </c>
-      <c r="E123" s="23"/>
-      <c r="F123" s="23"/>
-      <c r="G123" s="23"/>
-      <c r="H123" s="23"/>
-      <c r="I123" s="23"/>
-      <c r="J123" s="23"/>
-      <c r="K123" s="23"/>
-      <c r="L123" s="23"/>
-      <c r="M123" s="23"/>
-      <c r="N123" s="23"/>
-    </row>
-    <row r="124" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B124" s="21">
-        <v>10</v>
-      </c>
-      <c r="C124" s="21">
-        <v>18</v>
-      </c>
-      <c r="D124" s="21">
-        <v>2</v>
-      </c>
-      <c r="E124" s="23"/>
-      <c r="F124" s="23"/>
-      <c r="G124" s="23"/>
-      <c r="H124" s="23"/>
-      <c r="I124" s="23"/>
-      <c r="J124" s="23"/>
-      <c r="K124" s="23"/>
-      <c r="L124" s="23"/>
-      <c r="M124" s="23"/>
-      <c r="N124" s="23"/>
-    </row>
-    <row r="125" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B125" s="21">
-        <v>10</v>
-      </c>
-      <c r="C125" s="21">
-        <v>29</v>
-      </c>
-      <c r="D125" s="21">
-        <v>4</v>
-      </c>
-      <c r="E125" s="23"/>
-      <c r="F125" s="23"/>
-      <c r="G125" s="23"/>
-      <c r="H125" s="23"/>
-      <c r="I125" s="23"/>
-      <c r="J125" s="23"/>
-      <c r="K125" s="23"/>
-      <c r="L125" s="23"/>
-      <c r="M125" s="23"/>
-      <c r="N125" s="23"/>
-    </row>
-    <row r="126" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B126" s="21">
-        <v>11</v>
-      </c>
-      <c r="C126" s="21">
-        <v>33</v>
-      </c>
-      <c r="D126" s="21">
-        <v>2</v>
-      </c>
-      <c r="E126" s="23"/>
-      <c r="F126" s="23"/>
-      <c r="G126" s="23"/>
-      <c r="H126" s="23"/>
-      <c r="I126" s="23"/>
-      <c r="J126" s="23"/>
-      <c r="K126" s="23"/>
-      <c r="L126" s="23"/>
-      <c r="M126" s="23"/>
-      <c r="N126" s="23"/>
-    </row>
-    <row r="127" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B127" s="21">
-        <v>11</v>
-      </c>
-      <c r="C127" s="21">
-        <v>65</v>
-      </c>
-      <c r="D127" s="21">
-        <v>1</v>
-      </c>
-      <c r="E127" s="23"/>
-      <c r="F127" s="23"/>
-      <c r="G127" s="23"/>
-      <c r="H127" s="23"/>
-      <c r="I127" s="23"/>
-      <c r="J127" s="23"/>
-      <c r="K127" s="23"/>
-      <c r="L127" s="23"/>
-      <c r="M127" s="23"/>
-      <c r="N127" s="23"/>
-    </row>
-    <row r="128" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B128" s="21">
-        <v>11</v>
-      </c>
-      <c r="C128" s="21">
-        <v>1</v>
-      </c>
-      <c r="D128" s="21">
-        <v>1</v>
-      </c>
-      <c r="E128" s="23"/>
-      <c r="F128" s="23"/>
-      <c r="G128" s="23"/>
-      <c r="H128" s="23"/>
-      <c r="I128" s="23"/>
-      <c r="J128" s="23"/>
-      <c r="K128" s="23"/>
-      <c r="L128" s="23"/>
-      <c r="M128" s="23"/>
-      <c r="N128" s="23"/>
-    </row>
-    <row r="129" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B129" s="21">
-        <v>11</v>
-      </c>
-      <c r="C129" s="21">
-        <v>2</v>
-      </c>
-      <c r="D129" s="21">
-        <v>2</v>
-      </c>
-      <c r="E129" s="23"/>
-      <c r="F129" s="23"/>
-      <c r="G129" s="23"/>
-      <c r="H129" s="23"/>
-      <c r="I129" s="23"/>
-      <c r="J129" s="23"/>
-      <c r="K129" s="23"/>
-      <c r="L129" s="23"/>
-      <c r="M129" s="23"/>
-      <c r="N129" s="23"/>
-    </row>
-    <row r="130" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B130" s="21">
-        <v>11</v>
-      </c>
-      <c r="C130" s="21">
-        <v>5</v>
-      </c>
-      <c r="D130" s="21">
-        <v>5</v>
-      </c>
-      <c r="E130" s="23"/>
-      <c r="F130" s="23"/>
-      <c r="G130" s="23"/>
-      <c r="H130" s="23"/>
-      <c r="I130" s="23"/>
-      <c r="J130" s="23"/>
-      <c r="K130" s="23"/>
-      <c r="L130" s="23"/>
-      <c r="M130" s="23"/>
-      <c r="N130" s="23"/>
-    </row>
-    <row r="131" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B131" s="21">
-        <v>11</v>
-      </c>
-      <c r="C131" s="21">
-        <v>7</v>
-      </c>
-      <c r="D131" s="21">
-        <v>10</v>
-      </c>
-      <c r="E131" s="23"/>
-      <c r="F131" s="23"/>
-      <c r="G131" s="23"/>
-      <c r="H131" s="23"/>
-      <c r="I131" s="23"/>
-      <c r="J131" s="23"/>
-      <c r="K131" s="23"/>
-      <c r="L131" s="23"/>
-      <c r="M131" s="23"/>
-      <c r="N131" s="23"/>
-    </row>
-    <row r="132" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B132" s="21">
-        <v>12</v>
-      </c>
-      <c r="C132" s="21">
-        <v>55</v>
-      </c>
-      <c r="D132" s="21">
-        <v>1</v>
-      </c>
-      <c r="E132" s="23"/>
-      <c r="F132" s="23"/>
-      <c r="G132" s="23"/>
-      <c r="H132" s="23"/>
-      <c r="I132" s="23"/>
-      <c r="J132" s="23"/>
-      <c r="K132" s="23"/>
-      <c r="L132" s="23"/>
-      <c r="M132" s="23"/>
-      <c r="N132" s="23"/>
-    </row>
-    <row r="133" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B133" s="21">
-        <v>13</v>
-      </c>
-      <c r="C133" s="21">
-        <v>92</v>
-      </c>
-      <c r="D133" s="21">
-        <v>1</v>
-      </c>
-      <c r="E133" s="23"/>
-      <c r="F133" s="23"/>
-      <c r="G133" s="23"/>
-      <c r="H133" s="23"/>
-      <c r="I133" s="23"/>
-      <c r="J133" s="23"/>
-      <c r="K133" s="23"/>
-      <c r="L133" s="23"/>
-      <c r="M133" s="23"/>
-      <c r="N133" s="23"/>
-    </row>
-    <row r="134" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B134" s="21">
-        <v>13</v>
-      </c>
-      <c r="C134" s="21">
-        <v>14</v>
-      </c>
-      <c r="D134" s="21">
-        <v>2</v>
-      </c>
-      <c r="E134" s="23"/>
-      <c r="F134" s="23"/>
-      <c r="G134" s="23"/>
-      <c r="H134" s="23"/>
-      <c r="I134" s="23"/>
-      <c r="J134" s="23"/>
-      <c r="K134" s="23"/>
-      <c r="L134" s="23"/>
-      <c r="M134" s="23"/>
-      <c r="N134" s="23"/>
-    </row>
-    <row r="135" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B135" s="23"/>
-      <c r="C135" s="23"/>
-      <c r="D135" s="23"/>
-      <c r="E135" s="23"/>
-      <c r="F135" s="23"/>
-      <c r="G135" s="23"/>
-      <c r="H135" s="23"/>
-      <c r="I135" s="23"/>
-      <c r="J135" s="23"/>
-      <c r="K135" s="23"/>
-      <c r="L135" s="23"/>
-      <c r="M135" s="23"/>
-      <c r="N135" s="23"/>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="C73:E74"/>
-    <mergeCell ref="C79:D80"/>
-    <mergeCell ref="C86:F89"/>
-    <mergeCell ref="B93:C95"/>
-    <mergeCell ref="B99:D101"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q22:R22"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/1. Database Design/Java23 QuyenPhan Database Design.xlsx
+++ b/1. Database Design/Java23 QuyenPhan Database Design.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java23\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2DA501-580C-443E-9607-72818A602B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E68749-AECD-42AF-B262-33C7D66849E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="588" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="588" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
@@ -2493,6 +2493,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2513,9 +2516,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2911,21 +2911,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A4:L24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="8" width="16.88671875" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
-    <col min="10" max="10" width="18.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="8" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" customWidth="1"/>
-    <col min="13" max="18" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" customWidth="1"/>
+    <col min="13" max="18" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
         <v>118</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>119</v>
       </c>
@@ -3060,7 +3060,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -3090,7 +3090,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
         <v>90</v>
       </c>
@@ -3113,7 +3113,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
         <v>117</v>
       </c>
@@ -3136,7 +3136,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
         <v>116</v>
       </c>
@@ -3159,7 +3159,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="28" t="s">
         <v>115</v>
       </c>
@@ -3176,7 +3176,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
@@ -3190,7 +3190,7 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -3203,7 +3203,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -3216,7 +3216,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -3229,7 +3229,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -3242,7 +3242,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -3255,7 +3255,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -3268,7 +3268,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -3281,12 +3281,12 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="2:12" s="14" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:12" s="14" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3297,27 +3297,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00967ACB-CFA1-460B-A734-E9F64BF353E8}">
   <dimension ref="A2:P58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="9" width="16.88671875" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="13" width="18.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="13" width="18.7109375" customWidth="1"/>
     <col min="14" max="14" width="21" customWidth="1"/>
-    <col min="15" max="15" width="17.44140625" customWidth="1"/>
-    <col min="16" max="16" width="18.33203125" customWidth="1"/>
-    <col min="17" max="21" width="12.6640625" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" customWidth="1"/>
+    <col min="16" max="16" width="18.28515625" customWidth="1"/>
+    <col min="17" max="21" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F2" s="14" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="30" t="s">
         <v>1</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
         <v>118</v>
       </c>
@@ -3449,7 +3449,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>119</v>
       </c>
@@ -3488,7 +3488,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -3521,7 +3521,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
         <v>117</v>
       </c>
@@ -3547,7 +3547,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
         <v>116</v>
       </c>
@@ -3571,7 +3571,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
         <v>115</v>
       </c>
@@ -3595,7 +3595,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
@@ -3615,7 +3615,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -3630,7 +3630,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -3646,7 +3646,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -3662,7 +3662,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -3678,7 +3678,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -3694,7 +3694,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -3710,7 +3710,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -3726,7 +3726,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -3742,12 +3742,12 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>65</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="24" spans="2:16" s="14" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16" s="14" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24"/>
       <c r="C24" t="s">
         <v>66</v>
@@ -3787,7 +3787,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B25" s="8" t="s">
         <v>67</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B26" s="8" t="s">
         <v>68</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>69</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="H28" s="23" t="s">
         <v>139</v>
       </c>
@@ -3884,7 +3884,7 @@
       <c r="O28" s="23"/>
       <c r="P28" s="23"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="H29" s="23" t="s">
         <v>139</v>
       </c>
@@ -3901,7 +3901,7 @@
       <c r="O29" s="23"/>
       <c r="P29" s="23"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="G30" s="31" t="s">
         <v>141</v>
       </c>
@@ -3921,14 +3921,14 @@
       <c r="O30" s="23"/>
       <c r="P30" s="23"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="N31" s="23" t="s">
         <v>101</v>
       </c>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="N32" s="4" t="s">
         <v>102</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="N33" s="4">
         <v>1</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H34" t="s">
         <v>0</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H35" s="28" t="s">
         <v>1</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H36" s="23" t="s">
         <v>132</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H37" s="23" t="s">
         <v>133</v>
       </c>
@@ -4000,7 +4000,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H38" s="23" t="s">
         <v>134</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -4026,7 +4026,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
       <c r="D40" s="23"/>
@@ -4038,7 +4038,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -4050,7 +4050,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42" s="23"/>
       <c r="C42" s="23"/>
       <c r="D42" s="23"/>
@@ -4062,7 +4062,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>160</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
         <v>104</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45" s="23" t="s">
         <v>159</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46" s="23" t="s">
         <v>159</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47" s="23" t="s">
         <v>159</v>
       </c>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="G47" s="23"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48" s="23"/>
       <c r="C48" s="23"/>
       <c r="D48" s="23"/>
@@ -4166,7 +4166,7 @@
       <c r="G48" s="23"/>
       <c r="H48" s="23"/>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
       <c r="D49" s="23"/>
@@ -4175,7 +4175,7 @@
       <c r="G49" s="23"/>
       <c r="H49" s="23"/>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B50" s="23" t="s">
         <v>127</v>
       </c>
@@ -4186,7 +4186,7 @@
       <c r="G50" s="23"/>
       <c r="H50" s="23"/>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
         <v>104</v>
       </c>
@@ -4201,7 +4201,7 @@
       <c r="G51" s="23"/>
       <c r="H51" s="23"/>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B52" s="23" t="s">
         <v>159</v>
       </c>
@@ -4216,7 +4216,7 @@
       <c r="G52" s="23"/>
       <c r="H52" s="23"/>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B53" s="23" t="s">
         <v>161</v>
       </c>
@@ -4231,7 +4231,7 @@
       <c r="G53" s="23"/>
       <c r="H53" s="23"/>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B54" s="23" t="s">
         <v>162</v>
       </c>
@@ -4246,7 +4246,7 @@
       <c r="G54" s="23"/>
       <c r="H54" s="23"/>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
       <c r="D55" s="23"/>
@@ -4255,7 +4255,7 @@
       <c r="G55" s="23"/>
       <c r="H55" s="23"/>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B56" s="23"/>
       <c r="C56" s="23"/>
       <c r="D56" s="23"/>
@@ -4264,7 +4264,7 @@
       <c r="G56" s="23"/>
       <c r="H56" s="23"/>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57" s="23"/>
       <c r="C57" s="23"/>
       <c r="D57" s="23"/>
@@ -4273,7 +4273,7 @@
       <c r="G57" s="23"/>
       <c r="H57" s="23"/>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B58" s="23"/>
       <c r="C58" s="23"/>
       <c r="D58" s="23"/>
@@ -4292,16 +4292,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:U43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" customWidth="1"/>
-    <col min="15" max="15" width="12.5546875" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>76</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -4331,10 +4331,10 @@
       </c>
       <c r="P4" s="25"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="N5" s="25"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>38</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D8" s="4"/>
       <c r="P8" s="17" t="s">
         <v>54</v>
@@ -4355,7 +4355,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>23</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>40</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>58</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>41</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>52</v>
       </c>
@@ -4523,14 +4523,14 @@
       <c r="Q13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="R13" s="62" t="s">
+      <c r="R13" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="S13" s="62"/>
-      <c r="T13" s="62"/>
-      <c r="U13" s="62"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="S13" s="63"/>
+      <c r="T13" s="63"/>
+      <c r="U13" s="63"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D14" s="4"/>
       <c r="O14" s="12" t="s">
         <v>38</v>
@@ -4541,20 +4541,20 @@
       <c r="Q14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="R14" s="62"/>
-      <c r="S14" s="62"/>
-      <c r="T14" s="62"/>
-      <c r="U14" s="62"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R14" s="63"/>
+      <c r="S14" s="63"/>
+      <c r="T14" s="63"/>
+      <c r="U14" s="63"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J16" s="25"/>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>32</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -4585,7 +4585,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>33</v>
       </c>
@@ -4614,7 +4614,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" s="11">
         <v>1</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>49</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <v>3</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="G23" s="4">
         <v>4</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="G24" s="4">
         <v>5</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="G25" s="4">
         <v>6</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="G26" s="4">
         <v>7</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="N27" s="25" t="s">
         <v>1</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>64</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>65</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>66</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31" s="8" t="s">
         <v>67</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" s="8" t="s">
         <v>68</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>69</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="N34">
         <v>3</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>169</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>170</v>
       </c>
@@ -4871,31 +4871,31 @@
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="I37" s="23"/>
       <c r="J37" s="23"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="I38" s="23"/>
       <c r="J38" s="23"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
       <c r="I39" s="23"/>
       <c r="J39" s="23"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="I40" s="23"/>
       <c r="J40" s="23"/>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="I42" s="26"/>
       <c r="J42" s="26"/>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="I43" s="23"/>
       <c r="J43" s="23"/>
     </row>
@@ -4911,27 +4911,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD2C7DF-5616-418E-B427-D50946AF144B}">
   <dimension ref="A2:Q58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="9" width="16.88671875" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="13" width="18.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="13" width="18.7109375" customWidth="1"/>
     <col min="14" max="14" width="21" customWidth="1"/>
-    <col min="15" max="15" width="17.44140625" customWidth="1"/>
-    <col min="16" max="16" width="18.33203125" customWidth="1"/>
-    <col min="17" max="21" width="12.6640625" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" customWidth="1"/>
+    <col min="16" max="16" width="18.28515625" customWidth="1"/>
+    <col min="17" max="21" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F2" s="14" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>141</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -5016,7 +5016,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="30" t="s">
         <v>1</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
         <v>118</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>119</v>
       </c>
@@ -5143,7 +5143,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -5176,7 +5176,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
         <v>117</v>
       </c>
@@ -5202,7 +5202,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
         <v>116</v>
       </c>
@@ -5226,7 +5226,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
         <v>115</v>
       </c>
@@ -5250,7 +5250,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
@@ -5270,7 +5270,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -5285,7 +5285,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -5301,7 +5301,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -5317,7 +5317,7 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -5333,7 +5333,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -5349,7 +5349,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -5365,7 +5365,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -5381,7 +5381,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -5397,12 +5397,12 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C23" s="32" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="24" spans="2:17" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:17" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24"/>
       <c r="C24" s="16" t="s">
         <v>172</v>
@@ -5421,17 +5421,17 @@
       <c r="P24"/>
       <c r="Q24"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C25" s="16" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C27" s="32" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C28" s="16" t="s">
         <v>175</v>
       </c>
@@ -5441,7 +5441,7 @@
       <c r="O28" s="23"/>
       <c r="P28" s="23"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C29" s="16" t="s">
         <v>176</v>
       </c>
@@ -5451,47 +5451,47 @@
       <c r="O29" s="23"/>
       <c r="P29" s="23"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="L30" s="23"/>
       <c r="M30" s="23"/>
       <c r="N30" s="23"/>
       <c r="O30" s="23"/>
       <c r="P30" s="23"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C31" s="32" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C32" s="16" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C33" s="16" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C35" s="32" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C36" s="16" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C37" s="16"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C38" s="16" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="23"/>
       <c r="C39" s="33" t="s">
         <v>183</v>
@@ -5502,23 +5502,23 @@
       <c r="G39" s="23"/>
       <c r="H39" s="23"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G40" s="23"/>
       <c r="H40" s="23"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G41" s="23"/>
       <c r="H41" s="23"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G42" s="23"/>
       <c r="H42" s="23"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G43" s="23"/>
       <c r="H43" s="23"/>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
       <c r="D49" s="23"/>
@@ -5527,32 +5527,32 @@
       <c r="G49" s="23"/>
       <c r="H49" s="23"/>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F50" s="23"/>
       <c r="G50" s="23"/>
       <c r="H50" s="23"/>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F51" s="23"/>
       <c r="G51" s="23"/>
       <c r="H51" s="23"/>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F52" s="23"/>
       <c r="G52" s="23"/>
       <c r="H52" s="23"/>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F53" s="23"/>
       <c r="G53" s="23"/>
       <c r="H53" s="23"/>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F54" s="23"/>
       <c r="G54" s="23"/>
       <c r="H54" s="23"/>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
       <c r="D55" s="23"/>
@@ -5561,7 +5561,7 @@
       <c r="G55" s="23"/>
       <c r="H55" s="23"/>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B56" s="23"/>
       <c r="C56" s="23"/>
       <c r="D56" s="23"/>
@@ -5570,7 +5570,7 @@
       <c r="G56" s="23"/>
       <c r="H56" s="23"/>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57" s="23"/>
       <c r="C57" s="23"/>
       <c r="D57" s="23"/>
@@ -5579,7 +5579,7 @@
       <c r="G57" s="23"/>
       <c r="H57" s="23"/>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B58" s="23"/>
       <c r="C58" s="23"/>
       <c r="D58" s="23"/>
@@ -5598,39 +5598,39 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:T58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="21.109375" customWidth="1"/>
-    <col min="7" max="7" width="29.88671875" customWidth="1"/>
-    <col min="8" max="8" width="24.88671875" customWidth="1"/>
-    <col min="9" max="9" width="21.88671875" customWidth="1"/>
-    <col min="10" max="10" width="21.6640625" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" customWidth="1"/>
+    <col min="7" max="7" width="29.85546875" customWidth="1"/>
+    <col min="8" max="8" width="24.85546875" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" customWidth="1"/>
     <col min="12" max="12" width="26" customWidth="1"/>
-    <col min="13" max="13" width="27.6640625" customWidth="1"/>
-    <col min="14" max="14" width="30.88671875" customWidth="1"/>
-    <col min="15" max="17" width="22.6640625" customWidth="1"/>
-    <col min="18" max="18" width="26.33203125" customWidth="1"/>
-    <col min="19" max="19" width="35.109375" customWidth="1"/>
-    <col min="20" max="20" width="21.5546875" customWidth="1"/>
-    <col min="21" max="22" width="12.6640625" customWidth="1"/>
+    <col min="13" max="13" width="27.7109375" customWidth="1"/>
+    <col min="14" max="14" width="30.85546875" customWidth="1"/>
+    <col min="15" max="17" width="22.7109375" customWidth="1"/>
+    <col min="18" max="18" width="26.28515625" customWidth="1"/>
+    <col min="19" max="19" width="35.140625" customWidth="1"/>
+    <col min="20" max="20" width="21.5703125" customWidth="1"/>
+    <col min="21" max="22" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>188</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-    </row>
-    <row r="3" spans="2:20" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+    </row>
+    <row r="3" spans="2:20" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D3" s="23" t="s">
         <v>206</v>
       </c>
@@ -5640,62 +5640,62 @@
         <v>287</v>
       </c>
     </row>
-    <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="69" t="s">
+    <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="69" t="s">
+      <c r="C4" s="62" t="s">
         <v>196</v>
       </c>
-      <c r="D4" s="69" t="s">
+      <c r="D4" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="E4" s="69" t="s">
+      <c r="E4" s="62" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="62" t="s">
         <v>229</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="62" t="s">
         <v>236</v>
       </c>
-      <c r="I4" s="69" t="s">
+      <c r="I4" s="62" t="s">
         <v>266</v>
       </c>
       <c r="J4" s="1"/>
-      <c r="K4" s="69" t="s">
+      <c r="K4" s="62" t="s">
         <v>244</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="62" t="s">
         <v>247</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="62" t="s">
         <v>261</v>
       </c>
       <c r="O4" s="1"/>
-      <c r="P4" s="1" t="s">
+      <c r="P4" s="62" t="s">
         <v>273</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="Q4" s="62" t="s">
         <v>306</v>
       </c>
-      <c r="R4" s="69" t="s">
+      <c r="R4" s="62" t="s">
         <v>288</v>
       </c>
-      <c r="S4" s="69" t="s">
+      <c r="S4" s="62" t="s">
         <v>297</v>
       </c>
-      <c r="T4" s="69" t="s">
+      <c r="T4" s="62" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="36" t="s">
         <v>190</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>191</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="38" t="s">
         <v>217</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>417</v>
       </c>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="T8" s="2"/>
     </row>
-    <row r="9" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="38"/>
       <c r="C9" s="34"/>
       <c r="D9" s="2" t="s">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="28"/>
       <c r="C10" s="34"/>
       <c r="D10" s="2" t="s">
@@ -5951,7 +5951,7 @@
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="28"/>
       <c r="C11" s="34"/>
       <c r="D11" s="2"/>
@@ -5978,7 +5978,7 @@
       <c r="S11" s="38"/>
       <c r="T11" s="38"/>
     </row>
-    <row r="12" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="34"/>
       <c r="C12" s="34"/>
       <c r="D12" s="2"/>
@@ -6005,7 +6005,7 @@
       <c r="S12" s="38"/>
       <c r="T12" s="38"/>
     </row>
-    <row r="13" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
       <c r="D13" s="2"/>
@@ -6029,7 +6029,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
       <c r="D14" s="2"/>
@@ -6054,7 +6054,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
       <c r="D15" s="2"/>
@@ -6075,7 +6075,7 @@
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
     </row>
-    <row r="16" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="34"/>
       <c r="C16" s="34"/>
       <c r="D16" s="2"/>
@@ -6096,7 +6096,7 @@
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
     </row>
-    <row r="17" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
       <c r="D17" s="2"/>
@@ -6117,7 +6117,7 @@
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
     </row>
-    <row r="18" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
       <c r="D18" s="2"/>
@@ -6138,7 +6138,7 @@
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
     </row>
-    <row r="19" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
       <c r="D19" s="2"/>
@@ -6159,7 +6159,7 @@
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
     </row>
-    <row r="20" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
       <c r="D20" s="2"/>
@@ -6180,27 +6180,27 @@
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="I21" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="I22" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="I23" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="I24" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>184</v>
       </c>
@@ -6210,15 +6210,15 @@
       <c r="I25" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="J25" s="63" t="s">
+      <c r="J25" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="K25" s="63"/>
+      <c r="K25" s="64"/>
       <c r="N25" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>185</v>
       </c>
@@ -6241,7 +6241,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>186</v>
       </c>
@@ -6265,7 +6265,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>192</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" s="16" t="s">
         <v>187</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="F30" t="s">
         <v>221</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="F31" s="15" t="s">
         <v>222</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="F32" s="15">
         <v>1</v>
       </c>
@@ -6363,7 +6363,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="40" t="s">
         <v>250</v>
       </c>
@@ -6389,7 +6389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="40" t="s">
         <v>251</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="43">
         <v>1</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="43">
         <v>1</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="43">
         <v>1</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="43">
         <v>2</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="43">
         <v>2</v>
       </c>
@@ -6541,7 +6541,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="43">
         <v>2</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="43">
         <v>2</v>
       </c>
@@ -6595,7 +6595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="43"/>
       <c r="C42" s="43"/>
       <c r="D42" s="43"/>
@@ -6614,7 +6614,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="44"/>
       <c r="C43" s="44"/>
       <c r="D43" s="44"/>
@@ -6631,7 +6631,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="42"/>
       <c r="C44" s="42"/>
       <c r="D44" s="42"/>
@@ -6648,7 +6648,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F45" s="15">
         <v>2</v>
       </c>
@@ -6661,7 +6661,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F46" s="15">
         <v>2</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F47" s="15">
         <v>2</v>
       </c>
@@ -6687,42 +6687,42 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E49" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E50" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E51" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E53" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E54" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E56" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E57" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E58" t="s">
         <v>305</v>
       </c>
@@ -6748,19 +6748,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E46F37-4B03-4545-ABD0-F1F3CE57095A}">
   <dimension ref="A3:L201"/>
-  <sheetFormatPr defaultColWidth="30.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="30.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="10" max="10" width="37.44140625" customWidth="1"/>
-    <col min="11" max="11" width="34.88671875" customWidth="1"/>
+    <col min="10" max="10" width="37.42578125" customWidth="1"/>
+    <col min="11" max="11" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="47" t="s">
         <v>418</v>
       </c>
       <c r="C3" s="23"/>
     </row>
-    <row r="4" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="48" t="s">
         <v>419</v>
       </c>
@@ -6774,7 +6774,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
-    <row r="5" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="21">
         <v>1</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="21">
         <v>2</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="21">
         <v>3</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="21">
         <v>4</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="21">
         <v>5</v>
       </c>
@@ -6874,7 +6874,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="21">
         <v>6</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="21">
         <v>7</v>
       </c>
@@ -6914,7 +6914,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G12" s="21">
         <v>7</v>
       </c>
@@ -6928,7 +6928,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G13" s="21">
         <v>8</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="14" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B14" s="47" t="s">
         <v>189</v>
       </c>
@@ -6962,7 +6962,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B15" s="48" t="s">
         <v>190</v>
       </c>
@@ -6988,7 +6988,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="21">
         <v>1</v>
       </c>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="E16" s="21"/>
     </row>
-    <row r="17" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="21">
         <v>2</v>
       </c>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="H17" s="23"/>
     </row>
-    <row r="18" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="21">
         <v>3</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="21">
         <v>4</v>
       </c>
@@ -7052,13 +7052,13 @@
         <v>2</v>
       </c>
       <c r="E19" s="21"/>
-      <c r="G19" s="68" t="s">
+      <c r="G19" s="69" t="s">
         <v>423</v>
       </c>
-      <c r="H19" s="68"/>
-      <c r="I19" s="68"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="21">
         <v>5</v>
       </c>
@@ -7069,11 +7069,11 @@
         <v>2</v>
       </c>
       <c r="E20" s="21"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="21">
         <v>6</v>
       </c>
@@ -7084,11 +7084,11 @@
         <v>3</v>
       </c>
       <c r="E21" s="21"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="66"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="21">
         <v>7</v>
       </c>
@@ -7099,11 +7099,11 @@
         <v>3</v>
       </c>
       <c r="E22" s="21"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="21">
         <v>8</v>
       </c>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="E23" s="21"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="21">
         <v>9</v>
       </c>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B25" s="21">
         <v>10</v>
       </c>
@@ -7149,7 +7149,7 @@
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
     </row>
-    <row r="26" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="21">
         <v>11</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="21">
         <v>12</v>
       </c>
@@ -7199,7 +7199,7 @@
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="21">
         <v>13</v>
       </c>
@@ -7211,15 +7211,15 @@
       </c>
       <c r="E28" s="21"/>
       <c r="G28" s="23"/>
-      <c r="H28" s="66" t="s">
+      <c r="H28" s="67" t="s">
         <v>421</v>
       </c>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="67"/>
       <c r="L28" s="23"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="21">
         <v>14</v>
       </c>
@@ -7231,13 +7231,13 @@
       </c>
       <c r="E29" s="21"/>
       <c r="G29" s="23"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="66"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
       <c r="L29" s="23"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="21">
         <v>15</v>
       </c>
@@ -7249,13 +7249,13 @@
       </c>
       <c r="E30" s="21"/>
       <c r="G30" s="23"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="66"/>
-      <c r="K30" s="66"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="67"/>
       <c r="L30" s="23"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="21">
         <v>16</v>
       </c>
@@ -7267,13 +7267,13 @@
       </c>
       <c r="E31" s="21"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="66"/>
-      <c r="J31" s="66"/>
-      <c r="K31" s="66"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
       <c r="L31" s="23"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="21">
         <v>17</v>
       </c>
@@ -7284,12 +7284,12 @@
         <v>6</v>
       </c>
       <c r="E32" s="21"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="66"/>
-      <c r="K32" s="66"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H32" s="67"/>
+      <c r="I32" s="67"/>
+      <c r="J32" s="67"/>
+      <c r="K32" s="67"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="21">
         <v>18</v>
       </c>
@@ -7300,12 +7300,12 @@
         <v>5</v>
       </c>
       <c r="E33" s="21"/>
-      <c r="H33" s="66"/>
-      <c r="I33" s="66"/>
-      <c r="J33" s="66"/>
-      <c r="K33" s="66"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H33" s="67"/>
+      <c r="I33" s="67"/>
+      <c r="J33" s="67"/>
+      <c r="K33" s="67"/>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="21">
         <v>19</v>
       </c>
@@ -7316,12 +7316,12 @@
         <v>7</v>
       </c>
       <c r="E34" s="21"/>
-      <c r="H34" s="66"/>
-      <c r="I34" s="66"/>
-      <c r="J34" s="66"/>
-      <c r="K34" s="66"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H34" s="67"/>
+      <c r="I34" s="67"/>
+      <c r="J34" s="67"/>
+      <c r="K34" s="67"/>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="21">
         <v>20</v>
       </c>
@@ -7335,17 +7335,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D37" s="54" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="39" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B39" s="47" t="s">
         <v>244</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="40" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B40" s="48" t="s">
         <v>245</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="41" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="21">
         <v>1</v>
       </c>
@@ -7369,7 +7369,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="21">
         <v>2</v>
       </c>
@@ -7377,7 +7377,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="21">
         <v>3</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="21">
         <v>4</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="21">
         <v>5</v>
       </c>
@@ -7401,7 +7401,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="21">
         <v>6</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="21">
         <v>7</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="21">
         <v>8</v>
       </c>
@@ -7425,12 +7425,12 @@
         <v>316</v>
       </c>
     </row>
-    <row r="51" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B51" s="47" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="52" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B52" s="48" t="s">
         <v>237</v>
       </c>
@@ -7455,15 +7455,15 @@
       <c r="I52" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="J52" s="67" t="s">
+      <c r="J52" s="68" t="s">
         <v>425</v>
       </c>
-      <c r="K52" s="67"/>
+      <c r="K52" s="68"/>
       <c r="L52" s="2" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" s="21">
         <v>1</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" s="21">
         <v>2</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B55" s="21">
         <v>3</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56" s="21">
         <v>4</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B57" s="21">
         <v>5</v>
       </c>
@@ -7616,7 +7616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B58" s="21">
         <v>6</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B59" s="21">
         <v>7</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B60" s="21">
         <v>8</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B61" s="21">
         <v>9</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B62" s="21">
         <v>10</v>
       </c>
@@ -7761,15 +7761,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L63" s="4"/>
     </row>
-    <row r="65" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B65" s="47" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="66" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B66" s="48" t="s">
         <v>267</v>
       </c>
@@ -7791,10 +7791,10 @@
       <c r="H66" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="I66" s="67" t="s">
+      <c r="I66" s="68" t="s">
         <v>452</v>
       </c>
-      <c r="J66" s="67"/>
+      <c r="J66" s="68"/>
       <c r="K66" s="2" t="s">
         <v>453</v>
       </c>
@@ -7802,7 +7802,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B67" s="21">
         <v>1</v>
       </c>
@@ -7831,7 +7831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B68" s="21">
         <v>2</v>
       </c>
@@ -7862,7 +7862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B69" s="21">
         <v>3</v>
       </c>
@@ -7893,7 +7893,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B70" s="21">
         <v>4</v>
       </c>
@@ -7924,7 +7924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B71" s="21">
         <v>5</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B72" s="21">
         <v>6</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B73" s="21">
         <v>7</v>
       </c>
@@ -8013,7 +8013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B74" s="21">
         <v>8</v>
       </c>
@@ -8042,7 +8042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B75" s="21">
         <v>9</v>
       </c>
@@ -8071,7 +8071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B76" s="21">
         <v>10</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B77" s="21">
         <v>11</v>
       </c>
@@ -8129,7 +8129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B78" s="21">
         <v>12</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B79" s="21">
         <v>13</v>
       </c>
@@ -8187,13 +8187,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B82" s="47" t="s">
         <v>261</v>
       </c>
       <c r="C82" s="23"/>
     </row>
-    <row r="83" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B83" s="48" t="s">
         <v>461</v>
       </c>
@@ -8201,7 +8201,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B84" s="21">
         <v>1</v>
       </c>
@@ -8209,7 +8209,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B85" s="21">
         <v>2</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B86" s="21">
         <v>3</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B87" s="21">
         <v>4</v>
       </c>
@@ -8233,15 +8233,15 @@
         <v>338</v>
       </c>
     </row>
-    <row r="88" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B88" s="49"/>
     </row>
-    <row r="89" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B89" s="47" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="90" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B90" s="48" t="s">
         <v>230</v>
       </c>
@@ -8267,7 +8267,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B91" s="21">
         <v>1</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92" s="21">
         <v>2</v>
       </c>
@@ -8319,7 +8319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B93" s="21">
         <v>3</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B94" s="21">
         <v>4</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B95" s="21">
         <v>5</v>
       </c>
@@ -8397,7 +8397,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96" s="21">
         <v>6</v>
       </c>
@@ -8423,7 +8423,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B97" s="21">
         <v>7</v>
       </c>
@@ -8449,7 +8449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B98" s="21">
         <v>8</v>
       </c>
@@ -8475,7 +8475,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B99" s="21">
         <v>9</v>
       </c>
@@ -8501,7 +8501,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B100" s="21">
         <v>10</v>
       </c>
@@ -8527,7 +8527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="23" t="s">
         <v>477</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="23" t="s">
         <v>477</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="23" t="s">
         <v>477</v>
       </c>
@@ -8614,12 +8614,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B107" s="47" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B108" s="48" t="s">
         <v>274</v>
       </c>
@@ -8633,62 +8633,62 @@
         <v>277</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B110" s="66" t="s">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B110" s="67" t="s">
         <v>476</v>
       </c>
-      <c r="C110" s="64"/>
-      <c r="D110" s="64"/>
-      <c r="E110" s="64"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B111" s="64"/>
-      <c r="C111" s="64"/>
-      <c r="D111" s="64"/>
-      <c r="E111" s="64"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B112" s="64"/>
-      <c r="C112" s="64"/>
-      <c r="D112" s="64"/>
-      <c r="E112" s="64"/>
-    </row>
-    <row r="113" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="64"/>
-      <c r="C113" s="64"/>
-      <c r="D113" s="64"/>
-      <c r="E113" s="64"/>
+      <c r="C110" s="65"/>
+      <c r="D110" s="65"/>
+      <c r="E110" s="65"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B111" s="65"/>
+      <c r="C111" s="65"/>
+      <c r="D111" s="65"/>
+      <c r="E111" s="65"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B112" s="65"/>
+      <c r="C112" s="65"/>
+      <c r="D112" s="65"/>
+      <c r="E112" s="65"/>
+    </row>
+    <row r="113" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="65"/>
+      <c r="C113" s="65"/>
+      <c r="D113" s="65"/>
+      <c r="E113" s="65"/>
       <c r="F113" s="23"/>
       <c r="G113" s="23"/>
       <c r="H113" s="23"/>
       <c r="I113" s="23"/>
     </row>
-    <row r="114" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B114" s="64"/>
-      <c r="C114" s="64"/>
-      <c r="D114" s="64"/>
-      <c r="E114" s="64"/>
+    <row r="114" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B114" s="65"/>
+      <c r="C114" s="65"/>
+      <c r="D114" s="65"/>
+      <c r="E114" s="65"/>
       <c r="F114" s="58"/>
       <c r="G114" s="58"/>
       <c r="H114" s="59"/>
       <c r="I114" s="59"/>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B115" s="64"/>
-      <c r="C115" s="64"/>
-      <c r="D115" s="64"/>
-      <c r="E115" s="64"/>
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B115" s="65"/>
+      <c r="C115" s="65"/>
+      <c r="D115" s="65"/>
+      <c r="E115" s="65"/>
       <c r="G115" s="23"/>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D116" s="23"/>
       <c r="G116" s="23"/>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D117" s="23"/>
       <c r="G117" s="23"/>
     </row>
-    <row r="118" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B118" s="47" t="s">
         <v>306</v>
       </c>
@@ -8696,7 +8696,7 @@
       <c r="D118" s="23"/>
       <c r="G118" s="23"/>
     </row>
-    <row r="119" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B119" s="48" t="s">
         <v>279</v>
       </c>
@@ -8708,27 +8708,27 @@
       </c>
       <c r="G119" s="23"/>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B120" s="65" t="s">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B120" s="66" t="s">
         <v>415</v>
       </c>
-      <c r="C120" s="65"/>
-      <c r="D120" s="65"/>
+      <c r="C120" s="66"/>
+      <c r="D120" s="66"/>
       <c r="G120" s="23"/>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B121" s="65"/>
-      <c r="C121" s="65"/>
-      <c r="D121" s="65"/>
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B121" s="66"/>
+      <c r="C121" s="66"/>
+      <c r="D121" s="66"/>
       <c r="G121" s="23"/>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B122" s="65"/>
-      <c r="C122" s="65"/>
-      <c r="D122" s="65"/>
+    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B122" s="66"/>
+      <c r="C122" s="66"/>
+      <c r="D122" s="66"/>
       <c r="G122" s="23"/>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B123" s="21">
         <v>1</v>
       </c>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="G123" s="23"/>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B124" s="21">
         <v>1</v>
       </c>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="G124" s="23"/>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B125" s="21">
         <v>2</v>
       </c>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="G125" s="23"/>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B126" s="21">
         <v>2</v>
       </c>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="G126" s="23"/>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B127" s="21">
         <v>3</v>
       </c>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="G127" s="23"/>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B128" s="21">
         <v>3</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B129" s="21">
         <v>4</v>
       </c>
@@ -8810,7 +8810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B130" s="21">
         <v>4</v>
       </c>
@@ -8821,7 +8821,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131" s="21">
         <v>5</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132" s="21">
         <v>5</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B133" s="21">
         <v>5</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B134" s="21">
         <v>5</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135" s="21">
         <v>6</v>
       </c>
@@ -8876,7 +8876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136" s="21">
         <v>7</v>
       </c>
@@ -8887,7 +8887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="21">
         <v>8</v>
       </c>
@@ -8898,7 +8898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="21">
         <v>8</v>
       </c>
@@ -8909,7 +8909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="21">
         <v>8</v>
       </c>
@@ -8920,7 +8920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="21">
         <v>9</v>
       </c>
@@ -8931,7 +8931,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="21">
         <v>9</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="21">
         <v>9</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="21">
         <v>9</v>
       </c>
@@ -8964,7 +8964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="21">
         <v>9</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="21">
         <v>10</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="21">
         <v>10</v>
       </c>
@@ -8997,7 +8997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="21">
         <v>11</v>
       </c>
@@ -9008,7 +9008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="21">
         <v>11</v>
       </c>
@@ -9019,7 +9019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B149" s="21">
         <v>11</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B150" s="21">
         <v>11</v>
       </c>
@@ -9041,7 +9041,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B151" s="21">
         <v>11</v>
       </c>
@@ -9052,7 +9052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B152" s="21">
         <v>11</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B153" s="21">
         <v>12</v>
       </c>
@@ -9074,7 +9074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" s="21">
         <v>13</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B155" s="21">
         <v>13</v>
       </c>
@@ -9096,12 +9096,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159" s="1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" s="36" t="s">
         <v>289</v>
       </c>
@@ -9112,35 +9112,35 @@
         <v>291</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B161" s="21">
         <v>1</v>
       </c>
       <c r="C161" s="21"/>
       <c r="D161" s="21"/>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B162" s="21">
         <v>2</v>
       </c>
       <c r="C162" s="21"/>
       <c r="D162" s="21"/>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B163" s="21">
         <v>3</v>
       </c>
       <c r="C163" s="21"/>
       <c r="D163" s="21"/>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B164" s="21">
         <v>4</v>
       </c>
       <c r="C164" s="21"/>
       <c r="D164" s="21"/>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165" s="21">
         <v>5</v>
       </c>
@@ -9151,7 +9151,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166" s="21">
         <v>6</v>
       </c>
@@ -9160,40 +9160,40 @@
         <v>480</v>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167" s="21">
         <v>7</v>
       </c>
       <c r="C167" s="21"/>
       <c r="D167" s="21"/>
     </row>
-    <row r="168" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168" s="21">
         <v>8</v>
       </c>
       <c r="C168" s="21"/>
       <c r="D168" s="21"/>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169" s="21">
         <v>9</v>
       </c>
       <c r="C169" s="21"/>
       <c r="D169" s="21"/>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B170" s="21">
         <v>10</v>
       </c>
       <c r="C170" s="21"/>
       <c r="D170" s="21"/>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B173" s="1" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B174" s="30" t="s">
         <v>284</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B175" s="3">
         <v>1</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="176" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B176" s="3">
         <v>2</v>
       </c>
@@ -9226,7 +9226,7 @@
         <v>23456</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B177" s="3">
         <v>3</v>
       </c>
@@ -9237,7 +9237,7 @@
         <v>34567</v>
       </c>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B178" s="3">
         <v>4</v>
       </c>
@@ -9248,7 +9248,7 @@
         <v>72727</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B179" s="3">
         <v>5</v>
       </c>
@@ -9259,7 +9259,7 @@
         <v>28282</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B182" s="1" t="s">
         <v>297</v>
       </c>
@@ -9268,7 +9268,7 @@
       <c r="E182" s="23"/>
       <c r="F182" s="23"/>
     </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B183" s="36" t="s">
         <v>293</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B184" s="23" t="s">
         <v>487</v>
       </c>
@@ -9302,14 +9302,14 @@
         <v>491</v>
       </c>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B185" s="23"/>
       <c r="C185" s="23"/>
       <c r="D185" s="23"/>
       <c r="E185" s="23"/>
       <c r="F185" s="23"/>
     </row>
-    <row r="186" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B186" s="23">
         <v>1</v>
       </c>
@@ -9320,7 +9320,7 @@
       <c r="E186" s="23"/>
       <c r="F186" s="23"/>
     </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B187" s="23">
         <v>2</v>
       </c>
@@ -9331,7 +9331,7 @@
       <c r="E187" s="23"/>
       <c r="F187" s="23"/>
     </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B188" s="23">
         <v>3</v>
       </c>
@@ -9342,7 +9342,7 @@
       <c r="E188" s="23"/>
       <c r="F188" s="23"/>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B189" s="23">
         <v>4</v>
       </c>
@@ -9353,7 +9353,7 @@
       <c r="E189" s="23"/>
       <c r="F189" s="23"/>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B190" s="23">
         <v>5</v>
       </c>
@@ -9364,7 +9364,7 @@
       <c r="E190" s="23"/>
       <c r="F190" s="23"/>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B191" s="23">
         <v>6</v>
       </c>
@@ -9375,7 +9375,7 @@
       <c r="E191" s="23"/>
       <c r="F191" s="23"/>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B192" s="23"/>
       <c r="C192" s="23" t="s">
         <v>490</v>
@@ -9384,7 +9384,7 @@
       <c r="E192" s="23"/>
       <c r="F192" s="23"/>
     </row>
-    <row r="193" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B193" s="23">
         <v>10</v>
       </c>
@@ -9395,7 +9395,7 @@
       <c r="E193" s="23"/>
       <c r="F193" s="23"/>
     </row>
-    <row r="194" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B194" s="23">
         <v>1</v>
       </c>
@@ -9406,7 +9406,7 @@
       <c r="E194" s="23"/>
       <c r="F194" s="23"/>
     </row>
-    <row r="195" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B195" s="23"/>
       <c r="C195" s="23" t="s">
         <v>490</v>
@@ -9415,7 +9415,7 @@
       <c r="E195" s="23"/>
       <c r="F195" s="23"/>
     </row>
-    <row r="196" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B196" s="23">
         <v>10</v>
       </c>
@@ -9426,7 +9426,7 @@
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
     </row>
-    <row r="197" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B197" s="4"/>
       <c r="C197" s="4" t="s">
         <v>490</v>
@@ -9435,7 +9435,7 @@
       <c r="E197" s="4"/>
       <c r="F197" s="4"/>
     </row>
-    <row r="198" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B198" s="61">
         <v>3</v>
       </c>
@@ -9446,7 +9446,7 @@
       <c r="E198" s="4"/>
       <c r="F198" s="4"/>
     </row>
-    <row r="199" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B199" s="61">
         <v>6</v>
       </c>
@@ -9457,7 +9457,7 @@
       <c r="E199" s="4"/>
       <c r="F199" s="4"/>
     </row>
-    <row r="200" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B200" s="61">
         <v>9</v>
       </c>
@@ -9468,7 +9468,7 @@
       <c r="E200" s="4"/>
       <c r="F200" s="4"/>
     </row>
-    <row r="201" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>

--- a/1. Database Design/Java23 QuyenPhan Database Design.xlsx
+++ b/1. Database Design/Java23 QuyenPhan Database Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java23\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E68749-AECD-42AF-B262-33C7D66849E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073230FE-10E8-482F-9BB5-82DDDD166741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="588" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="588" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
@@ -5672,7 +5672,7 @@
       <c r="L4" s="62" t="s">
         <v>247</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="62" t="s">
         <v>250</v>
       </c>
       <c r="N4" s="62" t="s">

--- a/1. Database Design/Java23 QuyenPhan Database Design.xlsx
+++ b/1. Database Design/Java23 QuyenPhan Database Design.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java23\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073230FE-10E8-482F-9BB5-82DDDD166741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42EA9C7-8B32-4247-AAC1-F852AF13E118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="588" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1620" windowWidth="29040" windowHeight="17640" tabRatio="588" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
@@ -372,7 +372,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="511">
   <si>
     <t>MatHang</t>
   </si>
@@ -2053,6 +2053,21 @@
   </si>
   <si>
     <t>nv13@gmail.com</t>
+  </si>
+  <si>
+    <t>1-N</t>
+  </si>
+  <si>
+    <t>MatHang - LoaiHang</t>
+  </si>
+  <si>
+    <t>N-N</t>
+  </si>
+  <si>
+    <t>DonHang - HoaDon</t>
+  </si>
+  <si>
+    <t>MatHang - DonHang</t>
   </si>
 </sst>
 </file>
@@ -2332,7 +2347,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2517,6 +2532,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2540,15 +2556,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>42134</xdr:colOff>
+      <xdr:colOff>918434</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>58144</xdr:rowOff>
+      <xdr:rowOff>220069</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1190022</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>64163</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>704247</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>35588</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2571,8 +2587,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1046181" y="2693768"/>
-          <a:ext cx="3666970" cy="2767148"/>
+          <a:off x="1899509" y="2848969"/>
+          <a:ext cx="3595813" cy="2787319"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5507,14 +5523,32 @@
       <c r="H40" s="23"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>506</v>
+      </c>
+      <c r="D41" t="s">
+        <v>507</v>
+      </c>
       <c r="G41" s="23"/>
       <c r="H41" s="23"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C42" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" t="s">
+        <v>509</v>
+      </c>
       <c r="G42" s="23"/>
       <c r="H42" s="23"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>508</v>
+      </c>
+      <c r="D43" t="s">
+        <v>510</v>
+      </c>
       <c r="G43" s="23"/>
       <c r="H43" s="23"/>
     </row>
